--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4191,43 +4191,85 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D90" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E90" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1131</v>
+        <v>0.1143</v>
       </c>
       <c r="G90" t="n">
         <v>47.5</v>
       </c>
       <c r="H90" t="n">
-        <v>25.5</v>
+        <v>26.3</v>
       </c>
       <c r="I90" t="n">
-        <v>222.3</v>
+        <v>221.7</v>
       </c>
       <c r="J90" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="K90" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="L90" t="n">
-        <v>33.9</v>
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>218</v>
+      </c>
+      <c r="D91" t="n">
+        <v>218</v>
+      </c>
+      <c r="E91" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.1143</v>
+      </c>
+      <c r="G91" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="I91" t="n">
+        <v>221.7</v>
+      </c>
+      <c r="J91" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="K91" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="L91" t="n">
+        <v>34.6</v>
       </c>
     </row>
   </sheetData>
@@ -4241,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R90"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9619,19 +9661,19 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D90" t="n">
-        <v>0.4457</v>
+        <v>0.4464</v>
       </c>
       <c r="E90" t="n">
         <v>45.60888944834404</v>
@@ -9646,13 +9688,13 @@
         <v>465</v>
       </c>
       <c r="I90" t="n">
-        <v>0.4457</v>
+        <v>0.4464</v>
       </c>
       <c r="J90" t="n">
         <v>0.2471</v>
       </c>
       <c r="K90" t="n">
-        <v>0.3072</v>
+        <v>0.3065</v>
       </c>
       <c r="L90" t="n">
         <v>-2.4694</v>
@@ -9661,19 +9703,79 @@
         <v>3.5973</v>
       </c>
       <c r="N90" t="n">
-        <v>0.2346</v>
+        <v>0.2389</v>
       </c>
       <c r="O90" t="n">
-        <v>1.8389</v>
+        <v>1.8438</v>
       </c>
       <c r="P90" t="n">
-        <v>50.95</v>
+        <v>50.89</v>
       </c>
       <c r="Q90" t="n">
-        <v>49.05</v>
+        <v>49.11</v>
       </c>
       <c r="R90" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>218</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="E91" t="n">
+        <v>45.60888944834404</v>
+      </c>
+      <c r="F91" t="n">
+        <v>41.82180942093328</v>
+      </c>
+      <c r="G91" t="n">
+        <v>3.833948100564366</v>
+      </c>
+      <c r="H91" t="n">
+        <v>465</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.2471</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-2.4694</v>
+      </c>
+      <c r="M91" t="n">
+        <v>3.5973</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.2389</v>
+      </c>
+      <c r="O91" t="n">
+        <v>1.8438</v>
+      </c>
+      <c r="P91" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>49.11</v>
+      </c>
+      <c r="R91" t="n">
+        <v>1.79</v>
       </c>
     </row>
   </sheetData>
@@ -9687,7 +9789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J90"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12913,16 +13015,16 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D90" t="n">
         <v>42.84</v>
@@ -12943,6 +13045,42 @@
         <v>5.41</v>
       </c>
       <c r="J90" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-03-30</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>218</v>
+      </c>
+      <c r="D91" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="E91" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="F91" t="n">
+        <v>-11.24</v>
+      </c>
+      <c r="G91" t="n">
+        <v>30</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="I91" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="J91" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4233,43 +4233,85 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D91" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E91" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="F91" t="n">
-        <v>0.1143</v>
+        <v>0.1154</v>
       </c>
       <c r="G91" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="H91" t="n">
-        <v>26.3</v>
+        <v>15.2</v>
       </c>
       <c r="I91" t="n">
-        <v>221.7</v>
+        <v>222.6</v>
       </c>
       <c r="J91" t="n">
-        <v>50.4</v>
+        <v>52</v>
       </c>
       <c r="K91" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="L91" t="n">
-        <v>34.6</v>
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>217</v>
+      </c>
+      <c r="D92" t="n">
+        <v>217</v>
+      </c>
+      <c r="E92" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.1154</v>
+      </c>
+      <c r="G92" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="H92" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>222.6</v>
+      </c>
+      <c r="J92" t="n">
+        <v>52</v>
+      </c>
+      <c r="K92" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="L92" t="n">
+        <v>26.5</v>
       </c>
     </row>
   </sheetData>
@@ -4283,7 +4325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:R92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9721,61 +9763,121 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D91" t="n">
-        <v>0.4464</v>
+        <v>0.4471</v>
       </c>
       <c r="E91" t="n">
-        <v>45.60888944834404</v>
+        <v>45.69314064017149</v>
       </c>
       <c r="F91" t="n">
-        <v>41.82180942093328</v>
+        <v>41.85788655348188</v>
       </c>
       <c r="G91" t="n">
-        <v>3.833948100564366</v>
+        <v>3.880459839312738</v>
       </c>
       <c r="H91" t="n">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="I91" t="n">
-        <v>0.4464</v>
+        <v>0.4471</v>
       </c>
       <c r="J91" t="n">
-        <v>0.2471</v>
+        <v>0.2472</v>
       </c>
       <c r="K91" t="n">
-        <v>0.3065</v>
+        <v>0.3057</v>
       </c>
       <c r="L91" t="n">
-        <v>-2.4694</v>
+        <v>-2.4755</v>
       </c>
       <c r="M91" t="n">
-        <v>3.5973</v>
+        <v>3.6343</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2389</v>
+        <v>0.2564</v>
       </c>
       <c r="O91" t="n">
-        <v>1.8438</v>
+        <v>1.8768</v>
       </c>
       <c r="P91" t="n">
-        <v>50.89</v>
+        <v>50.96</v>
       </c>
       <c r="Q91" t="n">
-        <v>49.11</v>
+        <v>49.04</v>
       </c>
       <c r="R91" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>217</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="E92" t="n">
+        <v>45.69314064017149</v>
+      </c>
+      <c r="F92" t="n">
+        <v>41.85788655348188</v>
+      </c>
+      <c r="G92" t="n">
+        <v>3.880459839312738</v>
+      </c>
+      <c r="H92" t="n">
+        <v>470</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.2472</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-2.4755</v>
+      </c>
+      <c r="M92" t="n">
+        <v>3.6343</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="O92" t="n">
+        <v>1.8768</v>
+      </c>
+      <c r="P92" t="n">
+        <v>50.96</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>49.04</v>
+      </c>
+      <c r="R92" t="n">
+        <v>1.93</v>
       </c>
     </row>
   </sheetData>
@@ -9789,7 +9891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13051,36 +13153,72 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D91" t="n">
-        <v>42.84</v>
+        <v>42.77</v>
       </c>
       <c r="E91" t="n">
-        <v>54.08</v>
+        <v>54.1</v>
       </c>
       <c r="F91" t="n">
-        <v>-11.24</v>
+        <v>-11.33</v>
       </c>
       <c r="G91" t="n">
         <v>30</v>
       </c>
       <c r="H91" t="n">
-        <v>-5.41</v>
+        <v>-5.42</v>
       </c>
       <c r="I91" t="n">
-        <v>5.41</v>
+        <v>5.42</v>
       </c>
       <c r="J91" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>217</v>
+      </c>
+      <c r="D92" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E92" t="n">
+        <v>54.1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>-11.33</v>
+      </c>
+      <c r="G92" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I92" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J92" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,28 +510,28 @@
         <v>306</v>
       </c>
       <c r="E2" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
       <c r="F2" t="n">
         <v>0.0476</v>
       </c>
       <c r="G2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H2" t="n">
-        <v>22.4</v>
+        <v>32.1</v>
       </c>
       <c r="I2" t="n">
-        <v>218.8</v>
+        <v>228.9</v>
       </c>
       <c r="J2" t="n">
-        <v>48.3</v>
+        <v>54.1</v>
       </c>
       <c r="K2" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="L2" t="n">
-        <v>29.2</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="3">
@@ -552,28 +552,28 @@
         <v>305</v>
       </c>
       <c r="E3" t="n">
-        <v>1.07</v>
+        <v>3.01</v>
       </c>
       <c r="F3" t="n">
         <v>0.0481</v>
       </c>
       <c r="G3" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
       <c r="H3" t="n">
-        <v>24.1</v>
+        <v>30.8</v>
       </c>
       <c r="I3" t="n">
-        <v>217.8</v>
+        <v>228.2</v>
       </c>
       <c r="J3" t="n">
-        <v>45.7</v>
+        <v>53.1</v>
       </c>
       <c r="K3" t="n">
-        <v>20.9</v>
+        <v>21.9</v>
       </c>
       <c r="L3" t="n">
-        <v>27.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="4">
@@ -594,28 +594,28 @@
         <v>304</v>
       </c>
       <c r="E4" t="n">
-        <v>1.15</v>
+        <v>3.17</v>
       </c>
       <c r="F4" t="n">
         <v>0.0486</v>
       </c>
       <c r="G4" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="H4" t="n">
-        <v>21.7</v>
+        <v>31.1</v>
       </c>
       <c r="I4" t="n">
-        <v>218.6</v>
+        <v>229.4</v>
       </c>
       <c r="J4" t="n">
-        <v>47.5</v>
+        <v>53.9</v>
       </c>
       <c r="K4" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="L4" t="n">
-        <v>28.6</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="5">
@@ -636,28 +636,28 @@
         <v>303</v>
       </c>
       <c r="E5" t="n">
-        <v>1.07</v>
+        <v>2.84</v>
       </c>
       <c r="F5" t="n">
         <v>0.049</v>
       </c>
       <c r="G5" t="n">
-        <v>47</v>
+        <v>47.9</v>
       </c>
       <c r="H5" t="n">
-        <v>26</v>
+        <v>29.7</v>
       </c>
       <c r="I5" t="n">
-        <v>218.2</v>
+        <v>227.9</v>
       </c>
       <c r="J5" t="n">
-        <v>48</v>
+        <v>51.6</v>
       </c>
       <c r="K5" t="n">
-        <v>21.1</v>
+        <v>21.8</v>
       </c>
       <c r="L5" t="n">
-        <v>29.3</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="6">
@@ -678,28 +678,28 @@
         <v>302</v>
       </c>
       <c r="E6" t="n">
-        <v>1.14</v>
+        <v>3.07</v>
       </c>
       <c r="F6" t="n">
         <v>0.0495</v>
       </c>
       <c r="G6" t="n">
-        <v>46.8</v>
+        <v>48</v>
       </c>
       <c r="H6" t="n">
-        <v>21.2</v>
+        <v>31.1</v>
       </c>
       <c r="I6" t="n">
-        <v>218.4</v>
+        <v>228.8</v>
       </c>
       <c r="J6" t="n">
-        <v>48.7</v>
+        <v>54.1</v>
       </c>
       <c r="K6" t="n">
-        <v>21.1</v>
+        <v>22</v>
       </c>
       <c r="L6" t="n">
-        <v>28</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="7">
@@ -720,28 +720,28 @@
         <v>301</v>
       </c>
       <c r="E7" t="n">
-        <v>1.37</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>0.05</v>
       </c>
       <c r="G7" t="n">
-        <v>47.1</v>
+        <v>48</v>
       </c>
       <c r="H7" t="n">
-        <v>23.2</v>
+        <v>31.2</v>
       </c>
       <c r="I7" t="n">
-        <v>219.5</v>
+        <v>228.5</v>
       </c>
       <c r="J7" t="n">
-        <v>48.8</v>
+        <v>53.2</v>
       </c>
       <c r="K7" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="L7" t="n">
-        <v>29.5</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="8">
@@ -762,28 +762,28 @@
         <v>300</v>
       </c>
       <c r="E8" t="n">
-        <v>1.13</v>
+        <v>2.9</v>
       </c>
       <c r="F8" t="n">
         <v>0.0505</v>
       </c>
       <c r="G8" t="n">
-        <v>47</v>
+        <v>47.9</v>
       </c>
       <c r="H8" t="n">
-        <v>23.5</v>
+        <v>30.2</v>
       </c>
       <c r="I8" t="n">
-        <v>218.8</v>
+        <v>227.3</v>
       </c>
       <c r="J8" t="n">
-        <v>47.9</v>
+        <v>51.9</v>
       </c>
       <c r="K8" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="L8" t="n">
-        <v>29</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="9">
@@ -804,28 +804,28 @@
         <v>299</v>
       </c>
       <c r="E9" t="n">
-        <v>0.98</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>0.051</v>
       </c>
       <c r="G9" t="n">
-        <v>46.9</v>
+        <v>47.9</v>
       </c>
       <c r="H9" t="n">
-        <v>23.5</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
-        <v>218.1</v>
+        <v>227.6</v>
       </c>
       <c r="J9" t="n">
-        <v>49.7</v>
+        <v>53.9</v>
       </c>
       <c r="K9" t="n">
-        <v>21.1</v>
+        <v>21.8</v>
       </c>
       <c r="L9" t="n">
-        <v>27.7</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="10">
@@ -846,28 +846,28 @@
         <v>298</v>
       </c>
       <c r="E10" t="n">
-        <v>1.14</v>
+        <v>2.82</v>
       </c>
       <c r="F10" t="n">
         <v>0.0516</v>
       </c>
       <c r="G10" t="n">
-        <v>47.1</v>
+        <v>47.9</v>
       </c>
       <c r="H10" t="n">
-        <v>23.3</v>
+        <v>31</v>
       </c>
       <c r="I10" t="n">
-        <v>219.2</v>
+        <v>226.4</v>
       </c>
       <c r="J10" t="n">
-        <v>48.8</v>
+        <v>52.3</v>
       </c>
       <c r="K10" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="L10" t="n">
-        <v>29.1</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="11">
@@ -888,28 +888,28 @@
         <v>297</v>
       </c>
       <c r="E11" t="n">
-        <v>1.28</v>
+        <v>3.19</v>
       </c>
       <c r="F11" t="n">
         <v>0.0521</v>
       </c>
       <c r="G11" t="n">
-        <v>47</v>
+        <v>48.1</v>
       </c>
       <c r="H11" t="n">
-        <v>23.6</v>
+        <v>30.8</v>
       </c>
       <c r="I11" t="n">
-        <v>219.3</v>
+        <v>229.1</v>
       </c>
       <c r="J11" t="n">
-        <v>48.2</v>
+        <v>52.5</v>
       </c>
       <c r="K11" t="n">
-        <v>21.2</v>
+        <v>22</v>
       </c>
       <c r="L11" t="n">
-        <v>29.4</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="12">
@@ -930,28 +930,28 @@
         <v>296</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2</v>
+        <v>3.09</v>
       </c>
       <c r="F12" t="n">
         <v>0.0526</v>
       </c>
       <c r="G12" t="n">
-        <v>47.1</v>
+        <v>48</v>
       </c>
       <c r="H12" t="n">
-        <v>22.6</v>
+        <v>31.2</v>
       </c>
       <c r="I12" t="n">
-        <v>219.2</v>
+        <v>228.3</v>
       </c>
       <c r="J12" t="n">
-        <v>48.3</v>
+        <v>52.2</v>
       </c>
       <c r="K12" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="L12" t="n">
-        <v>27.8</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="13">
@@ -972,28 +972,28 @@
         <v>295</v>
       </c>
       <c r="E13" t="n">
-        <v>1.42</v>
+        <v>2.97</v>
       </c>
       <c r="F13" t="n">
         <v>0.0531</v>
       </c>
       <c r="G13" t="n">
-        <v>47.3</v>
+        <v>48.1</v>
       </c>
       <c r="H13" t="n">
-        <v>25.1</v>
+        <v>30.3</v>
       </c>
       <c r="I13" t="n">
-        <v>220.6</v>
+        <v>228.8</v>
       </c>
       <c r="J13" t="n">
-        <v>49.6</v>
+        <v>53.1</v>
       </c>
       <c r="K13" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="L13" t="n">
-        <v>30.1</v>
+        <v>36.8</v>
       </c>
     </row>
     <row r="14">
@@ -1014,28 +1014,28 @@
         <v>294</v>
       </c>
       <c r="E14" t="n">
-        <v>1.51</v>
+        <v>3.3</v>
       </c>
       <c r="F14" t="n">
         <v>0.0536</v>
       </c>
       <c r="G14" t="n">
-        <v>47.2</v>
+        <v>48.2</v>
       </c>
       <c r="H14" t="n">
-        <v>23.4</v>
+        <v>30.9</v>
       </c>
       <c r="I14" t="n">
-        <v>220.1</v>
+        <v>229.9</v>
       </c>
       <c r="J14" t="n">
-        <v>48.9</v>
+        <v>54.9</v>
       </c>
       <c r="K14" t="n">
-        <v>21.3</v>
+        <v>22.1</v>
       </c>
       <c r="L14" t="n">
-        <v>30.6</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="15">
@@ -1056,28 +1056,28 @@
         <v>293</v>
       </c>
       <c r="E15" t="n">
-        <v>1.37</v>
+        <v>3.12</v>
       </c>
       <c r="F15" t="n">
         <v>0.0542</v>
       </c>
       <c r="G15" t="n">
-        <v>47.1</v>
+        <v>48.1</v>
       </c>
       <c r="H15" t="n">
-        <v>24.7</v>
+        <v>30.2</v>
       </c>
       <c r="I15" t="n">
-        <v>219.3</v>
+        <v>229.2</v>
       </c>
       <c r="J15" t="n">
-        <v>47.6</v>
+        <v>52.5</v>
       </c>
       <c r="K15" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="L15" t="n">
-        <v>29.2</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="16">
@@ -1098,28 +1098,28 @@
         <v>292</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>2.62</v>
       </c>
       <c r="F16" t="n">
         <v>0.0547</v>
       </c>
       <c r="G16" t="n">
-        <v>47.1</v>
+        <v>47.9</v>
       </c>
       <c r="H16" t="n">
-        <v>24.6</v>
+        <v>29.6</v>
       </c>
       <c r="I16" t="n">
-        <v>219.7</v>
+        <v>226.8</v>
       </c>
       <c r="J16" t="n">
-        <v>48.8</v>
+        <v>52.5</v>
       </c>
       <c r="K16" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="L16" t="n">
-        <v>30.4</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="17">
@@ -1140,28 +1140,28 @@
         <v>291</v>
       </c>
       <c r="E17" t="n">
-        <v>1.47</v>
+        <v>2.52</v>
       </c>
       <c r="F17" t="n">
         <v>0.0553</v>
       </c>
       <c r="G17" t="n">
-        <v>47.2</v>
+        <v>47.9</v>
       </c>
       <c r="H17" t="n">
-        <v>24.9</v>
+        <v>29.9</v>
       </c>
       <c r="I17" t="n">
-        <v>220.1</v>
+        <v>226.4</v>
       </c>
       <c r="J17" t="n">
-        <v>48.3</v>
+        <v>51</v>
       </c>
       <c r="K17" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="L17" t="n">
-        <v>28.6</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="18">
@@ -1182,28 +1182,28 @@
         <v>290</v>
       </c>
       <c r="E18" t="n">
-        <v>1.32</v>
+        <v>2.47</v>
       </c>
       <c r="F18" t="n">
         <v>0.0558</v>
       </c>
       <c r="G18" t="n">
-        <v>47.1</v>
+        <v>47.9</v>
       </c>
       <c r="H18" t="n">
-        <v>23.6</v>
+        <v>30</v>
       </c>
       <c r="I18" t="n">
-        <v>219.6</v>
+        <v>226.3</v>
       </c>
       <c r="J18" t="n">
-        <v>49</v>
+        <v>51.8</v>
       </c>
       <c r="K18" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="L18" t="n">
-        <v>30</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="19">
@@ -1224,28 +1224,28 @@
         <v>289</v>
       </c>
       <c r="E19" t="n">
-        <v>1.21</v>
+        <v>2.61</v>
       </c>
       <c r="F19" t="n">
         <v>0.0564</v>
       </c>
       <c r="G19" t="n">
-        <v>47.1</v>
+        <v>47.9</v>
       </c>
       <c r="H19" t="n">
-        <v>22.7</v>
+        <v>30.1</v>
       </c>
       <c r="I19" t="n">
-        <v>219</v>
+        <v>226.7</v>
       </c>
       <c r="J19" t="n">
-        <v>48.7</v>
+        <v>52.4</v>
       </c>
       <c r="K19" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="L19" t="n">
-        <v>29.5</v>
+        <v>34.9</v>
       </c>
     </row>
     <row r="20">
@@ -1266,28 +1266,28 @@
         <v>288</v>
       </c>
       <c r="E20" t="n">
-        <v>1.26</v>
+        <v>2.55</v>
       </c>
       <c r="F20" t="n">
         <v>0.0569</v>
       </c>
       <c r="G20" t="n">
-        <v>47.2</v>
+        <v>48</v>
       </c>
       <c r="H20" t="n">
-        <v>22.3</v>
+        <v>30.1</v>
       </c>
       <c r="I20" t="n">
-        <v>219.3</v>
+        <v>226.7</v>
       </c>
       <c r="J20" t="n">
-        <v>49.2</v>
+        <v>53</v>
       </c>
       <c r="K20" t="n">
-        <v>21.1</v>
+        <v>21.8</v>
       </c>
       <c r="L20" t="n">
-        <v>27.4</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="21">
@@ -1308,28 +1308,28 @@
         <v>287</v>
       </c>
       <c r="E21" t="n">
-        <v>1.17</v>
+        <v>2.63</v>
       </c>
       <c r="F21" t="n">
         <v>0.0575</v>
       </c>
       <c r="G21" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H21" t="n">
-        <v>22.1</v>
+        <v>30</v>
       </c>
       <c r="I21" t="n">
-        <v>218.4</v>
+        <v>226.9</v>
       </c>
       <c r="J21" t="n">
-        <v>46.1</v>
+        <v>53.1</v>
       </c>
       <c r="K21" t="n">
-        <v>21.1</v>
+        <v>21.7</v>
       </c>
       <c r="L21" t="n">
-        <v>29.6</v>
+        <v>35.2</v>
       </c>
     </row>
     <row r="22">
@@ -1350,28 +1350,28 @@
         <v>286</v>
       </c>
       <c r="E22" t="n">
-        <v>1.13</v>
+        <v>2.6</v>
       </c>
       <c r="F22" t="n">
         <v>0.0581</v>
       </c>
       <c r="G22" t="n">
-        <v>47.1</v>
+        <v>47.8</v>
       </c>
       <c r="H22" t="n">
-        <v>24.5</v>
+        <v>30.5</v>
       </c>
       <c r="I22" t="n">
-        <v>218.7</v>
+        <v>225.6</v>
       </c>
       <c r="J22" t="n">
-        <v>47.8</v>
+        <v>50.8</v>
       </c>
       <c r="K22" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="L22" t="n">
-        <v>28.8</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="23">
@@ -1392,28 +1392,28 @@
         <v>285</v>
       </c>
       <c r="E23" t="n">
-        <v>1.4</v>
+        <v>2.71</v>
       </c>
       <c r="F23" t="n">
         <v>0.0587</v>
       </c>
       <c r="G23" t="n">
-        <v>47.2</v>
+        <v>47.9</v>
       </c>
       <c r="H23" t="n">
-        <v>22.6</v>
+        <v>30.5</v>
       </c>
       <c r="I23" t="n">
-        <v>220</v>
+        <v>226.7</v>
       </c>
       <c r="J23" t="n">
-        <v>48.1</v>
+        <v>53.1</v>
       </c>
       <c r="K23" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="L23" t="n">
-        <v>29.7</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="24">
@@ -1434,28 +1434,28 @@
         <v>284</v>
       </c>
       <c r="E24" t="n">
-        <v>1.22</v>
+        <v>2.66</v>
       </c>
       <c r="F24" t="n">
         <v>0.0593</v>
       </c>
       <c r="G24" t="n">
-        <v>47</v>
+        <v>47.8</v>
       </c>
       <c r="H24" t="n">
-        <v>23.5</v>
+        <v>29.7</v>
       </c>
       <c r="I24" t="n">
-        <v>218.8</v>
+        <v>226.4</v>
       </c>
       <c r="J24" t="n">
-        <v>48.3</v>
+        <v>52.9</v>
       </c>
       <c r="K24" t="n">
-        <v>21.1</v>
+        <v>21.7</v>
       </c>
       <c r="L24" t="n">
-        <v>31.5</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="25">
@@ -1476,28 +1476,28 @@
         <v>283</v>
       </c>
       <c r="E25" t="n">
-        <v>1.41</v>
+        <v>2.73</v>
       </c>
       <c r="F25" t="n">
         <v>0.0598</v>
       </c>
       <c r="G25" t="n">
-        <v>47.2</v>
+        <v>48</v>
       </c>
       <c r="H25" t="n">
-        <v>23.6</v>
+        <v>30</v>
       </c>
       <c r="I25" t="n">
-        <v>220.1</v>
+        <v>227.5</v>
       </c>
       <c r="J25" t="n">
-        <v>48</v>
+        <v>53.3</v>
       </c>
       <c r="K25" t="n">
-        <v>21.2</v>
+        <v>21.9</v>
       </c>
       <c r="L25" t="n">
-        <v>28.7</v>
+        <v>34.3</v>
       </c>
     </row>
     <row r="26">
@@ -1518,28 +1518,28 @@
         <v>282</v>
       </c>
       <c r="E26" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
       <c r="F26" t="n">
         <v>0.0604</v>
       </c>
       <c r="G26" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H26" t="n">
-        <v>22.4</v>
+        <v>31.7</v>
       </c>
       <c r="I26" t="n">
-        <v>218.9</v>
+        <v>227.1</v>
       </c>
       <c r="J26" t="n">
-        <v>46.9</v>
+        <v>53.1</v>
       </c>
       <c r="K26" t="n">
-        <v>21.1</v>
+        <v>21.8</v>
       </c>
       <c r="L26" t="n">
-        <v>27.7</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="27">
@@ -1560,28 +1560,28 @@
         <v>281</v>
       </c>
       <c r="E27" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
       <c r="F27" t="n">
         <v>0.0611</v>
       </c>
       <c r="G27" t="n">
-        <v>47.2</v>
+        <v>47.9</v>
       </c>
       <c r="H27" t="n">
-        <v>24.6</v>
+        <v>29.3</v>
       </c>
       <c r="I27" t="n">
-        <v>220.5</v>
+        <v>226.4</v>
       </c>
       <c r="J27" t="n">
-        <v>48.6</v>
+        <v>53.5</v>
       </c>
       <c r="K27" t="n">
-        <v>21.4</v>
+        <v>21.7</v>
       </c>
       <c r="L27" t="n">
-        <v>29.1</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="28">
@@ -1602,28 +1602,28 @@
         <v>280</v>
       </c>
       <c r="E28" t="n">
-        <v>1.45</v>
+        <v>2.65</v>
       </c>
       <c r="F28" t="n">
         <v>0.0617</v>
       </c>
       <c r="G28" t="n">
-        <v>47.1</v>
+        <v>47.8</v>
       </c>
       <c r="H28" t="n">
-        <v>22.6</v>
+        <v>29.5</v>
       </c>
       <c r="I28" t="n">
-        <v>219.1</v>
+        <v>226.5</v>
       </c>
       <c r="J28" t="n">
-        <v>46.5</v>
+        <v>52.7</v>
       </c>
       <c r="K28" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="L28" t="n">
-        <v>28.2</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="29">
@@ -1644,28 +1644,28 @@
         <v>279</v>
       </c>
       <c r="E29" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
       <c r="F29" t="n">
         <v>0.0623</v>
       </c>
       <c r="G29" t="n">
-        <v>47.3</v>
+        <v>47.9</v>
       </c>
       <c r="H29" t="n">
-        <v>24.1</v>
+        <v>30.3</v>
       </c>
       <c r="I29" t="n">
-        <v>221.1</v>
+        <v>227.4</v>
       </c>
       <c r="J29" t="n">
-        <v>50.4</v>
+        <v>53.6</v>
       </c>
       <c r="K29" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="L29" t="n">
-        <v>30.4</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="30">
@@ -1686,28 +1686,28 @@
         <v>278</v>
       </c>
       <c r="E30" t="n">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
       <c r="F30" t="n">
         <v>0.0629</v>
       </c>
       <c r="G30" t="n">
-        <v>47.2</v>
+        <v>47.9</v>
       </c>
       <c r="H30" t="n">
-        <v>23.3</v>
+        <v>28.8</v>
       </c>
       <c r="I30" t="n">
-        <v>220.4</v>
+        <v>227.2</v>
       </c>
       <c r="J30" t="n">
-        <v>51.2</v>
+        <v>52.4</v>
       </c>
       <c r="K30" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="L30" t="n">
-        <v>28.4</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="31">
@@ -1728,28 +1728,28 @@
         <v>277</v>
       </c>
       <c r="E31" t="n">
-        <v>1.42</v>
+        <v>2.89</v>
       </c>
       <c r="F31" t="n">
         <v>0.0635</v>
       </c>
       <c r="G31" t="n">
-        <v>47.4</v>
+        <v>47.9</v>
       </c>
       <c r="H31" t="n">
-        <v>24.7</v>
+        <v>28.9</v>
       </c>
       <c r="I31" t="n">
-        <v>220.9</v>
+        <v>227.2</v>
       </c>
       <c r="J31" t="n">
-        <v>50.6</v>
+        <v>52.3</v>
       </c>
       <c r="K31" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="L31" t="n">
-        <v>28.7</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="32">
@@ -1770,28 +1770,28 @@
         <v>276</v>
       </c>
       <c r="E32" t="n">
-        <v>1.38</v>
+        <v>2.78</v>
       </c>
       <c r="F32" t="n">
         <v>0.06419999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>47.2</v>
+        <v>48.1</v>
       </c>
       <c r="H32" t="n">
-        <v>25</v>
+        <v>31.1</v>
       </c>
       <c r="I32" t="n">
-        <v>220</v>
+        <v>227.9</v>
       </c>
       <c r="J32" t="n">
-        <v>49.1</v>
+        <v>53.5</v>
       </c>
       <c r="K32" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="L32" t="n">
-        <v>29.1</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="33">
@@ -1812,28 +1812,28 @@
         <v>275</v>
       </c>
       <c r="E33" t="n">
-        <v>1.35</v>
+        <v>2.65</v>
       </c>
       <c r="F33" t="n">
         <v>0.0648</v>
       </c>
       <c r="G33" t="n">
-        <v>47.2</v>
+        <v>47.8</v>
       </c>
       <c r="H33" t="n">
-        <v>23.5</v>
+        <v>29.1</v>
       </c>
       <c r="I33" t="n">
-        <v>219.8</v>
+        <v>226.6</v>
       </c>
       <c r="J33" t="n">
-        <v>49.9</v>
+        <v>52.2</v>
       </c>
       <c r="K33" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="L33" t="n">
-        <v>29</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="34">
@@ -1854,28 +1854,28 @@
         <v>274</v>
       </c>
       <c r="E34" t="n">
-        <v>1.53</v>
+        <v>2.67</v>
       </c>
       <c r="F34" t="n">
         <v>0.0655</v>
       </c>
       <c r="G34" t="n">
-        <v>47.2</v>
+        <v>47.7</v>
       </c>
       <c r="H34" t="n">
-        <v>24.8</v>
+        <v>28.9</v>
       </c>
       <c r="I34" t="n">
-        <v>220.3</v>
+        <v>225.8</v>
       </c>
       <c r="J34" t="n">
-        <v>48.8</v>
+        <v>50.7</v>
       </c>
       <c r="K34" t="n">
-        <v>21.2</v>
+        <v>21.5</v>
       </c>
       <c r="L34" t="n">
-        <v>30.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -1896,28 +1896,28 @@
         <v>273</v>
       </c>
       <c r="E35" t="n">
-        <v>1.33</v>
+        <v>2.77</v>
       </c>
       <c r="F35" t="n">
         <v>0.06610000000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>47.1</v>
+        <v>47.8</v>
       </c>
       <c r="H35" t="n">
-        <v>23.3</v>
+        <v>28</v>
       </c>
       <c r="I35" t="n">
-        <v>219.3</v>
+        <v>226.8</v>
       </c>
       <c r="J35" t="n">
-        <v>47.7</v>
+        <v>52.2</v>
       </c>
       <c r="K35" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="L35" t="n">
-        <v>28.8</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="36">
@@ -1938,28 +1938,28 @@
         <v>272</v>
       </c>
       <c r="E36" t="n">
-        <v>1.35</v>
+        <v>2.62</v>
       </c>
       <c r="F36" t="n">
         <v>0.0668</v>
       </c>
       <c r="G36" t="n">
-        <v>47.2</v>
+        <v>47.9</v>
       </c>
       <c r="H36" t="n">
-        <v>25.4</v>
+        <v>28.9</v>
       </c>
       <c r="I36" t="n">
-        <v>220.2</v>
+        <v>226.8</v>
       </c>
       <c r="J36" t="n">
-        <v>49.1</v>
+        <v>51.9</v>
       </c>
       <c r="K36" t="n">
-        <v>21.3</v>
+        <v>21.7</v>
       </c>
       <c r="L36" t="n">
-        <v>29.8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
@@ -1980,28 +1980,28 @@
         <v>271</v>
       </c>
       <c r="E37" t="n">
-        <v>1.24</v>
+        <v>2.61</v>
       </c>
       <c r="F37" t="n">
         <v>0.0674</v>
       </c>
       <c r="G37" t="n">
-        <v>47.2</v>
+        <v>47.9</v>
       </c>
       <c r="H37" t="n">
-        <v>24.8</v>
+        <v>29.5</v>
       </c>
       <c r="I37" t="n">
-        <v>219.8</v>
+        <v>226.4</v>
       </c>
       <c r="J37" t="n">
-        <v>48.7</v>
+        <v>52.8</v>
       </c>
       <c r="K37" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="L37" t="n">
-        <v>28.5</v>
+        <v>31.4</v>
       </c>
     </row>
     <row r="38">
@@ -2022,28 +2022,28 @@
         <v>270</v>
       </c>
       <c r="E38" t="n">
-        <v>1.31</v>
+        <v>2.46</v>
       </c>
       <c r="F38" t="n">
         <v>0.06809999999999999</v>
       </c>
       <c r="G38" t="n">
-        <v>47.2</v>
+        <v>48</v>
       </c>
       <c r="H38" t="n">
-        <v>22.8</v>
+        <v>29.5</v>
       </c>
       <c r="I38" t="n">
-        <v>219.8</v>
+        <v>226.5</v>
       </c>
       <c r="J38" t="n">
-        <v>48.9</v>
+        <v>52.7</v>
       </c>
       <c r="K38" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="L38" t="n">
-        <v>28.8</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="39">
@@ -2064,28 +2064,28 @@
         <v>269</v>
       </c>
       <c r="E39" t="n">
-        <v>1.43</v>
+        <v>2.61</v>
       </c>
       <c r="F39" t="n">
         <v>0.0688</v>
       </c>
       <c r="G39" t="n">
-        <v>47.3</v>
+        <v>48</v>
       </c>
       <c r="H39" t="n">
-        <v>25.3</v>
+        <v>29.8</v>
       </c>
       <c r="I39" t="n">
-        <v>220.7</v>
+        <v>226.9</v>
       </c>
       <c r="J39" t="n">
-        <v>50</v>
+        <v>53.6</v>
       </c>
       <c r="K39" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="L39" t="n">
-        <v>30.2</v>
+        <v>34.1</v>
       </c>
     </row>
     <row r="40">
@@ -2106,28 +2106,28 @@
         <v>268</v>
       </c>
       <c r="E40" t="n">
-        <v>1.35</v>
+        <v>2.76</v>
       </c>
       <c r="F40" t="n">
         <v>0.06950000000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>47.2</v>
+        <v>48</v>
       </c>
       <c r="H40" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I40" t="n">
-        <v>220.4</v>
+        <v>227.5</v>
       </c>
       <c r="J40" t="n">
-        <v>48.4</v>
+        <v>53.2</v>
       </c>
       <c r="K40" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="L40" t="n">
-        <v>29.9</v>
+        <v>34</v>
       </c>
     </row>
     <row r="41">
@@ -2148,28 +2148,28 @@
         <v>267</v>
       </c>
       <c r="E41" t="n">
-        <v>1.19</v>
+        <v>2.39</v>
       </c>
       <c r="F41" t="n">
         <v>0.0702</v>
       </c>
       <c r="G41" t="n">
-        <v>47.1</v>
+        <v>47.9</v>
       </c>
       <c r="H41" t="n">
-        <v>22.8</v>
+        <v>30</v>
       </c>
       <c r="I41" t="n">
-        <v>219.1</v>
+        <v>225.8</v>
       </c>
       <c r="J41" t="n">
-        <v>47.7</v>
+        <v>50.8</v>
       </c>
       <c r="K41" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="L41" t="n">
-        <v>29.3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="42">
@@ -2190,28 +2190,28 @@
         <v>266</v>
       </c>
       <c r="E42" t="n">
-        <v>1.45</v>
+        <v>2.74</v>
       </c>
       <c r="F42" t="n">
         <v>0.0709</v>
       </c>
       <c r="G42" t="n">
-        <v>47.2</v>
+        <v>47.9</v>
       </c>
       <c r="H42" t="n">
-        <v>24.1</v>
+        <v>28.7</v>
       </c>
       <c r="I42" t="n">
-        <v>220.3</v>
+        <v>227.3</v>
       </c>
       <c r="J42" t="n">
-        <v>49.8</v>
+        <v>53.1</v>
       </c>
       <c r="K42" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="L42" t="n">
-        <v>28.7</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="43">
@@ -2232,28 +2232,28 @@
         <v>265</v>
       </c>
       <c r="E43" t="n">
-        <v>1.56</v>
+        <v>2.57</v>
       </c>
       <c r="F43" t="n">
         <v>0.0716</v>
       </c>
       <c r="G43" t="n">
-        <v>47.4</v>
+        <v>47.9</v>
       </c>
       <c r="H43" t="n">
-        <v>24.2</v>
+        <v>28.7</v>
       </c>
       <c r="I43" t="n">
-        <v>221.7</v>
+        <v>226</v>
       </c>
       <c r="J43" t="n">
-        <v>51.4</v>
+        <v>51.1</v>
       </c>
       <c r="K43" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="L43" t="n">
-        <v>28.7</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="44">
@@ -2274,28 +2274,28 @@
         <v>264</v>
       </c>
       <c r="E44" t="n">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
       <c r="F44" t="n">
         <v>0.0723</v>
       </c>
       <c r="G44" t="n">
-        <v>47.2</v>
+        <v>48</v>
       </c>
       <c r="H44" t="n">
-        <v>23.8</v>
+        <v>29.5</v>
       </c>
       <c r="I44" t="n">
-        <v>220.1</v>
+        <v>226.9</v>
       </c>
       <c r="J44" t="n">
-        <v>48.6</v>
+        <v>52.3</v>
       </c>
       <c r="K44" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="L44" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45">
@@ -2316,28 +2316,28 @@
         <v>263</v>
       </c>
       <c r="E45" t="n">
-        <v>1.44</v>
+        <v>3.01</v>
       </c>
       <c r="F45" t="n">
         <v>0.073</v>
       </c>
       <c r="G45" t="n">
-        <v>47.2</v>
+        <v>48</v>
       </c>
       <c r="H45" t="n">
-        <v>25.1</v>
+        <v>27.8</v>
       </c>
       <c r="I45" t="n">
-        <v>219.9</v>
+        <v>228.1</v>
       </c>
       <c r="J45" t="n">
-        <v>48.9</v>
+        <v>53.4</v>
       </c>
       <c r="K45" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="L45" t="n">
-        <v>29.4</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="46">
@@ -2358,28 +2358,28 @@
         <v>262</v>
       </c>
       <c r="E46" t="n">
-        <v>1.5</v>
+        <v>2.59</v>
       </c>
       <c r="F46" t="n">
         <v>0.0738</v>
       </c>
       <c r="G46" t="n">
-        <v>47.3</v>
+        <v>47.9</v>
       </c>
       <c r="H46" t="n">
-        <v>23.3</v>
+        <v>29.8</v>
       </c>
       <c r="I46" t="n">
-        <v>221.1</v>
+        <v>226.1</v>
       </c>
       <c r="J46" t="n">
-        <v>51.2</v>
+        <v>51.9</v>
       </c>
       <c r="K46" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="L46" t="n">
-        <v>30.6</v>
+        <v>34.4</v>
       </c>
     </row>
     <row r="47">
@@ -2400,28 +2400,28 @@
         <v>261</v>
       </c>
       <c r="E47" t="n">
-        <v>1.51</v>
+        <v>2.96</v>
       </c>
       <c r="F47" t="n">
         <v>0.0745</v>
       </c>
       <c r="G47" t="n">
-        <v>47.2</v>
+        <v>48</v>
       </c>
       <c r="H47" t="n">
-        <v>23.6</v>
+        <v>29</v>
       </c>
       <c r="I47" t="n">
-        <v>220.6</v>
+        <v>228.2</v>
       </c>
       <c r="J47" t="n">
-        <v>48.2</v>
+        <v>52.2</v>
       </c>
       <c r="K47" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="L47" t="n">
-        <v>27.7</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="48">
@@ -2442,28 +2442,28 @@
         <v>260</v>
       </c>
       <c r="E48" t="n">
-        <v>1.51</v>
+        <v>2.72</v>
       </c>
       <c r="F48" t="n">
         <v>0.0752</v>
       </c>
       <c r="G48" t="n">
-        <v>47.3</v>
+        <v>48</v>
       </c>
       <c r="H48" t="n">
-        <v>23.8</v>
+        <v>30.7</v>
       </c>
       <c r="I48" t="n">
-        <v>220.8</v>
+        <v>227.4</v>
       </c>
       <c r="J48" t="n">
-        <v>49.8</v>
+        <v>52.1</v>
       </c>
       <c r="K48" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="L48" t="n">
-        <v>30.6</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="49">
@@ -2484,28 +2484,28 @@
         <v>259</v>
       </c>
       <c r="E49" t="n">
-        <v>1.25</v>
+        <v>2.69</v>
       </c>
       <c r="F49" t="n">
         <v>0.076</v>
       </c>
       <c r="G49" t="n">
-        <v>47.2</v>
+        <v>48.1</v>
       </c>
       <c r="H49" t="n">
-        <v>23.7</v>
+        <v>31.5</v>
       </c>
       <c r="I49" t="n">
-        <v>219.5</v>
+        <v>227.1</v>
       </c>
       <c r="J49" t="n">
-        <v>48.9</v>
+        <v>53.5</v>
       </c>
       <c r="K49" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="L49" t="n">
-        <v>28.8</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="50">
@@ -2526,28 +2526,28 @@
         <v>258</v>
       </c>
       <c r="E50" t="n">
-        <v>1.53</v>
+        <v>2.81</v>
       </c>
       <c r="F50" t="n">
         <v>0.07679999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>47.3</v>
+        <v>48.1</v>
       </c>
       <c r="H50" t="n">
-        <v>27.1</v>
+        <v>29.2</v>
       </c>
       <c r="I50" t="n">
-        <v>220.4</v>
+        <v>227.6</v>
       </c>
       <c r="J50" t="n">
-        <v>49.4</v>
+        <v>52.9</v>
       </c>
       <c r="K50" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="L50" t="n">
-        <v>29</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="51">
@@ -2568,28 +2568,28 @@
         <v>257</v>
       </c>
       <c r="E51" t="n">
-        <v>1.47</v>
+        <v>2.63</v>
       </c>
       <c r="F51" t="n">
         <v>0.0775</v>
       </c>
       <c r="G51" t="n">
-        <v>47.2</v>
+        <v>47.9</v>
       </c>
       <c r="H51" t="n">
-        <v>26.7</v>
+        <v>28.4</v>
       </c>
       <c r="I51" t="n">
-        <v>220.2</v>
+        <v>226.4</v>
       </c>
       <c r="J51" t="n">
-        <v>48.8</v>
+        <v>52.9</v>
       </c>
       <c r="K51" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="L51" t="n">
-        <v>30.2</v>
+        <v>32</v>
       </c>
     </row>
     <row r="52">
@@ -2610,28 +2610,28 @@
         <v>256</v>
       </c>
       <c r="E52" t="n">
-        <v>1.69</v>
+        <v>2.86</v>
       </c>
       <c r="F52" t="n">
         <v>0.07829999999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>47.4</v>
+        <v>48</v>
       </c>
       <c r="H52" t="n">
-        <v>24.6</v>
+        <v>28.6</v>
       </c>
       <c r="I52" t="n">
-        <v>221.5</v>
+        <v>227.8</v>
       </c>
       <c r="J52" t="n">
-        <v>49.8</v>
+        <v>53</v>
       </c>
       <c r="K52" t="n">
-        <v>21.5</v>
+        <v>21.9</v>
       </c>
       <c r="L52" t="n">
-        <v>28.9</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="53">
@@ -2652,28 +2652,28 @@
         <v>255</v>
       </c>
       <c r="E53" t="n">
-        <v>1.47</v>
+        <v>2.88</v>
       </c>
       <c r="F53" t="n">
         <v>0.0791</v>
       </c>
       <c r="G53" t="n">
-        <v>47.3</v>
+        <v>48.1</v>
       </c>
       <c r="H53" t="n">
-        <v>24.3</v>
+        <v>29.6</v>
       </c>
       <c r="I53" t="n">
-        <v>220.6</v>
+        <v>228.1</v>
       </c>
       <c r="J53" t="n">
-        <v>49.5</v>
+        <v>54.5</v>
       </c>
       <c r="K53" t="n">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="L53" t="n">
-        <v>30.6</v>
+        <v>33.7</v>
       </c>
     </row>
     <row r="54">
@@ -2694,28 +2694,28 @@
         <v>254</v>
       </c>
       <c r="E54" t="n">
-        <v>1.44</v>
+        <v>2.96</v>
       </c>
       <c r="F54" t="n">
         <v>0.0799</v>
       </c>
       <c r="G54" t="n">
-        <v>47.2</v>
+        <v>48.1</v>
       </c>
       <c r="H54" t="n">
-        <v>24.6</v>
+        <v>30.5</v>
       </c>
       <c r="I54" t="n">
-        <v>220.4</v>
+        <v>228.4</v>
       </c>
       <c r="J54" t="n">
-        <v>48.4</v>
+        <v>53.4</v>
       </c>
       <c r="K54" t="n">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
       <c r="L54" t="n">
-        <v>32.3</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="55">
@@ -2736,28 +2736,28 @@
         <v>253</v>
       </c>
       <c r="E55" t="n">
-        <v>1.59</v>
+        <v>2.98</v>
       </c>
       <c r="F55" t="n">
         <v>0.08069999999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>47.4</v>
+        <v>48.1</v>
       </c>
       <c r="H55" t="n">
-        <v>25.1</v>
+        <v>29.4</v>
       </c>
       <c r="I55" t="n">
-        <v>221.4</v>
+        <v>228.6</v>
       </c>
       <c r="J55" t="n">
-        <v>50</v>
+        <v>53.7</v>
       </c>
       <c r="K55" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="L55" t="n">
-        <v>33.7</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="56">
@@ -2778,28 +2778,28 @@
         <v>252</v>
       </c>
       <c r="E56" t="n">
-        <v>1.38</v>
+        <v>2.94</v>
       </c>
       <c r="F56" t="n">
         <v>0.0815</v>
       </c>
       <c r="G56" t="n">
-        <v>47.2</v>
+        <v>48</v>
       </c>
       <c r="H56" t="n">
-        <v>24.8</v>
+        <v>28.4</v>
       </c>
       <c r="I56" t="n">
-        <v>219.8</v>
+        <v>228</v>
       </c>
       <c r="J56" t="n">
-        <v>47.4</v>
+        <v>52.9</v>
       </c>
       <c r="K56" t="n">
-        <v>21.3</v>
+        <v>22</v>
       </c>
       <c r="L56" t="n">
-        <v>32.2</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="57">
@@ -2820,28 +2820,28 @@
         <v>251</v>
       </c>
       <c r="E57" t="n">
-        <v>1.72</v>
+        <v>2.96</v>
       </c>
       <c r="F57" t="n">
         <v>0.0823</v>
       </c>
       <c r="G57" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
       <c r="H57" t="n">
-        <v>24.6</v>
+        <v>31.5</v>
       </c>
       <c r="I57" t="n">
-        <v>221.9</v>
+        <v>228.5</v>
       </c>
       <c r="J57" t="n">
-        <v>49.9</v>
+        <v>54.1</v>
       </c>
       <c r="K57" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="L57" t="n">
-        <v>33.8</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="58">
@@ -2862,28 +2862,28 @@
         <v>250</v>
       </c>
       <c r="E58" t="n">
-        <v>1.91</v>
+        <v>2.84</v>
       </c>
       <c r="F58" t="n">
         <v>0.08309999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>47.6</v>
+        <v>47.9</v>
       </c>
       <c r="H58" t="n">
-        <v>24.6</v>
+        <v>28.7</v>
       </c>
       <c r="I58" t="n">
-        <v>222.7</v>
+        <v>226.7</v>
       </c>
       <c r="J58" t="n">
-        <v>51</v>
+        <v>52.2</v>
       </c>
       <c r="K58" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="L58" t="n">
-        <v>34.1</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="59">
@@ -2904,28 +2904,28 @@
         <v>249</v>
       </c>
       <c r="E59" t="n">
-        <v>1.72</v>
+        <v>2.91</v>
       </c>
       <c r="F59" t="n">
         <v>0.0839</v>
       </c>
       <c r="G59" t="n">
-        <v>47.4</v>
+        <v>48.1</v>
       </c>
       <c r="H59" t="n">
-        <v>23.8</v>
+        <v>29.8</v>
       </c>
       <c r="I59" t="n">
-        <v>221.8</v>
+        <v>228</v>
       </c>
       <c r="J59" t="n">
-        <v>49.3</v>
+        <v>53.5</v>
       </c>
       <c r="K59" t="n">
-        <v>21.5</v>
+        <v>22</v>
       </c>
       <c r="L59" t="n">
-        <v>31.3</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="60">
@@ -2946,28 +2946,28 @@
         <v>248</v>
       </c>
       <c r="E60" t="n">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
       <c r="F60" t="n">
         <v>0.0848</v>
       </c>
       <c r="G60" t="n">
-        <v>47.4</v>
+        <v>48.1</v>
       </c>
       <c r="H60" t="n">
-        <v>25.1</v>
+        <v>29.6</v>
       </c>
       <c r="I60" t="n">
-        <v>222.1</v>
+        <v>228.2</v>
       </c>
       <c r="J60" t="n">
-        <v>49.8</v>
+        <v>53</v>
       </c>
       <c r="K60" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="L60" t="n">
-        <v>33.4</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="61">
@@ -2988,28 +2988,28 @@
         <v>247</v>
       </c>
       <c r="E61" t="n">
-        <v>1.6</v>
+        <v>3.03</v>
       </c>
       <c r="F61" t="n">
         <v>0.0856</v>
       </c>
       <c r="G61" t="n">
-        <v>47.3</v>
+        <v>48.2</v>
       </c>
       <c r="H61" t="n">
-        <v>23.8</v>
+        <v>29.5</v>
       </c>
       <c r="I61" t="n">
-        <v>220.8</v>
+        <v>229.2</v>
       </c>
       <c r="J61" t="n">
-        <v>50.2</v>
+        <v>53.8</v>
       </c>
       <c r="K61" t="n">
-        <v>21.4</v>
+        <v>22.2</v>
       </c>
       <c r="L61" t="n">
-        <v>33.4</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="62">
@@ -3030,28 +3030,28 @@
         <v>246</v>
       </c>
       <c r="E62" t="n">
-        <v>1.89</v>
+        <v>3.01</v>
       </c>
       <c r="F62" t="n">
         <v>0.08649999999999999</v>
       </c>
       <c r="G62" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="H62" t="n">
-        <v>25.3</v>
+        <v>28.6</v>
       </c>
       <c r="I62" t="n">
-        <v>222.1</v>
+        <v>227.8</v>
       </c>
       <c r="J62" t="n">
-        <v>50.9</v>
+        <v>53.2</v>
       </c>
       <c r="K62" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="L62" t="n">
-        <v>33.8</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63">
@@ -3072,28 +3072,28 @@
         <v>245</v>
       </c>
       <c r="E63" t="n">
-        <v>1.54</v>
+        <v>2.97</v>
       </c>
       <c r="F63" t="n">
         <v>0.08740000000000001</v>
       </c>
       <c r="G63" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="H63" t="n">
-        <v>25.8</v>
+        <v>30.2</v>
       </c>
       <c r="I63" t="n">
-        <v>221</v>
+        <v>228.6</v>
       </c>
       <c r="J63" t="n">
-        <v>49.2</v>
+        <v>54.6</v>
       </c>
       <c r="K63" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="L63" t="n">
-        <v>34.5</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="64">
@@ -3114,28 +3114,28 @@
         <v>244</v>
       </c>
       <c r="E64" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
       <c r="F64" t="n">
         <v>0.0882</v>
       </c>
       <c r="G64" t="n">
-        <v>47.6</v>
+        <v>48</v>
       </c>
       <c r="H64" t="n">
-        <v>26</v>
+        <v>28.2</v>
       </c>
       <c r="I64" t="n">
-        <v>222.7</v>
+        <v>227.7</v>
       </c>
       <c r="J64" t="n">
-        <v>50.1</v>
+        <v>51.7</v>
       </c>
       <c r="K64" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="L64" t="n">
-        <v>32.9</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="65">
@@ -3156,28 +3156,28 @@
         <v>243</v>
       </c>
       <c r="E65" t="n">
-        <v>1.74</v>
+        <v>2.86</v>
       </c>
       <c r="F65" t="n">
         <v>0.0891</v>
       </c>
       <c r="G65" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="H65" t="n">
-        <v>23.3</v>
+        <v>28.5</v>
       </c>
       <c r="I65" t="n">
-        <v>221.5</v>
+        <v>228.4</v>
       </c>
       <c r="J65" t="n">
-        <v>49.4</v>
+        <v>54.4</v>
       </c>
       <c r="K65" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="L65" t="n">
-        <v>33.5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="66">
@@ -3198,28 +3198,28 @@
         <v>242</v>
       </c>
       <c r="E66" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
       <c r="F66" t="n">
         <v>0.09</v>
       </c>
       <c r="G66" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="H66" t="n">
-        <v>24.8</v>
+        <v>29.5</v>
       </c>
       <c r="I66" t="n">
-        <v>221.8</v>
+        <v>228.9</v>
       </c>
       <c r="J66" t="n">
-        <v>50.3</v>
+        <v>53.2</v>
       </c>
       <c r="K66" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="L66" t="n">
-        <v>33</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="67">
@@ -3240,28 +3240,28 @@
         <v>241</v>
       </c>
       <c r="E67" t="n">
-        <v>1.7</v>
+        <v>2.89</v>
       </c>
       <c r="F67" t="n">
         <v>0.09089999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="H67" t="n">
-        <v>25</v>
+        <v>28.6</v>
       </c>
       <c r="I67" t="n">
-        <v>222</v>
+        <v>227.5</v>
       </c>
       <c r="J67" t="n">
-        <v>51.6</v>
+        <v>52.8</v>
       </c>
       <c r="K67" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="L67" t="n">
-        <v>33.2</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="68">
@@ -3282,28 +3282,28 @@
         <v>240</v>
       </c>
       <c r="E68" t="n">
-        <v>1.66</v>
+        <v>3.18</v>
       </c>
       <c r="F68" t="n">
         <v>0.09180000000000001</v>
       </c>
       <c r="G68" t="n">
-        <v>47.4</v>
+        <v>48.3</v>
       </c>
       <c r="H68" t="n">
-        <v>24.2</v>
+        <v>31.8</v>
       </c>
       <c r="I68" t="n">
-        <v>221.6</v>
+        <v>229.6</v>
       </c>
       <c r="J68" t="n">
-        <v>49.5</v>
+        <v>54.3</v>
       </c>
       <c r="K68" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="L68" t="n">
-        <v>33.7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69">
@@ -3324,28 +3324,28 @@
         <v>239</v>
       </c>
       <c r="E69" t="n">
-        <v>1.89</v>
+        <v>3</v>
       </c>
       <c r="F69" t="n">
         <v>0.0927</v>
       </c>
       <c r="G69" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
       <c r="H69" t="n">
-        <v>25.2</v>
+        <v>29.8</v>
       </c>
       <c r="I69" t="n">
-        <v>222.5</v>
+        <v>229.5</v>
       </c>
       <c r="J69" t="n">
-        <v>50.8</v>
+        <v>53.7</v>
       </c>
       <c r="K69" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="L69" t="n">
-        <v>34.1</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="70">
@@ -3366,28 +3366,28 @@
         <v>238</v>
       </c>
       <c r="E70" t="n">
-        <v>1.63</v>
+        <v>2.84</v>
       </c>
       <c r="F70" t="n">
         <v>0.09370000000000001</v>
       </c>
       <c r="G70" t="n">
-        <v>47.5</v>
+        <v>48.2</v>
       </c>
       <c r="H70" t="n">
-        <v>25.8</v>
+        <v>29.2</v>
       </c>
       <c r="I70" t="n">
-        <v>221.5</v>
+        <v>228.2</v>
       </c>
       <c r="J70" t="n">
-        <v>50.9</v>
+        <v>53.7</v>
       </c>
       <c r="K70" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="L70" t="n">
-        <v>34.7</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="71">
@@ -3408,28 +3408,28 @@
         <v>237</v>
       </c>
       <c r="E71" t="n">
-        <v>1.73</v>
+        <v>3.01</v>
       </c>
       <c r="F71" t="n">
         <v>0.0946</v>
       </c>
       <c r="G71" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="H71" t="n">
-        <v>23.5</v>
+        <v>29.2</v>
       </c>
       <c r="I71" t="n">
-        <v>221.3</v>
+        <v>228.3</v>
       </c>
       <c r="J71" t="n">
-        <v>49.6</v>
+        <v>53.9</v>
       </c>
       <c r="K71" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="L71" t="n">
-        <v>31.6</v>
+        <v>35.4</v>
       </c>
     </row>
     <row r="72">
@@ -3450,28 +3450,28 @@
         <v>236</v>
       </c>
       <c r="E72" t="n">
-        <v>1.76</v>
+        <v>3.07</v>
       </c>
       <c r="F72" t="n">
         <v>0.0955</v>
       </c>
       <c r="G72" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="H72" t="n">
-        <v>23.7</v>
+        <v>32.4</v>
       </c>
       <c r="I72" t="n">
-        <v>221.4</v>
+        <v>229.1</v>
       </c>
       <c r="J72" t="n">
-        <v>49.7</v>
+        <v>54.1</v>
       </c>
       <c r="K72" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="L72" t="n">
-        <v>31.4</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="73">
@@ -3492,28 +3492,28 @@
         <v>235</v>
       </c>
       <c r="E73" t="n">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
       <c r="F73" t="n">
         <v>0.0965</v>
       </c>
       <c r="G73" t="n">
-        <v>47.5</v>
+        <v>48</v>
       </c>
       <c r="H73" t="n">
-        <v>24.8</v>
+        <v>28.8</v>
       </c>
       <c r="I73" t="n">
-        <v>222.8</v>
+        <v>227.8</v>
       </c>
       <c r="J73" t="n">
-        <v>51.2</v>
+        <v>53.3</v>
       </c>
       <c r="K73" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="L73" t="n">
-        <v>35.3</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="74">
@@ -3534,28 +3534,28 @@
         <v>234</v>
       </c>
       <c r="E74" t="n">
-        <v>1.72</v>
+        <v>3.13</v>
       </c>
       <c r="F74" t="n">
         <v>0.0975</v>
       </c>
       <c r="G74" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
       <c r="H74" t="n">
-        <v>26</v>
+        <v>31.7</v>
       </c>
       <c r="I74" t="n">
-        <v>222.5</v>
+        <v>229.6</v>
       </c>
       <c r="J74" t="n">
-        <v>52</v>
+        <v>53.9</v>
       </c>
       <c r="K74" t="n">
-        <v>21.7</v>
+        <v>22.3</v>
       </c>
       <c r="L74" t="n">
-        <v>34.8</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="75">
@@ -3576,28 +3576,28 @@
         <v>233</v>
       </c>
       <c r="E75" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="F75" t="n">
         <v>0.0984</v>
       </c>
       <c r="G75" t="n">
-        <v>47.7</v>
+        <v>48.1</v>
       </c>
       <c r="H75" t="n">
-        <v>24.9</v>
+        <v>29.1</v>
       </c>
       <c r="I75" t="n">
-        <v>223.4</v>
+        <v>227.9</v>
       </c>
       <c r="J75" t="n">
-        <v>50.4</v>
+        <v>54.2</v>
       </c>
       <c r="K75" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="L75" t="n">
-        <v>34.3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76">
@@ -3618,28 +3618,28 @@
         <v>232</v>
       </c>
       <c r="E76" t="n">
-        <v>1.73</v>
+        <v>2.95</v>
       </c>
       <c r="F76" t="n">
         <v>0.0994</v>
       </c>
       <c r="G76" t="n">
-        <v>47.4</v>
+        <v>48.1</v>
       </c>
       <c r="H76" t="n">
-        <v>23.7</v>
+        <v>29</v>
       </c>
       <c r="I76" t="n">
-        <v>221.5</v>
+        <v>228.2</v>
       </c>
       <c r="J76" t="n">
-        <v>50.3</v>
+        <v>54</v>
       </c>
       <c r="K76" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="L76" t="n">
-        <v>33.5</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="77">
@@ -3660,28 +3660,28 @@
         <v>231</v>
       </c>
       <c r="E77" t="n">
-        <v>1.87</v>
+        <v>3.16</v>
       </c>
       <c r="F77" t="n">
         <v>0.1004</v>
       </c>
       <c r="G77" t="n">
-        <v>47.5</v>
+        <v>48.2</v>
       </c>
       <c r="H77" t="n">
-        <v>25.6</v>
+        <v>28</v>
       </c>
       <c r="I77" t="n">
-        <v>222.1</v>
+        <v>229.1</v>
       </c>
       <c r="J77" t="n">
-        <v>50.1</v>
+        <v>52.5</v>
       </c>
       <c r="K77" t="n">
-        <v>21.6</v>
+        <v>22</v>
       </c>
       <c r="L77" t="n">
-        <v>32.9</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="78">
@@ -3702,28 +3702,28 @@
         <v>230</v>
       </c>
       <c r="E78" t="n">
-        <v>1.79</v>
+        <v>3.12</v>
       </c>
       <c r="F78" t="n">
         <v>0.1014</v>
       </c>
       <c r="G78" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="H78" t="n">
-        <v>23.1</v>
+        <v>30.3</v>
       </c>
       <c r="I78" t="n">
-        <v>222.1</v>
+        <v>229.7</v>
       </c>
       <c r="J78" t="n">
-        <v>50</v>
+        <v>54.7</v>
       </c>
       <c r="K78" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="L78" t="n">
-        <v>32.8</v>
+        <v>36.4</v>
       </c>
     </row>
     <row r="79">
@@ -3744,28 +3744,28 @@
         <v>229</v>
       </c>
       <c r="E79" t="n">
-        <v>1.91</v>
+        <v>3.23</v>
       </c>
       <c r="F79" t="n">
         <v>0.1024</v>
       </c>
       <c r="G79" t="n">
-        <v>47.6</v>
+        <v>48.3</v>
       </c>
       <c r="H79" t="n">
-        <v>26.3</v>
+        <v>29.1</v>
       </c>
       <c r="I79" t="n">
-        <v>223.1</v>
+        <v>229.5</v>
       </c>
       <c r="J79" t="n">
-        <v>51.3</v>
+        <v>55</v>
       </c>
       <c r="K79" t="n">
-        <v>21.8</v>
+        <v>22.2</v>
       </c>
       <c r="L79" t="n">
-        <v>33.2</v>
+        <v>35.1</v>
       </c>
     </row>
     <row r="80">
@@ -3786,28 +3786,28 @@
         <v>228</v>
       </c>
       <c r="E80" t="n">
-        <v>1.97</v>
+        <v>3.06</v>
       </c>
       <c r="F80" t="n">
         <v>0.1034</v>
       </c>
       <c r="G80" t="n">
-        <v>47.7</v>
+        <v>48.2</v>
       </c>
       <c r="H80" t="n">
-        <v>26.3</v>
+        <v>29.6</v>
       </c>
       <c r="I80" t="n">
-        <v>223.3</v>
+        <v>229</v>
       </c>
       <c r="J80" t="n">
-        <v>51.2</v>
+        <v>54.8</v>
       </c>
       <c r="K80" t="n">
-        <v>21.7</v>
+        <v>22.2</v>
       </c>
       <c r="L80" t="n">
-        <v>34.3</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="81">
@@ -3828,28 +3828,28 @@
         <v>227</v>
       </c>
       <c r="E81" t="n">
-        <v>1.86</v>
+        <v>3.04</v>
       </c>
       <c r="F81" t="n">
         <v>0.1045</v>
       </c>
       <c r="G81" t="n">
-        <v>47.4</v>
+        <v>48.1</v>
       </c>
       <c r="H81" t="n">
-        <v>25.6</v>
+        <v>28</v>
       </c>
       <c r="I81" t="n">
-        <v>221.9</v>
+        <v>228.3</v>
       </c>
       <c r="J81" t="n">
-        <v>50.4</v>
+        <v>53.1</v>
       </c>
       <c r="K81" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="L81" t="n">
-        <v>33.9</v>
+        <v>35.6</v>
       </c>
     </row>
     <row r="82">
@@ -3870,28 +3870,28 @@
         <v>226</v>
       </c>
       <c r="E82" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
       <c r="F82" t="n">
         <v>0.1055</v>
       </c>
       <c r="G82" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="H82" t="n">
-        <v>24</v>
+        <v>29.1</v>
       </c>
       <c r="I82" t="n">
-        <v>221.5</v>
+        <v>229.2</v>
       </c>
       <c r="J82" t="n">
-        <v>49.5</v>
+        <v>53.6</v>
       </c>
       <c r="K82" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="L82" t="n">
-        <v>32.9</v>
+        <v>36.9</v>
       </c>
     </row>
     <row r="83">
@@ -3912,28 +3912,28 @@
         <v>225</v>
       </c>
       <c r="E83" t="n">
-        <v>1.89</v>
+        <v>3.29</v>
       </c>
       <c r="F83" t="n">
         <v>0.1066</v>
       </c>
       <c r="G83" t="n">
-        <v>47.6</v>
+        <v>48.4</v>
       </c>
       <c r="H83" t="n">
-        <v>27</v>
+        <v>29.8</v>
       </c>
       <c r="I83" t="n">
-        <v>222.3</v>
+        <v>230.5</v>
       </c>
       <c r="J83" t="n">
-        <v>49.4</v>
+        <v>55.1</v>
       </c>
       <c r="K83" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="L83" t="n">
-        <v>34.9</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="84">
@@ -3954,28 +3954,28 @@
         <v>224</v>
       </c>
       <c r="E84" t="n">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
       <c r="F84" t="n">
         <v>0.1076</v>
       </c>
       <c r="G84" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
       <c r="H84" t="n">
-        <v>25.1</v>
+        <v>30.4</v>
       </c>
       <c r="I84" t="n">
-        <v>222.7</v>
+        <v>229.8</v>
       </c>
       <c r="J84" t="n">
-        <v>50.7</v>
+        <v>53.8</v>
       </c>
       <c r="K84" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="L84" t="n">
-        <v>33.1</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="85">
@@ -3996,28 +3996,28 @@
         <v>223</v>
       </c>
       <c r="E85" t="n">
-        <v>1.89</v>
+        <v>2.96</v>
       </c>
       <c r="F85" t="n">
         <v>0.1087</v>
       </c>
       <c r="G85" t="n">
-        <v>47.5</v>
+        <v>48.2</v>
       </c>
       <c r="H85" t="n">
-        <v>26.6</v>
+        <v>29.7</v>
       </c>
       <c r="I85" t="n">
-        <v>222.4</v>
+        <v>228.7</v>
       </c>
       <c r="J85" t="n">
-        <v>51.2</v>
+        <v>54.3</v>
       </c>
       <c r="K85" t="n">
-        <v>21.7</v>
+        <v>22.3</v>
       </c>
       <c r="L85" t="n">
-        <v>33.5</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="86">
@@ -4038,28 +4038,28 @@
         <v>222</v>
       </c>
       <c r="E86" t="n">
-        <v>1.89</v>
+        <v>3.19</v>
       </c>
       <c r="F86" t="n">
         <v>0.1098</v>
       </c>
       <c r="G86" t="n">
-        <v>47.5</v>
+        <v>48.3</v>
       </c>
       <c r="H86" t="n">
-        <v>25.2</v>
+        <v>29.9</v>
       </c>
       <c r="I86" t="n">
-        <v>222.4</v>
+        <v>230</v>
       </c>
       <c r="J86" t="n">
-        <v>49.3</v>
+        <v>54.1</v>
       </c>
       <c r="K86" t="n">
-        <v>21.7</v>
+        <v>22.3</v>
       </c>
       <c r="L86" t="n">
-        <v>32.1</v>
+        <v>36.7</v>
       </c>
     </row>
     <row r="87">
@@ -4080,28 +4080,28 @@
         <v>221</v>
       </c>
       <c r="E87" t="n">
-        <v>1.83</v>
+        <v>3.33</v>
       </c>
       <c r="F87" t="n">
         <v>0.1109</v>
       </c>
       <c r="G87" t="n">
-        <v>47.4</v>
+        <v>48.3</v>
       </c>
       <c r="H87" t="n">
-        <v>23.5</v>
+        <v>30.7</v>
       </c>
       <c r="I87" t="n">
-        <v>222.2</v>
+        <v>230.3</v>
       </c>
       <c r="J87" t="n">
-        <v>50</v>
+        <v>54.9</v>
       </c>
       <c r="K87" t="n">
-        <v>21.6</v>
+        <v>22.4</v>
       </c>
       <c r="L87" t="n">
-        <v>32.6</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="88">
@@ -4122,28 +4122,28 @@
         <v>220</v>
       </c>
       <c r="E88" t="n">
-        <v>1.74</v>
+        <v>3.06</v>
       </c>
       <c r="F88" t="n">
         <v>0.112</v>
       </c>
       <c r="G88" t="n">
-        <v>47.5</v>
+        <v>48.2</v>
       </c>
       <c r="H88" t="n">
-        <v>24.8</v>
+        <v>28.3</v>
       </c>
       <c r="I88" t="n">
-        <v>221.8</v>
+        <v>228.7</v>
       </c>
       <c r="J88" t="n">
-        <v>51.1</v>
+        <v>53.5</v>
       </c>
       <c r="K88" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="L88" t="n">
-        <v>31.9</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="89">
@@ -4164,28 +4164,28 @@
         <v>219</v>
       </c>
       <c r="E89" t="n">
-        <v>1.9</v>
+        <v>3.21</v>
       </c>
       <c r="F89" t="n">
         <v>0.1131</v>
       </c>
       <c r="G89" t="n">
-        <v>47.5</v>
+        <v>48.1</v>
       </c>
       <c r="H89" t="n">
-        <v>25.5</v>
+        <v>28</v>
       </c>
       <c r="I89" t="n">
-        <v>222.3</v>
+        <v>228.6</v>
       </c>
       <c r="J89" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K89" t="n">
-        <v>21.6</v>
+        <v>22.1</v>
       </c>
       <c r="L89" t="n">
-        <v>33.9</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="90">
@@ -4206,28 +4206,28 @@
         <v>218</v>
       </c>
       <c r="E90" t="n">
-        <v>1.79</v>
+        <v>3.3</v>
       </c>
       <c r="F90" t="n">
         <v>0.1143</v>
       </c>
       <c r="G90" t="n">
-        <v>47.5</v>
+        <v>48.1</v>
       </c>
       <c r="H90" t="n">
-        <v>26.3</v>
+        <v>28</v>
       </c>
       <c r="I90" t="n">
-        <v>221.7</v>
+        <v>229.2</v>
       </c>
       <c r="J90" t="n">
-        <v>50.4</v>
+        <v>52.7</v>
       </c>
       <c r="K90" t="n">
-        <v>21.5</v>
+        <v>22.1</v>
       </c>
       <c r="L90" t="n">
-        <v>34.6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="91">
@@ -4248,70 +4248,154 @@
         <v>217</v>
       </c>
       <c r="E91" t="n">
-        <v>1.93</v>
+        <v>3.13</v>
       </c>
       <c r="F91" t="n">
         <v>0.1154</v>
       </c>
       <c r="G91" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
       <c r="H91" t="n">
-        <v>15.2</v>
+        <v>29.5</v>
       </c>
       <c r="I91" t="n">
-        <v>222.6</v>
+        <v>229.3</v>
       </c>
       <c r="J91" t="n">
-        <v>52</v>
+        <v>54.1</v>
       </c>
       <c r="K91" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="L91" t="n">
-        <v>26.5</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D92" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E92" t="n">
-        <v>1.93</v>
+        <v>3.18</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1154</v>
+        <v>0.1166</v>
       </c>
       <c r="G92" t="n">
-        <v>47.4</v>
+        <v>48.3</v>
       </c>
       <c r="H92" t="n">
-        <v>15.2</v>
+        <v>30.6</v>
       </c>
       <c r="I92" t="n">
-        <v>222.6</v>
+        <v>229.5</v>
       </c>
       <c r="J92" t="n">
-        <v>52</v>
+        <v>54.4</v>
       </c>
       <c r="K92" t="n">
-        <v>21.6</v>
+        <v>22.2</v>
       </c>
       <c r="L92" t="n">
-        <v>26.5</v>
+        <v>35.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>215</v>
+      </c>
+      <c r="D93" t="n">
+        <v>215</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="G93" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I93" t="n">
+        <v>229.1</v>
+      </c>
+      <c r="J93" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K93" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L93" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>215</v>
+      </c>
+      <c r="D94" t="n">
+        <v>215</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.1177</v>
+      </c>
+      <c r="G94" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="H94" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="I94" t="n">
+        <v>229.1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K94" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L94" t="n">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -4325,7 +4409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R92"/>
+  <dimension ref="A1:R94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4459,25 +4543,25 @@
         <v>0.3543</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.1588</v>
+        <v>3.1895</v>
       </c>
       <c r="M2" t="n">
         <v>2.9252</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.101</v>
+        <v>3.0825</v>
       </c>
       <c r="O2" t="n">
-        <v>1.1233</v>
+        <v>3.0183</v>
       </c>
       <c r="P2" t="n">
-        <v>50.55</v>
+        <v>51.52</v>
       </c>
       <c r="Q2" t="n">
-        <v>49.45</v>
+        <v>48.48</v>
       </c>
       <c r="R2" t="n">
-        <v>1.09</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="3">
@@ -4519,25 +4603,25 @@
         <v>0.354</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.035</v>
+        <v>3.1895</v>
       </c>
       <c r="M3" t="n">
         <v>2.9252</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0259</v>
+        <v>3.0824</v>
       </c>
       <c r="O3" t="n">
-        <v>1.1689</v>
+        <v>3.0182</v>
       </c>
       <c r="P3" t="n">
-        <v>50.54</v>
+        <v>51.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>49.46</v>
+        <v>48.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="4">
@@ -4579,25 +4663,25 @@
         <v>0.3536</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.035</v>
+        <v>3.1895</v>
       </c>
       <c r="M4" t="n">
         <v>2.9252</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0244</v>
+        <v>3.0824</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1707</v>
+        <v>3.0181</v>
       </c>
       <c r="P4" t="n">
-        <v>50.58</v>
+        <v>51.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>49.42</v>
+        <v>48.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.15</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="5">
@@ -4639,25 +4723,25 @@
         <v>0.3532</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.035</v>
+        <v>3.1895</v>
       </c>
       <c r="M5" t="n">
         <v>2.9155</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0268</v>
+        <v>3.0784</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1564</v>
+        <v>3.002</v>
       </c>
       <c r="P5" t="n">
-        <v>50.53</v>
+        <v>51.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>49.47</v>
+        <v>48.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="6">
@@ -4699,25 +4783,25 @@
         <v>0.3529</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9299</v>
+        <v>3.1895</v>
       </c>
       <c r="M6" t="n">
         <v>2.9303</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0432</v>
+        <v>3.0843</v>
       </c>
       <c r="O6" t="n">
-        <v>1.2159</v>
+        <v>3.0225</v>
       </c>
       <c r="P6" t="n">
-        <v>50.57</v>
+        <v>51.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>49.43</v>
+        <v>48.46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="7">
@@ -4759,25 +4843,25 @@
         <v>0.3525</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.8459</v>
+        <v>3.1895</v>
       </c>
       <c r="M7" t="n">
         <v>2.9303</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0945</v>
+        <v>3.0842</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2473</v>
+        <v>3.0224</v>
       </c>
       <c r="P7" t="n">
-        <v>50.69</v>
+        <v>51.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>49.31</v>
+        <v>48.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4819,25 +4903,25 @@
         <v>0.3521</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.0048</v>
+        <v>3.1895</v>
       </c>
       <c r="M8" t="n">
         <v>2.9381</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0049</v>
+        <v>3.0873</v>
       </c>
       <c r="O8" t="n">
-        <v>1.195</v>
+        <v>3.0242</v>
       </c>
       <c r="P8" t="n">
-        <v>50.56</v>
+        <v>51.45</v>
       </c>
       <c r="Q8" t="n">
-        <v>49.44</v>
+        <v>48.55</v>
       </c>
       <c r="R8" t="n">
-        <v>1.13</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="9">
@@ -4879,25 +4963,25 @@
         <v>0.3518</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.0584</v>
+        <v>3.1895</v>
       </c>
       <c r="M9" t="n">
         <v>2.925</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0307</v>
+        <v>3.0819</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1696</v>
+        <v>3.0157</v>
       </c>
       <c r="P9" t="n">
-        <v>50.49</v>
+        <v>51.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>49.51</v>
+        <v>48.5</v>
       </c>
       <c r="R9" t="n">
-        <v>0.98</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -4939,25 +5023,25 @@
         <v>0.3514</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8839</v>
+        <v>3.1895</v>
       </c>
       <c r="M10" t="n">
         <v>2.9313</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0769</v>
+        <v>3.0843</v>
       </c>
       <c r="O10" t="n">
-        <v>1.2344</v>
+        <v>3.0171</v>
       </c>
       <c r="P10" t="n">
-        <v>50.57</v>
+        <v>51.41</v>
       </c>
       <c r="Q10" t="n">
-        <v>49.43</v>
+        <v>48.59</v>
       </c>
       <c r="R10" t="n">
-        <v>1.14</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="11">
@@ -4999,25 +5083,25 @@
         <v>0.351</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.8839</v>
+        <v>3.1895</v>
       </c>
       <c r="M11" t="n">
         <v>2.9313</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0785</v>
+        <v>3.0843</v>
       </c>
       <c r="O11" t="n">
-        <v>1.2362</v>
+        <v>3.017</v>
       </c>
       <c r="P11" t="n">
-        <v>50.64</v>
+        <v>51.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>49.36</v>
+        <v>48.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.28</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="12">
@@ -5059,25 +5143,25 @@
         <v>0.3506</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8839</v>
+        <v>3.1895</v>
       </c>
       <c r="M12" t="n">
         <v>2.9549</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0897</v>
+        <v>3.0938</v>
       </c>
       <c r="O12" t="n">
-        <v>1.2348</v>
+        <v>3.0136</v>
       </c>
       <c r="P12" t="n">
-        <v>50.6</v>
+        <v>51.54</v>
       </c>
       <c r="Q12" t="n">
-        <v>49.4</v>
+        <v>48.46</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="13">
@@ -5119,25 +5203,25 @@
         <v>0.3502</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.8837</v>
+        <v>3.1895</v>
       </c>
       <c r="M13" t="n">
         <v>3.0158</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1163</v>
+        <v>3.1186</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2792</v>
+        <v>3.056</v>
       </c>
       <c r="P13" t="n">
-        <v>50.71</v>
+        <v>51.49</v>
       </c>
       <c r="Q13" t="n">
-        <v>49.29</v>
+        <v>48.51</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="14">
@@ -5179,25 +5263,25 @@
         <v>0.3498</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.7469</v>
+        <v>3.1895</v>
       </c>
       <c r="M14" t="n">
         <v>3.0412</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2091</v>
+        <v>3.1289</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3359</v>
+        <v>3.0629</v>
       </c>
       <c r="P14" t="n">
-        <v>50.75</v>
+        <v>51.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>49.25</v>
+        <v>48.35</v>
       </c>
       <c r="R14" t="n">
-        <v>1.51</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="15">
@@ -5239,25 +5323,25 @@
         <v>0.3494</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.8168</v>
+        <v>3.1895</v>
       </c>
       <c r="M15" t="n">
         <v>3.0176</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1598</v>
+        <v>3.1192</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3109</v>
+        <v>3.0603</v>
       </c>
       <c r="P15" t="n">
-        <v>50.68</v>
+        <v>51.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>49.32</v>
+        <v>48.44</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="16">
@@ -5299,25 +5383,25 @@
         <v>0.349</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.8024</v>
+        <v>1.8024</v>
       </c>
       <c r="M16" t="n">
         <v>3.02</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1709</v>
+        <v>2.3006</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3221</v>
+        <v>2.5803</v>
       </c>
       <c r="P16" t="n">
-        <v>50.65</v>
+        <v>51.31</v>
       </c>
       <c r="Q16" t="n">
-        <v>49.35</v>
+        <v>48.69</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="17">
@@ -5359,25 +5443,25 @@
         <v>0.3486</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.99</v>
+        <v>1.8024</v>
       </c>
       <c r="M17" t="n">
         <v>3.0257</v>
       </c>
       <c r="N17" t="n">
-        <v>0.06419999999999999</v>
+        <v>2.3034</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>2.5822</v>
       </c>
       <c r="P17" t="n">
-        <v>50.74</v>
+        <v>51.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>49.26</v>
+        <v>48.74</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="18">
@@ -5419,25 +5503,25 @@
         <v>0.3482</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.99</v>
+        <v>1.8024</v>
       </c>
       <c r="M18" t="n">
         <v>3.0391</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07140000000000001</v>
+        <v>2.3093</v>
       </c>
       <c r="O18" t="n">
-        <v>1.2738</v>
+        <v>2.5945</v>
       </c>
       <c r="P18" t="n">
-        <v>50.66</v>
+        <v>51.24</v>
       </c>
       <c r="Q18" t="n">
-        <v>49.34</v>
+        <v>48.76</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="19">
@@ -5479,25 +5563,25 @@
         <v>0.3478</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.99</v>
+        <v>1.8024</v>
       </c>
       <c r="M19" t="n">
         <v>3.0355</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0717</v>
+        <v>2.3083</v>
       </c>
       <c r="O19" t="n">
-        <v>1.2593</v>
+        <v>2.5783</v>
       </c>
       <c r="P19" t="n">
-        <v>50.61</v>
+        <v>51.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>49.39</v>
+        <v>48.7</v>
       </c>
       <c r="R19" t="n">
-        <v>1.21</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="20">
@@ -5539,25 +5623,25 @@
         <v>0.3474</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.99</v>
+        <v>1.8024</v>
       </c>
       <c r="M20" t="n">
         <v>3.0598</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0834</v>
+        <v>2.3187</v>
       </c>
       <c r="O20" t="n">
-        <v>1.2864</v>
+        <v>2.6039</v>
       </c>
       <c r="P20" t="n">
-        <v>50.63</v>
+        <v>51.27</v>
       </c>
       <c r="Q20" t="n">
-        <v>49.37</v>
+        <v>48.73</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="21">
@@ -5599,25 +5683,25 @@
         <v>0.347</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.1734</v>
+        <v>1.8024</v>
       </c>
       <c r="M21" t="n">
         <v>3.1108</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0019</v>
+        <v>2.3401</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2727</v>
+        <v>2.6522</v>
       </c>
       <c r="P21" t="n">
-        <v>50.58</v>
+        <v>51.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>49.42</v>
+        <v>48.68</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="22">
@@ -5659,25 +5743,25 @@
         <v>0.3466</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1581</v>
+        <v>1.8024</v>
       </c>
       <c r="M22" t="n">
         <v>3.0941</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0022</v>
+        <v>2.3337</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2762</v>
+        <v>2.6487</v>
       </c>
       <c r="P22" t="n">
-        <v>50.57</v>
+        <v>51.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>49.43</v>
+        <v>48.7</v>
       </c>
       <c r="R22" t="n">
-        <v>1.13</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="23">
@@ -5719,25 +5803,25 @@
         <v>0.3461</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.1897</v>
+        <v>1.8024</v>
       </c>
       <c r="M23" t="n">
         <v>3.1078</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0089</v>
+        <v>2.3398</v>
       </c>
       <c r="O23" t="n">
-        <v>1.3023</v>
+        <v>2.6841</v>
       </c>
       <c r="P23" t="n">
-        <v>50.7</v>
+        <v>51.35</v>
       </c>
       <c r="Q23" t="n">
-        <v>49.3</v>
+        <v>48.65</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="24">
@@ -5779,25 +5863,25 @@
         <v>0.3457</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.2456</v>
+        <v>1.8024</v>
       </c>
       <c r="M24" t="n">
         <v>3.1078</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0398</v>
+        <v>2.3403</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2853</v>
+        <v>2.6847</v>
       </c>
       <c r="P24" t="n">
-        <v>50.61</v>
+        <v>51.33</v>
       </c>
       <c r="Q24" t="n">
-        <v>49.39</v>
+        <v>48.67</v>
       </c>
       <c r="R24" t="n">
-        <v>1.22</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="25">
@@ -5839,25 +5923,25 @@
         <v>0.3453</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.2456</v>
+        <v>1.8024</v>
       </c>
       <c r="M25" t="n">
         <v>3.1018</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0403</v>
+        <v>2.3383</v>
       </c>
       <c r="O25" t="n">
-        <v>1.2912</v>
+        <v>2.6889</v>
       </c>
       <c r="P25" t="n">
-        <v>50.71</v>
+        <v>51.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>49.29</v>
+        <v>48.64</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="26">
@@ -5899,25 +5983,25 @@
         <v>0.3448</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.2456</v>
+        <v>1.8024</v>
       </c>
       <c r="M26" t="n">
         <v>3.1023</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.0381</v>
+        <v>2.339</v>
       </c>
       <c r="O26" t="n">
-        <v>1.2774</v>
+        <v>2.6732</v>
       </c>
       <c r="P26" t="n">
-        <v>50.63</v>
+        <v>51.29</v>
       </c>
       <c r="Q26" t="n">
-        <v>49.37</v>
+        <v>48.71</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="27">
@@ -5959,25 +6043,25 @@
         <v>0.3444</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.2486</v>
+        <v>1.8024</v>
       </c>
       <c r="M27" t="n">
         <v>3.1987</v>
       </c>
       <c r="N27" t="n">
-        <v>0.002</v>
+        <v>2.3793</v>
       </c>
       <c r="O27" t="n">
-        <v>1.3245</v>
+        <v>2.7196</v>
       </c>
       <c r="P27" t="n">
-        <v>50.72</v>
+        <v>51.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>49.28</v>
+        <v>48.68</v>
       </c>
       <c r="R27" t="n">
-        <v>1.44</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="28">
@@ -6019,25 +6103,25 @@
         <v>0.3439</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.1816</v>
+        <v>1.8024</v>
       </c>
       <c r="M28" t="n">
         <v>3.2044</v>
       </c>
       <c r="N28" t="n">
-        <v>0.0457</v>
+        <v>2.3822</v>
       </c>
       <c r="O28" t="n">
-        <v>1.3502</v>
+        <v>2.7205</v>
       </c>
       <c r="P28" t="n">
-        <v>50.73</v>
+        <v>51.33</v>
       </c>
       <c r="Q28" t="n">
-        <v>49.27</v>
+        <v>48.67</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="29">
@@ -6079,25 +6163,25 @@
         <v>0.3435</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.0389</v>
+        <v>1.8024</v>
       </c>
       <c r="M29" t="n">
         <v>3.1846</v>
       </c>
       <c r="N29" t="n">
-        <v>0.1232</v>
+        <v>2.3745</v>
       </c>
       <c r="O29" t="n">
-        <v>1.4136</v>
+        <v>2.733</v>
       </c>
       <c r="P29" t="n">
-        <v>50.78</v>
+        <v>51.32</v>
       </c>
       <c r="Q29" t="n">
-        <v>49.22</v>
+        <v>48.68</v>
       </c>
       <c r="R29" t="n">
-        <v>1.56</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="30">
@@ -6139,25 +6223,25 @@
         <v>0.343</v>
       </c>
       <c r="L30" t="n">
-        <v>-2.1414</v>
+        <v>1.8024</v>
       </c>
       <c r="M30" t="n">
         <v>3.17</v>
       </c>
       <c r="N30" t="n">
-        <v>0.0592</v>
+        <v>2.369</v>
       </c>
       <c r="O30" t="n">
-        <v>1.3819</v>
+        <v>2.7348</v>
       </c>
       <c r="P30" t="n">
-        <v>50.73</v>
+        <v>51.39</v>
       </c>
       <c r="Q30" t="n">
-        <v>49.27</v>
+        <v>48.61</v>
       </c>
       <c r="R30" t="n">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="31">
@@ -6199,25 +6283,25 @@
         <v>0.3426</v>
       </c>
       <c r="L31" t="n">
-        <v>-2.1377</v>
+        <v>1.8024</v>
       </c>
       <c r="M31" t="n">
         <v>3.2028</v>
       </c>
       <c r="N31" t="n">
-        <v>0.077</v>
+        <v>2.3831</v>
       </c>
       <c r="O31" t="n">
-        <v>1.4019</v>
+        <v>2.7517</v>
       </c>
       <c r="P31" t="n">
-        <v>50.71</v>
+        <v>51.44</v>
       </c>
       <c r="Q31" t="n">
-        <v>49.29</v>
+        <v>48.56</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="32">
@@ -6259,25 +6343,25 @@
         <v>0.3421</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.1377</v>
+        <v>1.8024</v>
       </c>
       <c r="M32" t="n">
         <v>3.2021</v>
       </c>
       <c r="N32" t="n">
-        <v>0.0789</v>
+        <v>2.3834</v>
       </c>
       <c r="O32" t="n">
-        <v>1.4042</v>
+        <v>2.7522</v>
       </c>
       <c r="P32" t="n">
-        <v>50.69</v>
+        <v>51.39</v>
       </c>
       <c r="Q32" t="n">
-        <v>49.31</v>
+        <v>48.61</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="33">
@@ -6319,25 +6403,25 @@
         <v>0.3416</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.181</v>
+        <v>1.732</v>
       </c>
       <c r="M33" t="n">
         <v>3.1805</v>
       </c>
       <c r="N33" t="n">
-        <v>0.0467</v>
+        <v>2.3339</v>
       </c>
       <c r="O33" t="n">
-        <v>1.3874</v>
+        <v>2.7242</v>
       </c>
       <c r="P33" t="n">
-        <v>50.68</v>
+        <v>51.32</v>
       </c>
       <c r="Q33" t="n">
-        <v>49.32</v>
+        <v>48.68</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="34">
@@ -6379,25 +6463,25 @@
         <v>0.3412</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.1799</v>
+        <v>1.8024</v>
       </c>
       <c r="M34" t="n">
         <v>3.2117</v>
       </c>
       <c r="N34" t="n">
-        <v>0.0625</v>
+        <v>2.3886</v>
       </c>
       <c r="O34" t="n">
-        <v>1.3985</v>
+        <v>2.7572</v>
       </c>
       <c r="P34" t="n">
-        <v>50.77</v>
+        <v>51.33</v>
       </c>
       <c r="Q34" t="n">
-        <v>49.23</v>
+        <v>48.67</v>
       </c>
       <c r="R34" t="n">
-        <v>1.53</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="35">
@@ -6439,25 +6523,25 @@
         <v>0.3407</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.2128</v>
+        <v>1.8024</v>
       </c>
       <c r="M35" t="n">
         <v>3.2117</v>
       </c>
       <c r="N35" t="n">
-        <v>0.0455</v>
+        <v>2.3891</v>
       </c>
       <c r="O35" t="n">
-        <v>1.39</v>
+        <v>2.7579</v>
       </c>
       <c r="P35" t="n">
-        <v>50.66</v>
+        <v>51.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>49.34</v>
+        <v>48.62</v>
       </c>
       <c r="R35" t="n">
-        <v>1.33</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="36">
@@ -6499,25 +6583,25 @@
         <v>0.3402</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.188</v>
+        <v>1.4776</v>
       </c>
       <c r="M36" t="n">
         <v>3.1999</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0573</v>
+        <v>2.1953</v>
       </c>
       <c r="O36" t="n">
-        <v>1.3987</v>
+        <v>2.6457</v>
       </c>
       <c r="P36" t="n">
-        <v>50.67</v>
+        <v>51.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>49.33</v>
+        <v>48.69</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="37">
@@ -6559,25 +6643,25 @@
         <v>0.3397</v>
       </c>
       <c r="L37" t="n">
-        <v>-2.3762</v>
+        <v>1.4776</v>
       </c>
       <c r="M37" t="n">
         <v>3.1983</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.0508</v>
+        <v>2.1954</v>
       </c>
       <c r="O37" t="n">
-        <v>1.3427</v>
+        <v>2.6519</v>
       </c>
       <c r="P37" t="n">
-        <v>50.62</v>
+        <v>51.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>49.38</v>
+        <v>48.69</v>
       </c>
       <c r="R37" t="n">
-        <v>1.24</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="38">
@@ -6619,25 +6703,25 @@
         <v>0.3392</v>
       </c>
       <c r="L38" t="n">
-        <v>-2.2261</v>
+        <v>1.4776</v>
       </c>
       <c r="M38" t="n">
         <v>3.2094</v>
       </c>
       <c r="N38" t="n">
-        <v>0.0436</v>
+        <v>2.2008</v>
       </c>
       <c r="O38" t="n">
-        <v>1.3991</v>
+        <v>2.6555</v>
       </c>
       <c r="P38" t="n">
-        <v>50.65</v>
+        <v>51.23</v>
       </c>
       <c r="Q38" t="n">
-        <v>49.35</v>
+        <v>48.77</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="39">
@@ -6679,25 +6763,25 @@
         <v>0.3387</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.2261</v>
+        <v>1.4776</v>
       </c>
       <c r="M39" t="n">
         <v>3.2094</v>
       </c>
       <c r="N39" t="n">
-        <v>0.0459</v>
+        <v>2.2015</v>
       </c>
       <c r="O39" t="n">
-        <v>1.4019</v>
+        <v>2.6564</v>
       </c>
       <c r="P39" t="n">
-        <v>50.71</v>
+        <v>51.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>49.29</v>
+        <v>48.69</v>
       </c>
       <c r="R39" t="n">
-        <v>1.43</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="40">
@@ -6739,25 +6823,25 @@
         <v>0.3382</v>
       </c>
       <c r="L40" t="n">
-        <v>-2.2261</v>
+        <v>1.732</v>
       </c>
       <c r="M40" t="n">
         <v>3.2225</v>
       </c>
       <c r="N40" t="n">
-        <v>0.0538</v>
+        <v>2.3557</v>
       </c>
       <c r="O40" t="n">
-        <v>1.4016</v>
+        <v>2.7403</v>
       </c>
       <c r="P40" t="n">
-        <v>50.67</v>
+        <v>51.38</v>
       </c>
       <c r="Q40" t="n">
-        <v>49.33</v>
+        <v>48.62</v>
       </c>
       <c r="R40" t="n">
-        <v>1.35</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="41">
@@ -6799,25 +6883,25 @@
         <v>0.3377</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.216</v>
+        <v>1.4776</v>
       </c>
       <c r="M41" t="n">
         <v>3.2414</v>
       </c>
       <c r="N41" t="n">
-        <v>0.0699</v>
+        <v>2.2164</v>
       </c>
       <c r="O41" t="n">
-        <v>1.4314</v>
+        <v>2.6788</v>
       </c>
       <c r="P41" t="n">
-        <v>50.6</v>
+        <v>51.19</v>
       </c>
       <c r="Q41" t="n">
-        <v>49.4</v>
+        <v>48.81</v>
       </c>
       <c r="R41" t="n">
-        <v>1.19</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="42">
@@ -6859,25 +6943,25 @@
         <v>0.3372</v>
       </c>
       <c r="L42" t="n">
-        <v>-2.1556</v>
+        <v>1.4776</v>
       </c>
       <c r="M42" t="n">
         <v>3.2952</v>
       </c>
       <c r="N42" t="n">
-        <v>0.1299</v>
+        <v>2.2397</v>
       </c>
       <c r="O42" t="n">
-        <v>1.4974</v>
+        <v>2.7226</v>
       </c>
       <c r="P42" t="n">
-        <v>50.72</v>
+        <v>51.37</v>
       </c>
       <c r="Q42" t="n">
-        <v>49.28</v>
+        <v>48.63</v>
       </c>
       <c r="R42" t="n">
-        <v>1.45</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="43">
@@ -6919,25 +7003,25 @@
         <v>0.3367</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.2212</v>
+        <v>1.732</v>
       </c>
       <c r="M43" t="n">
         <v>3.2952</v>
       </c>
       <c r="N43" t="n">
-        <v>0.09429999999999999</v>
+        <v>2.3882</v>
       </c>
       <c r="O43" t="n">
-        <v>1.4782</v>
+        <v>2.8093</v>
       </c>
       <c r="P43" t="n">
-        <v>50.78</v>
+        <v>51.29</v>
       </c>
       <c r="Q43" t="n">
-        <v>49.22</v>
+        <v>48.71</v>
       </c>
       <c r="R43" t="n">
-        <v>1.56</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="44">
@@ -6979,25 +7063,25 @@
         <v>0.3362</v>
       </c>
       <c r="L44" t="n">
-        <v>-2.3763</v>
+        <v>1.4776</v>
       </c>
       <c r="M44" t="n">
         <v>3.2916</v>
       </c>
       <c r="N44" t="n">
-        <v>0.0053</v>
+        <v>2.2398</v>
       </c>
       <c r="O44" t="n">
-        <v>1.4192</v>
+        <v>2.7148</v>
       </c>
       <c r="P44" t="n">
-        <v>50.69</v>
+        <v>51.34</v>
       </c>
       <c r="Q44" t="n">
-        <v>49.31</v>
+        <v>48.66</v>
       </c>
       <c r="R44" t="n">
-        <v>1.38</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="45">
@@ -7039,25 +7123,25 @@
         <v>0.3357</v>
       </c>
       <c r="L45" t="n">
-        <v>-2.3455</v>
+        <v>1.732</v>
       </c>
       <c r="M45" t="n">
         <v>3.2972</v>
       </c>
       <c r="N45" t="n">
-        <v>0.0281</v>
+        <v>2.3904</v>
       </c>
       <c r="O45" t="n">
-        <v>1.4339</v>
+        <v>2.8026</v>
       </c>
       <c r="P45" t="n">
-        <v>50.72</v>
+        <v>51.51</v>
       </c>
       <c r="Q45" t="n">
-        <v>49.28</v>
+        <v>48.49</v>
       </c>
       <c r="R45" t="n">
-        <v>1.44</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="46">
@@ -7099,25 +7183,25 @@
         <v>0.3351</v>
       </c>
       <c r="L46" t="n">
-        <v>-2.3455</v>
+        <v>1.732</v>
       </c>
       <c r="M46" t="n">
         <v>3.2972</v>
       </c>
       <c r="N46" t="n">
-        <v>0.0306</v>
+        <v>2.3911</v>
       </c>
       <c r="O46" t="n">
-        <v>1.4369</v>
+        <v>2.8034</v>
       </c>
       <c r="P46" t="n">
-        <v>50.75</v>
+        <v>51.3</v>
       </c>
       <c r="Q46" t="n">
-        <v>49.25</v>
+        <v>48.7</v>
       </c>
       <c r="R46" t="n">
-        <v>1.5</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="47">
@@ -7159,25 +7243,25 @@
         <v>0.3346</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.3455</v>
+        <v>1.732</v>
       </c>
       <c r="M47" t="n">
         <v>3.2972</v>
       </c>
       <c r="N47" t="n">
-        <v>0.0332</v>
+        <v>2.3919</v>
       </c>
       <c r="O47" t="n">
-        <v>1.4391</v>
+        <v>2.8034</v>
       </c>
       <c r="P47" t="n">
-        <v>50.75</v>
+        <v>51.48</v>
       </c>
       <c r="Q47" t="n">
-        <v>49.25</v>
+        <v>48.52</v>
       </c>
       <c r="R47" t="n">
-        <v>1.51</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="48">
@@ -7219,25 +7303,25 @@
         <v>0.3341</v>
       </c>
       <c r="L48" t="n">
-        <v>-2.3455</v>
+        <v>1.732</v>
       </c>
       <c r="M48" t="n">
         <v>3.3141</v>
       </c>
       <c r="N48" t="n">
-        <v>0.043</v>
+        <v>2.3997</v>
       </c>
       <c r="O48" t="n">
-        <v>1.456</v>
+        <v>2.8181</v>
       </c>
       <c r="P48" t="n">
-        <v>50.75</v>
+        <v>51.36</v>
       </c>
       <c r="Q48" t="n">
-        <v>49.25</v>
+        <v>48.64</v>
       </c>
       <c r="R48" t="n">
-        <v>1.51</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="49">
@@ -7279,25 +7363,25 @@
         <v>0.3335</v>
       </c>
       <c r="L49" t="n">
-        <v>-2.4345</v>
+        <v>1.732</v>
       </c>
       <c r="M49" t="n">
         <v>3.3317</v>
       </c>
       <c r="N49" t="n">
-        <v>0.0017</v>
+        <v>2.4079</v>
       </c>
       <c r="O49" t="n">
-        <v>1.4294</v>
+        <v>2.819</v>
       </c>
       <c r="P49" t="n">
-        <v>50.62</v>
+        <v>51.34</v>
       </c>
       <c r="Q49" t="n">
-        <v>49.38</v>
+        <v>48.66</v>
       </c>
       <c r="R49" t="n">
-        <v>1.25</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="50">
@@ -7339,25 +7423,25 @@
         <v>0.333</v>
       </c>
       <c r="L50" t="n">
-        <v>-2.381</v>
+        <v>1.732</v>
       </c>
       <c r="M50" t="n">
         <v>3.3215</v>
       </c>
       <c r="N50" t="n">
-        <v>0.031</v>
+        <v>2.4043</v>
       </c>
       <c r="O50" t="n">
-        <v>1.5027</v>
+        <v>2.8722</v>
       </c>
       <c r="P50" t="n">
-        <v>50.77</v>
+        <v>51.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>49.23</v>
+        <v>48.6</v>
       </c>
       <c r="R50" t="n">
-        <v>1.53</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="51">
@@ -7399,25 +7483,25 @@
         <v>0.3324</v>
       </c>
       <c r="L51" t="n">
-        <v>-2.4312</v>
+        <v>1.732</v>
       </c>
       <c r="M51" t="n">
         <v>3.3136</v>
       </c>
       <c r="N51" t="n">
-        <v>0.0015</v>
+        <v>2.4018</v>
       </c>
       <c r="O51" t="n">
-        <v>1.4899</v>
+        <v>2.8738</v>
       </c>
       <c r="P51" t="n">
-        <v>50.74</v>
+        <v>51.31</v>
       </c>
       <c r="Q51" t="n">
-        <v>49.26</v>
+        <v>48.69</v>
       </c>
       <c r="R51" t="n">
-        <v>1.47</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="52">
@@ -7459,25 +7543,25 @@
         <v>0.3319</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.388</v>
+        <v>1.732</v>
       </c>
       <c r="M52" t="n">
         <v>3.3752</v>
       </c>
       <c r="N52" t="n">
-        <v>0.0552</v>
+        <v>2.4286</v>
       </c>
       <c r="O52" t="n">
-        <v>1.5523</v>
+        <v>2.9195</v>
       </c>
       <c r="P52" t="n">
-        <v>50.85</v>
+        <v>51.43</v>
       </c>
       <c r="Q52" t="n">
-        <v>49.15</v>
+        <v>48.57</v>
       </c>
       <c r="R52" t="n">
-        <v>1.69</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="53">
@@ -7519,25 +7603,25 @@
         <v>0.3313</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.388</v>
+        <v>1.732</v>
       </c>
       <c r="M53" t="n">
         <v>3.3752</v>
       </c>
       <c r="N53" t="n">
-        <v>0.058</v>
+        <v>2.4294</v>
       </c>
       <c r="O53" t="n">
-        <v>1.5556</v>
+        <v>2.9205</v>
       </c>
       <c r="P53" t="n">
-        <v>50.74</v>
+        <v>51.44</v>
       </c>
       <c r="Q53" t="n">
-        <v>49.26</v>
+        <v>48.56</v>
       </c>
       <c r="R53" t="n">
-        <v>1.47</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="54">
@@ -7579,25 +7663,25 @@
         <v>0.3307</v>
       </c>
       <c r="L54" t="n">
-        <v>-2.388</v>
+        <v>1.732</v>
       </c>
       <c r="M54" t="n">
         <v>3.3738</v>
       </c>
       <c r="N54" t="n">
-        <v>0.0603</v>
+        <v>2.4296</v>
       </c>
       <c r="O54" t="n">
-        <v>1.5743</v>
+        <v>2.9369</v>
       </c>
       <c r="P54" t="n">
-        <v>50.72</v>
+        <v>51.48</v>
       </c>
       <c r="Q54" t="n">
-        <v>49.28</v>
+        <v>48.52</v>
       </c>
       <c r="R54" t="n">
-        <v>1.44</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="55">
@@ -7639,25 +7723,25 @@
         <v>0.3301</v>
       </c>
       <c r="L55" t="n">
-        <v>-2.4459</v>
+        <v>1.732</v>
       </c>
       <c r="M55" t="n">
         <v>3.4004</v>
       </c>
       <c r="N55" t="n">
-        <v>0.0412</v>
+        <v>2.4418</v>
       </c>
       <c r="O55" t="n">
-        <v>1.5679</v>
+        <v>2.9472</v>
       </c>
       <c r="P55" t="n">
-        <v>50.79</v>
+        <v>51.49</v>
       </c>
       <c r="Q55" t="n">
-        <v>49.21</v>
+        <v>48.51</v>
       </c>
       <c r="R55" t="n">
-        <v>1.59</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="56">
@@ -7699,25 +7783,25 @@
         <v>0.3296</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.2077</v>
+        <v>1.732</v>
       </c>
       <c r="M56" t="n">
         <v>3.4004</v>
       </c>
       <c r="N56" t="n">
-        <v>0.1809</v>
+        <v>2.4426</v>
       </c>
       <c r="O56" t="n">
-        <v>1.6499</v>
+        <v>2.9483</v>
       </c>
       <c r="P56" t="n">
-        <v>50.69</v>
+        <v>51.47</v>
       </c>
       <c r="Q56" t="n">
-        <v>49.31</v>
+        <v>48.53</v>
       </c>
       <c r="R56" t="n">
-        <v>1.38</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="57">
@@ -7759,25 +7843,25 @@
         <v>0.329</v>
       </c>
       <c r="L57" t="n">
-        <v>-2.0797</v>
+        <v>1.732</v>
       </c>
       <c r="M57" t="n">
         <v>3.3857</v>
       </c>
       <c r="N57" t="n">
-        <v>0.2509</v>
+        <v>2.4372</v>
       </c>
       <c r="O57" t="n">
-        <v>1.6918</v>
+        <v>2.9458</v>
       </c>
       <c r="P57" t="n">
-        <v>50.86</v>
+        <v>51.48</v>
       </c>
       <c r="Q57" t="n">
-        <v>49.14</v>
+        <v>48.52</v>
       </c>
       <c r="R57" t="n">
-        <v>1.72</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="58">
@@ -7819,25 +7903,25 @@
         <v>0.3284</v>
       </c>
       <c r="L58" t="n">
-        <v>-2.0865</v>
+        <v>1.732</v>
       </c>
       <c r="M58" t="n">
         <v>3.3337</v>
       </c>
       <c r="N58" t="n">
-        <v>0.2276</v>
+        <v>2.4159</v>
       </c>
       <c r="O58" t="n">
-        <v>1.6632</v>
+        <v>2.9172</v>
       </c>
       <c r="P58" t="n">
-        <v>50.95</v>
+        <v>51.42</v>
       </c>
       <c r="Q58" t="n">
-        <v>49.05</v>
+        <v>48.58</v>
       </c>
       <c r="R58" t="n">
-        <v>1.91</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="59">
@@ -7879,25 +7963,25 @@
         <v>0.3278</v>
       </c>
       <c r="L59" t="n">
-        <v>-2.1305</v>
+        <v>1.732</v>
       </c>
       <c r="M59" t="n">
         <v>3.3413</v>
       </c>
       <c r="N59" t="n">
-        <v>0.2085</v>
+        <v>2.4199</v>
       </c>
       <c r="O59" t="n">
-        <v>1.6504</v>
+        <v>2.9166</v>
       </c>
       <c r="P59" t="n">
-        <v>50.86</v>
+        <v>51.46</v>
       </c>
       <c r="Q59" t="n">
-        <v>49.14</v>
+        <v>48.54</v>
       </c>
       <c r="R59" t="n">
-        <v>1.72</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="60">
@@ -7939,25 +8023,25 @@
         <v>0.3272</v>
       </c>
       <c r="L60" t="n">
-        <v>-2.1305</v>
+        <v>1.732</v>
       </c>
       <c r="M60" t="n">
         <v>3.3568</v>
       </c>
       <c r="N60" t="n">
-        <v>0.218</v>
+        <v>2.4274</v>
       </c>
       <c r="O60" t="n">
-        <v>1.673</v>
+        <v>2.9368</v>
       </c>
       <c r="P60" t="n">
-        <v>50.88</v>
+        <v>51.48</v>
       </c>
       <c r="Q60" t="n">
-        <v>49.12</v>
+        <v>48.52</v>
       </c>
       <c r="R60" t="n">
-        <v>1.75</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="61">
@@ -7999,25 +8083,25 @@
         <v>0.3266</v>
       </c>
       <c r="L61" t="n">
-        <v>-2.1305</v>
+        <v>1.732</v>
       </c>
       <c r="M61" t="n">
         <v>3.3574</v>
       </c>
       <c r="N61" t="n">
-        <v>0.2212</v>
+        <v>2.4285</v>
       </c>
       <c r="O61" t="n">
-        <v>1.6752</v>
+        <v>2.9367</v>
       </c>
       <c r="P61" t="n">
-        <v>50.8</v>
+        <v>51.51</v>
       </c>
       <c r="Q61" t="n">
-        <v>49.2</v>
+        <v>48.49</v>
       </c>
       <c r="R61" t="n">
-        <v>1.6</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="62">
@@ -8059,25 +8143,25 @@
         <v>0.326</v>
       </c>
       <c r="L62" t="n">
-        <v>-1.9687</v>
+        <v>1.732</v>
       </c>
       <c r="M62" t="n">
         <v>3.3693</v>
       </c>
       <c r="N62" t="n">
-        <v>0.3216</v>
+        <v>2.4345</v>
       </c>
       <c r="O62" t="n">
-        <v>1.7399</v>
+        <v>2.9463</v>
       </c>
       <c r="P62" t="n">
-        <v>50.95</v>
+        <v>51.51</v>
       </c>
       <c r="Q62" t="n">
-        <v>49.05</v>
+        <v>48.49</v>
       </c>
       <c r="R62" t="n">
-        <v>1.89</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="63">
@@ -8119,25 +8203,25 @@
         <v>0.3254</v>
       </c>
       <c r="L63" t="n">
-        <v>-2.2166</v>
+        <v>1.732</v>
       </c>
       <c r="M63" t="n">
         <v>3.3579</v>
       </c>
       <c r="N63" t="n">
-        <v>0.1782</v>
+        <v>2.4305</v>
       </c>
       <c r="O63" t="n">
-        <v>1.6707</v>
+        <v>2.9554</v>
       </c>
       <c r="P63" t="n">
-        <v>50.77</v>
+        <v>51.48</v>
       </c>
       <c r="Q63" t="n">
-        <v>49.23</v>
+        <v>48.52</v>
       </c>
       <c r="R63" t="n">
-        <v>1.54</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="64">
@@ -8179,25 +8263,25 @@
         <v>0.3247</v>
       </c>
       <c r="L64" t="n">
-        <v>-1.9661</v>
+        <v>1.732</v>
       </c>
       <c r="M64" t="n">
         <v>3.3728</v>
       </c>
       <c r="N64" t="n">
-        <v>0.3303</v>
+        <v>2.4378</v>
       </c>
       <c r="O64" t="n">
-        <v>1.7644</v>
+        <v>2.9653</v>
       </c>
       <c r="P64" t="n">
-        <v>50.94</v>
+        <v>51.45</v>
       </c>
       <c r="Q64" t="n">
-        <v>49.06</v>
+        <v>48.55</v>
       </c>
       <c r="R64" t="n">
-        <v>1.89</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="65">
@@ -8239,25 +8323,25 @@
         <v>0.3241</v>
       </c>
       <c r="L65" t="n">
-        <v>-1.8997</v>
+        <v>1.732</v>
       </c>
       <c r="M65" t="n">
         <v>3.3744</v>
       </c>
       <c r="N65" t="n">
-        <v>0.3718</v>
+        <v>2.4394</v>
       </c>
       <c r="O65" t="n">
-        <v>1.7786</v>
+        <v>2.9557</v>
       </c>
       <c r="P65" t="n">
-        <v>50.87</v>
+        <v>51.43</v>
       </c>
       <c r="Q65" t="n">
-        <v>49.13</v>
+        <v>48.57</v>
       </c>
       <c r="R65" t="n">
-        <v>1.74</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="66">
@@ -8299,25 +8383,25 @@
         <v>0.3235</v>
       </c>
       <c r="L66" t="n">
-        <v>-2.1419</v>
+        <v>1.732</v>
       </c>
       <c r="M66" t="n">
         <v>3.3744</v>
       </c>
       <c r="N66" t="n">
-        <v>0.237</v>
+        <v>2.4403</v>
       </c>
       <c r="O66" t="n">
-        <v>1.7038</v>
+        <v>2.9569</v>
       </c>
       <c r="P66" t="n">
-        <v>50.81</v>
+        <v>51.53</v>
       </c>
       <c r="Q66" t="n">
-        <v>49.19</v>
+        <v>48.47</v>
       </c>
       <c r="R66" t="n">
-        <v>1.62</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="67">
@@ -8359,25 +8443,25 @@
         <v>0.3228</v>
       </c>
       <c r="L67" t="n">
-        <v>-2.1419</v>
+        <v>1.732</v>
       </c>
       <c r="M67" t="n">
         <v>3.375</v>
       </c>
       <c r="N67" t="n">
-        <v>0.2403</v>
+        <v>2.4415</v>
       </c>
       <c r="O67" t="n">
-        <v>1.7085</v>
+        <v>2.9591</v>
       </c>
       <c r="P67" t="n">
-        <v>50.85</v>
+        <v>51.44</v>
       </c>
       <c r="Q67" t="n">
-        <v>49.15</v>
+        <v>48.56</v>
       </c>
       <c r="R67" t="n">
-        <v>1.7</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="68">
@@ -8419,25 +8503,25 @@
         <v>0.3222</v>
       </c>
       <c r="L68" t="n">
-        <v>-2.1419</v>
+        <v>1.732</v>
       </c>
       <c r="M68" t="n">
         <v>3.3929</v>
       </c>
       <c r="N68" t="n">
-        <v>0.2512</v>
+        <v>2.4502</v>
       </c>
       <c r="O68" t="n">
-        <v>1.7156</v>
+        <v>2.9637</v>
       </c>
       <c r="P68" t="n">
-        <v>50.83</v>
+        <v>51.59</v>
       </c>
       <c r="Q68" t="n">
-        <v>49.17</v>
+        <v>48.41</v>
       </c>
       <c r="R68" t="n">
-        <v>1.66</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="69">
@@ -8479,25 +8563,25 @@
         <v>0.3215</v>
       </c>
       <c r="L69" t="n">
-        <v>-1.8818</v>
+        <v>1.732</v>
       </c>
       <c r="M69" t="n">
         <v>3.3979</v>
       </c>
       <c r="N69" t="n">
-        <v>0.4041</v>
+        <v>2.4533</v>
       </c>
       <c r="O69" t="n">
-        <v>1.8038</v>
+        <v>2.9658</v>
       </c>
       <c r="P69" t="n">
-        <v>50.95</v>
+        <v>51.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>49.05</v>
+        <v>48.5</v>
       </c>
       <c r="R69" t="n">
-        <v>1.89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70">
@@ -8539,25 +8623,25 @@
         <v>0.3209</v>
       </c>
       <c r="L70" t="n">
-        <v>-1.9582</v>
+        <v>1.732</v>
       </c>
       <c r="M70" t="n">
         <v>3.4198</v>
       </c>
       <c r="N70" t="n">
-        <v>0.3733</v>
+        <v>2.4637</v>
       </c>
       <c r="O70" t="n">
-        <v>1.7975</v>
+        <v>2.9817</v>
       </c>
       <c r="P70" t="n">
-        <v>50.82</v>
+        <v>51.42</v>
       </c>
       <c r="Q70" t="n">
-        <v>49.18</v>
+        <v>48.58</v>
       </c>
       <c r="R70" t="n">
-        <v>1.63</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="71">
@@ -8599,25 +8683,25 @@
         <v>0.3202</v>
       </c>
       <c r="L71" t="n">
-        <v>-1.6906</v>
+        <v>1.732</v>
       </c>
       <c r="M71" t="n">
         <v>3.4198</v>
       </c>
       <c r="N71" t="n">
-        <v>0.5279</v>
+        <v>2.4647</v>
       </c>
       <c r="O71" t="n">
-        <v>1.8869</v>
+        <v>2.9829</v>
       </c>
       <c r="P71" t="n">
-        <v>50.86</v>
+        <v>51.51</v>
       </c>
       <c r="Q71" t="n">
-        <v>49.14</v>
+        <v>48.49</v>
       </c>
       <c r="R71" t="n">
-        <v>1.73</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="72">
@@ -8659,25 +8743,25 @@
         <v>0.3196</v>
       </c>
       <c r="L72" t="n">
-        <v>-1.7696</v>
+        <v>1.732</v>
       </c>
       <c r="M72" t="n">
         <v>3.4114</v>
       </c>
       <c r="N72" t="n">
-        <v>0.4826</v>
+        <v>2.4621</v>
       </c>
       <c r="O72" t="n">
-        <v>1.8632</v>
+        <v>2.9821</v>
       </c>
       <c r="P72" t="n">
-        <v>50.88</v>
+        <v>51.53</v>
       </c>
       <c r="Q72" t="n">
-        <v>49.12</v>
+        <v>48.47</v>
       </c>
       <c r="R72" t="n">
-        <v>1.76</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="73">
@@ -8719,25 +8803,25 @@
         <v>0.3189</v>
       </c>
       <c r="L73" t="n">
-        <v>-1.8802</v>
+        <v>1.732</v>
       </c>
       <c r="M73" t="n">
         <v>3.4114</v>
       </c>
       <c r="N73" t="n">
-        <v>0.4233</v>
+        <v>2.4631</v>
       </c>
       <c r="O73" t="n">
-        <v>1.8316</v>
+        <v>2.9834</v>
       </c>
       <c r="P73" t="n">
-        <v>50.96</v>
+        <v>51.36</v>
       </c>
       <c r="Q73" t="n">
-        <v>49.04</v>
+        <v>48.64</v>
       </c>
       <c r="R73" t="n">
-        <v>1.93</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="74">
@@ -8779,25 +8863,25 @@
         <v>0.3182</v>
       </c>
       <c r="L74" t="n">
-        <v>-1.8802</v>
+        <v>1.732</v>
       </c>
       <c r="M74" t="n">
         <v>3.4114</v>
       </c>
       <c r="N74" t="n">
-        <v>0.4265</v>
+        <v>2.4641</v>
       </c>
       <c r="O74" t="n">
-        <v>1.8353</v>
+        <v>2.9847</v>
       </c>
       <c r="P74" t="n">
-        <v>50.86</v>
+        <v>51.57</v>
       </c>
       <c r="Q74" t="n">
-        <v>49.14</v>
+        <v>48.43</v>
       </c>
       <c r="R74" t="n">
-        <v>1.72</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="75">
@@ -8839,25 +8923,25 @@
         <v>0.3175</v>
       </c>
       <c r="L75" t="n">
-        <v>-1.8802</v>
+        <v>1.732</v>
       </c>
       <c r="M75" t="n">
         <v>3.4289</v>
       </c>
       <c r="N75" t="n">
-        <v>0.4373</v>
+        <v>2.4727</v>
       </c>
       <c r="O75" t="n">
-        <v>1.8588</v>
+        <v>3.0057</v>
       </c>
       <c r="P75" t="n">
-        <v>50.99</v>
+        <v>51.44</v>
       </c>
       <c r="Q75" t="n">
-        <v>49.01</v>
+        <v>48.56</v>
       </c>
       <c r="R75" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="76">
@@ -8899,25 +8983,25 @@
         <v>0.3168</v>
       </c>
       <c r="L76" t="n">
-        <v>-1.6356</v>
+        <v>1.732</v>
       </c>
       <c r="M76" t="n">
         <v>3.4862</v>
       </c>
       <c r="N76" t="n">
-        <v>0.6032999999999999</v>
+        <v>2.4988</v>
       </c>
       <c r="O76" t="n">
-        <v>1.9685</v>
+        <v>3.0354</v>
       </c>
       <c r="P76" t="n">
-        <v>50.87</v>
+        <v>51.48</v>
       </c>
       <c r="Q76" t="n">
-        <v>49.13</v>
+        <v>48.52</v>
       </c>
       <c r="R76" t="n">
-        <v>1.73</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="77">
@@ -8959,25 +9043,25 @@
         <v>0.3161</v>
       </c>
       <c r="L77" t="n">
-        <v>-1.8246</v>
+        <v>1.732</v>
       </c>
       <c r="M77" t="n">
         <v>3.4999</v>
       </c>
       <c r="N77" t="n">
-        <v>0.5062</v>
+        <v>2.5059</v>
       </c>
       <c r="O77" t="n">
-        <v>1.9438</v>
+        <v>3.0681</v>
       </c>
       <c r="P77" t="n">
-        <v>50.94</v>
+        <v>51.58</v>
       </c>
       <c r="Q77" t="n">
-        <v>49.06</v>
+        <v>48.42</v>
       </c>
       <c r="R77" t="n">
-        <v>1.87</v>
+        <v>3.16</v>
       </c>
     </row>
     <row r="78">
@@ -9019,25 +9103,25 @@
         <v>0.3154</v>
       </c>
       <c r="L78" t="n">
-        <v>-2.0255</v>
+        <v>1.732</v>
       </c>
       <c r="M78" t="n">
         <v>3.508</v>
       </c>
       <c r="N78" t="n">
-        <v>0.4003</v>
+        <v>2.5106</v>
       </c>
       <c r="O78" t="n">
-        <v>1.8908</v>
+        <v>3.076</v>
       </c>
       <c r="P78" t="n">
-        <v>50.9</v>
+        <v>51.56</v>
       </c>
       <c r="Q78" t="n">
-        <v>49.1</v>
+        <v>48.44</v>
       </c>
       <c r="R78" t="n">
-        <v>1.79</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="79">
@@ -9079,25 +9163,25 @@
         <v>0.3147</v>
       </c>
       <c r="L79" t="n">
-        <v>-1.9465</v>
+        <v>1.732</v>
       </c>
       <c r="M79" t="n">
         <v>3.4987</v>
       </c>
       <c r="N79" t="n">
-        <v>0.444</v>
+        <v>2.5076</v>
       </c>
       <c r="O79" t="n">
-        <v>1.9141</v>
+        <v>3.0718</v>
       </c>
       <c r="P79" t="n">
-        <v>50.96</v>
+        <v>51.62</v>
       </c>
       <c r="Q79" t="n">
-        <v>49.04</v>
+        <v>48.38</v>
       </c>
       <c r="R79" t="n">
-        <v>1.91</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="80">
@@ -9139,25 +9223,25 @@
         <v>0.314</v>
       </c>
       <c r="L80" t="n">
-        <v>-2.2024</v>
+        <v>1.8458</v>
       </c>
       <c r="M80" t="n">
         <v>3.5494</v>
       </c>
       <c r="N80" t="n">
-        <v>0.3264</v>
+        <v>2.5948</v>
       </c>
       <c r="O80" t="n">
-        <v>1.8504</v>
+        <v>3.1214</v>
       </c>
       <c r="P80" t="n">
-        <v>50.99</v>
+        <v>51.53</v>
       </c>
       <c r="Q80" t="n">
-        <v>49.01</v>
+        <v>48.47</v>
       </c>
       <c r="R80" t="n">
-        <v>1.97</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="81">
@@ -9199,25 +9283,25 @@
         <v>0.3133</v>
       </c>
       <c r="L81" t="n">
-        <v>-2.2024</v>
+        <v>1.8458</v>
       </c>
       <c r="M81" t="n">
         <v>3.5494</v>
       </c>
       <c r="N81" t="n">
-        <v>0.3301</v>
+        <v>2.5959</v>
       </c>
       <c r="O81" t="n">
-        <v>1.8547</v>
+        <v>3.1228</v>
       </c>
       <c r="P81" t="n">
-        <v>50.93</v>
+        <v>51.52</v>
       </c>
       <c r="Q81" t="n">
-        <v>49.07</v>
+        <v>48.48</v>
       </c>
       <c r="R81" t="n">
-        <v>1.86</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="82">
@@ -9259,25 +9343,25 @@
         <v>0.3125</v>
       </c>
       <c r="L82" t="n">
-        <v>-2.2024</v>
+        <v>1.8458</v>
       </c>
       <c r="M82" t="n">
         <v>3.5486</v>
       </c>
       <c r="N82" t="n">
-        <v>0.3336</v>
+        <v>2.5966</v>
       </c>
       <c r="O82" t="n">
-        <v>1.8571</v>
+        <v>3.1223</v>
       </c>
       <c r="P82" t="n">
-        <v>50.83</v>
+        <v>51.6</v>
       </c>
       <c r="Q82" t="n">
-        <v>49.17</v>
+        <v>48.4</v>
       </c>
       <c r="R82" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="83">
@@ -9319,25 +9403,25 @@
         <v>0.3118</v>
       </c>
       <c r="L83" t="n">
-        <v>-2.0696</v>
+        <v>1.8458</v>
       </c>
       <c r="M83" t="n">
         <v>3.6022</v>
       </c>
       <c r="N83" t="n">
-        <v>0.4352</v>
+        <v>2.6214</v>
       </c>
       <c r="O83" t="n">
-        <v>1.9286</v>
+        <v>3.1494</v>
       </c>
       <c r="P83" t="n">
-        <v>50.95</v>
+        <v>51.64</v>
       </c>
       <c r="Q83" t="n">
-        <v>49.05</v>
+        <v>48.36</v>
       </c>
       <c r="R83" t="n">
-        <v>1.89</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="84">
@@ -9379,25 +9463,25 @@
         <v>0.3111</v>
       </c>
       <c r="L84" t="n">
-        <v>-2.1145</v>
+        <v>1.8458</v>
       </c>
       <c r="M84" t="n">
         <v>3.6046</v>
       </c>
       <c r="N84" t="n">
-        <v>0.4149</v>
+        <v>2.6236</v>
       </c>
       <c r="O84" t="n">
-        <v>1.9196</v>
+        <v>3.1514</v>
       </c>
       <c r="P84" t="n">
-        <v>50.94</v>
+        <v>51.58</v>
       </c>
       <c r="Q84" t="n">
-        <v>49.06</v>
+        <v>48.42</v>
       </c>
       <c r="R84" t="n">
-        <v>1.89</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="85">
@@ -9439,25 +9523,25 @@
         <v>0.3103</v>
       </c>
       <c r="L85" t="n">
-        <v>-2.2323</v>
+        <v>1.8458</v>
       </c>
       <c r="M85" t="n">
         <v>3.6046</v>
       </c>
       <c r="N85" t="n">
-        <v>0.3531</v>
+        <v>2.6248</v>
       </c>
       <c r="O85" t="n">
-        <v>1.8874</v>
+        <v>3.1529</v>
       </c>
       <c r="P85" t="n">
-        <v>50.95</v>
+        <v>51.48</v>
       </c>
       <c r="Q85" t="n">
-        <v>49.05</v>
+        <v>48.52</v>
       </c>
       <c r="R85" t="n">
-        <v>1.89</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="86">
@@ -9499,25 +9583,25 @@
         <v>0.3095</v>
       </c>
       <c r="L86" t="n">
-        <v>-2.4159</v>
+        <v>1.8458</v>
       </c>
       <c r="M86" t="n">
         <v>3.5973</v>
       </c>
       <c r="N86" t="n">
-        <v>0.2517</v>
+        <v>2.6228</v>
       </c>
       <c r="O86" t="n">
-        <v>1.8409</v>
+        <v>3.1601</v>
       </c>
       <c r="P86" t="n">
-        <v>50.95</v>
+        <v>51.59</v>
       </c>
       <c r="Q86" t="n">
-        <v>49.05</v>
+        <v>48.41</v>
       </c>
       <c r="R86" t="n">
-        <v>1.89</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="87">
@@ -9559,25 +9643,25 @@
         <v>0.3088</v>
       </c>
       <c r="L87" t="n">
-        <v>-2.4694</v>
+        <v>1.8458</v>
       </c>
       <c r="M87" t="n">
         <v>3.5973</v>
       </c>
       <c r="N87" t="n">
-        <v>0.2261</v>
+        <v>2.624</v>
       </c>
       <c r="O87" t="n">
-        <v>1.8292</v>
+        <v>3.1616</v>
       </c>
       <c r="P87" t="n">
-        <v>50.92</v>
+        <v>51.67</v>
       </c>
       <c r="Q87" t="n">
-        <v>49.08</v>
+        <v>48.33</v>
       </c>
       <c r="R87" t="n">
-        <v>1.83</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="88">
@@ -9619,25 +9703,25 @@
         <v>0.308</v>
       </c>
       <c r="L88" t="n">
-        <v>-2.4694</v>
+        <v>1.8458</v>
       </c>
       <c r="M88" t="n">
         <v>3.5973</v>
       </c>
       <c r="N88" t="n">
-        <v>0.2303</v>
+        <v>2.6252</v>
       </c>
       <c r="O88" t="n">
-        <v>1.834</v>
+        <v>3.1631</v>
       </c>
       <c r="P88" t="n">
-        <v>50.87</v>
+        <v>51.53</v>
       </c>
       <c r="Q88" t="n">
-        <v>49.13</v>
+        <v>48.47</v>
       </c>
       <c r="R88" t="n">
-        <v>1.74</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="89">
@@ -9679,25 +9763,25 @@
         <v>0.3072</v>
       </c>
       <c r="L89" t="n">
-        <v>-2.4694</v>
+        <v>1.8458</v>
       </c>
       <c r="M89" t="n">
         <v>3.5973</v>
       </c>
       <c r="N89" t="n">
-        <v>0.2346</v>
+        <v>2.6264</v>
       </c>
       <c r="O89" t="n">
-        <v>1.8389</v>
+        <v>3.1646</v>
       </c>
       <c r="P89" t="n">
-        <v>50.95</v>
+        <v>51.6</v>
       </c>
       <c r="Q89" t="n">
-        <v>49.05</v>
+        <v>48.4</v>
       </c>
       <c r="R89" t="n">
-        <v>1.9</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="90">
@@ -9739,25 +9823,25 @@
         <v>0.3065</v>
       </c>
       <c r="L90" t="n">
-        <v>-2.4694</v>
+        <v>1.8458</v>
       </c>
       <c r="M90" t="n">
         <v>3.5973</v>
       </c>
       <c r="N90" t="n">
-        <v>0.2389</v>
+        <v>2.6277</v>
       </c>
       <c r="O90" t="n">
-        <v>1.8438</v>
+        <v>3.1662</v>
       </c>
       <c r="P90" t="n">
-        <v>50.89</v>
+        <v>51.65</v>
       </c>
       <c r="Q90" t="n">
-        <v>49.11</v>
+        <v>48.35</v>
       </c>
       <c r="R90" t="n">
-        <v>1.79</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="91">
@@ -9778,16 +9862,16 @@
         <v>0.4471</v>
       </c>
       <c r="E91" t="n">
-        <v>45.69314064017149</v>
+        <v>45.60888944834404</v>
       </c>
       <c r="F91" t="n">
-        <v>41.85788655348188</v>
+        <v>41.82180942093328</v>
       </c>
       <c r="G91" t="n">
-        <v>3.880459839312738</v>
+        <v>3.833948100564366</v>
       </c>
       <c r="H91" t="n">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="I91" t="n">
         <v>0.4471</v>
@@ -9799,85 +9883,205 @@
         <v>0.3057</v>
       </c>
       <c r="L91" t="n">
-        <v>-2.4755</v>
+        <v>1.8458</v>
       </c>
       <c r="M91" t="n">
-        <v>3.6343</v>
+        <v>3.5973</v>
       </c>
       <c r="N91" t="n">
-        <v>0.2564</v>
+        <v>2.6289</v>
       </c>
       <c r="O91" t="n">
-        <v>1.8768</v>
+        <v>3.1677</v>
       </c>
       <c r="P91" t="n">
-        <v>50.96</v>
+        <v>51.57</v>
       </c>
       <c r="Q91" t="n">
-        <v>49.04</v>
+        <v>48.43</v>
       </c>
       <c r="R91" t="n">
-        <v>1.93</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D92" t="n">
-        <v>0.4471</v>
+        <v>0.4479</v>
       </c>
       <c r="E92" t="n">
-        <v>45.69314064017149</v>
+        <v>45.60888944834404</v>
       </c>
       <c r="F92" t="n">
-        <v>41.85788655348188</v>
+        <v>41.82180942093328</v>
       </c>
       <c r="G92" t="n">
-        <v>3.880459839312738</v>
+        <v>3.833948100564366</v>
       </c>
       <c r="H92" t="n">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4471</v>
+        <v>0.4479</v>
       </c>
       <c r="J92" t="n">
-        <v>0.2472</v>
+        <v>0.2473</v>
       </c>
       <c r="K92" t="n">
-        <v>0.3057</v>
+        <v>0.3049</v>
       </c>
       <c r="L92" t="n">
-        <v>-2.4755</v>
+        <v>1.8458</v>
       </c>
       <c r="M92" t="n">
-        <v>3.6343</v>
+        <v>3.5973</v>
       </c>
       <c r="N92" t="n">
-        <v>0.2564</v>
+        <v>2.6302</v>
       </c>
       <c r="O92" t="n">
-        <v>1.8768</v>
+        <v>3.1693</v>
       </c>
       <c r="P92" t="n">
-        <v>50.96</v>
+        <v>51.59</v>
       </c>
       <c r="Q92" t="n">
-        <v>49.04</v>
+        <v>48.41</v>
       </c>
       <c r="R92" t="n">
-        <v>1.93</v>
+        <v>3.18</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>215</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="E93" t="n">
+        <v>45.60888944834404</v>
+      </c>
+      <c r="F93" t="n">
+        <v>41.82180942093328</v>
+      </c>
+      <c r="G93" t="n">
+        <v>3.833948100564366</v>
+      </c>
+      <c r="H93" t="n">
+        <v>465</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="L93" t="n">
+        <v>1.8458</v>
+      </c>
+      <c r="M93" t="n">
+        <v>3.5973</v>
+      </c>
+      <c r="N93" t="n">
+        <v>2.6315</v>
+      </c>
+      <c r="O93" t="n">
+        <v>3.1709</v>
+      </c>
+      <c r="P93" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="R93" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>215</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="E94" t="n">
+        <v>45.60888944834404</v>
+      </c>
+      <c r="F94" t="n">
+        <v>41.82180942093328</v>
+      </c>
+      <c r="G94" t="n">
+        <v>3.833948100564366</v>
+      </c>
+      <c r="H94" t="n">
+        <v>465</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="L94" t="n">
+        <v>1.8458</v>
+      </c>
+      <c r="M94" t="n">
+        <v>3.5973</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2.6315</v>
+      </c>
+      <c r="O94" t="n">
+        <v>3.1709</v>
+      </c>
+      <c r="P94" t="n">
+        <v>51.54</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>48.46</v>
+      </c>
+      <c r="R94" t="n">
+        <v>3.09</v>
       </c>
     </row>
   </sheetData>
@@ -9891,7 +10095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J92"/>
+  <dimension ref="A1:J94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13165,22 +13369,22 @@
         <v>217</v>
       </c>
       <c r="D91" t="n">
-        <v>42.77</v>
+        <v>42.84</v>
       </c>
       <c r="E91" t="n">
-        <v>54.1</v>
+        <v>54.08</v>
       </c>
       <c r="F91" t="n">
-        <v>-11.33</v>
+        <v>-11.24</v>
       </c>
       <c r="G91" t="n">
         <v>30</v>
       </c>
       <c r="H91" t="n">
-        <v>-5.42</v>
+        <v>-5.41</v>
       </c>
       <c r="I91" t="n">
-        <v>5.42</v>
+        <v>5.41</v>
       </c>
       <c r="J91" t="n">
         <v>0.151</v>
@@ -13189,36 +13393,108 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D92" t="n">
-        <v>42.77</v>
+        <v>42.84</v>
       </c>
       <c r="E92" t="n">
-        <v>54.1</v>
+        <v>54.08</v>
       </c>
       <c r="F92" t="n">
-        <v>-11.33</v>
+        <v>-11.24</v>
       </c>
       <c r="G92" t="n">
         <v>30</v>
       </c>
       <c r="H92" t="n">
-        <v>-5.42</v>
+        <v>-5.41</v>
       </c>
       <c r="I92" t="n">
-        <v>5.42</v>
+        <v>5.41</v>
       </c>
       <c r="J92" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>215</v>
+      </c>
+      <c r="D93" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="E93" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="F93" t="n">
+        <v>-11.24</v>
+      </c>
+      <c r="G93" t="n">
+        <v>30</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="I93" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>215</v>
+      </c>
+      <c r="D94" t="n">
+        <v>42.84</v>
+      </c>
+      <c r="E94" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="F94" t="n">
+        <v>-11.24</v>
+      </c>
+      <c r="G94" t="n">
+        <v>30</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-5.41</v>
+      </c>
+      <c r="I94" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="J94" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L94"/>
+  <dimension ref="A1:L95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4359,43 +4359,85 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D94" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E94" t="n">
-        <v>3.09</v>
+        <v>3.34</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1177</v>
+        <v>0.1189</v>
       </c>
       <c r="G94" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="H94" t="n">
-        <v>29.2</v>
+        <v>29.8</v>
       </c>
       <c r="I94" t="n">
-        <v>229.1</v>
+        <v>229.8</v>
       </c>
       <c r="J94" t="n">
-        <v>54.5</v>
+        <v>53.2</v>
       </c>
       <c r="K94" t="n">
         <v>22.2</v>
       </c>
       <c r="L94" t="n">
-        <v>37</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>214</v>
+      </c>
+      <c r="D95" t="n">
+        <v>214</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.1189</v>
+      </c>
+      <c r="G95" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H95" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="I95" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="J95" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="K95" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L95" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -4409,7 +4451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R94"/>
+  <dimension ref="A1:R95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10027,61 +10069,121 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D94" t="n">
-        <v>0.4486</v>
+        <v>0.4493</v>
       </c>
       <c r="E94" t="n">
-        <v>45.60888944834404</v>
+        <v>45.70944443944488</v>
       </c>
       <c r="F94" t="n">
-        <v>41.82180942093328</v>
+        <v>41.86011697608722</v>
       </c>
       <c r="G94" t="n">
-        <v>3.833948100564366</v>
+        <v>3.893823726942213</v>
       </c>
       <c r="H94" t="n">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4486</v>
+        <v>0.4493</v>
       </c>
       <c r="J94" t="n">
         <v>0.2474</v>
       </c>
       <c r="K94" t="n">
-        <v>0.3041</v>
+        <v>0.3032</v>
       </c>
       <c r="L94" t="n">
-        <v>1.8458</v>
+        <v>1.8177</v>
       </c>
       <c r="M94" t="n">
-        <v>3.5973</v>
+        <v>3.6652</v>
       </c>
       <c r="N94" t="n">
-        <v>2.6315</v>
+        <v>2.6478</v>
       </c>
       <c r="O94" t="n">
-        <v>3.1709</v>
+        <v>3.2077</v>
       </c>
       <c r="P94" t="n">
-        <v>51.54</v>
+        <v>51.67</v>
       </c>
       <c r="Q94" t="n">
-        <v>48.46</v>
+        <v>48.33</v>
       </c>
       <c r="R94" t="n">
-        <v>3.09</v>
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>214</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="E95" t="n">
+        <v>45.70944443944488</v>
+      </c>
+      <c r="F95" t="n">
+        <v>41.86011697608722</v>
+      </c>
+      <c r="G95" t="n">
+        <v>3.893823726942213</v>
+      </c>
+      <c r="H95" t="n">
+        <v>473</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.4493</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.2474</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1.8177</v>
+      </c>
+      <c r="M95" t="n">
+        <v>3.6652</v>
+      </c>
+      <c r="N95" t="n">
+        <v>2.6478</v>
+      </c>
+      <c r="O95" t="n">
+        <v>3.2077</v>
+      </c>
+      <c r="P95" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="R95" t="n">
+        <v>3.34</v>
       </c>
     </row>
   </sheetData>
@@ -10095,7 +10197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J94"/>
+  <dimension ref="A1:J95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13465,36 +13567,72 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D94" t="n">
-        <v>42.84</v>
+        <v>42.72</v>
       </c>
       <c r="E94" t="n">
-        <v>54.08</v>
+        <v>54.19</v>
       </c>
       <c r="F94" t="n">
-        <v>-11.24</v>
+        <v>-11.48</v>
       </c>
       <c r="G94" t="n">
         <v>30</v>
       </c>
       <c r="H94" t="n">
-        <v>-5.41</v>
+        <v>-5.44</v>
       </c>
       <c r="I94" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="J94" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-04-03</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>214</v>
+      </c>
+      <c r="D95" t="n">
+        <v>42.72</v>
+      </c>
+      <c r="E95" t="n">
+        <v>54.19</v>
+      </c>
+      <c r="F95" t="n">
+        <v>-11.48</v>
+      </c>
+      <c r="G95" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-5.44</v>
+      </c>
+      <c r="I95" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="J95" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4443,43 +4443,85 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D96" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E96" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1201</v>
+        <v>0.1213</v>
       </c>
       <c r="G96" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="H96" t="n">
-        <v>27.8</v>
+        <v>29.3</v>
       </c>
       <c r="I96" t="n">
-        <v>226.7</v>
+        <v>227.5</v>
       </c>
       <c r="J96" t="n">
-        <v>53.1</v>
+        <v>52.2</v>
       </c>
       <c r="K96" t="n">
-        <v>21.9</v>
+        <v>22.1</v>
       </c>
       <c r="L96" t="n">
-        <v>33.1</v>
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>212</v>
+      </c>
+      <c r="D97" t="n">
+        <v>212</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.1213</v>
+      </c>
+      <c r="G97" t="n">
+        <v>48</v>
+      </c>
+      <c r="H97" t="n">
+        <v>29.3</v>
+      </c>
+      <c r="I97" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="J97" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="K97" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L97" t="n">
+        <v>36.5</v>
       </c>
     </row>
   </sheetData>
@@ -4493,7 +4535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R96"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10231,61 +10273,121 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D96" t="n">
-        <v>0.4501</v>
+        <v>0.4508</v>
       </c>
       <c r="E96" t="n">
-        <v>45.67583791674215</v>
+        <v>45.74720692117553</v>
       </c>
       <c r="F96" t="n">
-        <v>41.80611540000019</v>
+        <v>41.84851252396025</v>
       </c>
       <c r="G96" t="n">
-        <v>2.607256410243362</v>
+        <v>2.648534174522336</v>
       </c>
       <c r="H96" t="n">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="I96" t="n">
-        <v>0.4501</v>
+        <v>0.4508</v>
       </c>
       <c r="J96" t="n">
-        <v>0.2475</v>
+        <v>0.2476</v>
       </c>
       <c r="K96" t="n">
-        <v>0.3024</v>
+        <v>0.3016</v>
       </c>
       <c r="L96" t="n">
         <v>1.8177</v>
       </c>
       <c r="M96" t="n">
-        <v>3.9489</v>
+        <v>4.0304</v>
       </c>
       <c r="N96" t="n">
-        <v>2.7769</v>
+        <v>2.8152</v>
       </c>
       <c r="O96" t="n">
-        <v>2.7005</v>
+        <v>2.7401</v>
       </c>
       <c r="P96" t="n">
-        <v>51.3</v>
+        <v>51.39</v>
       </c>
       <c r="Q96" t="n">
-        <v>48.7</v>
+        <v>48.61</v>
       </c>
       <c r="R96" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>212</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="E97" t="n">
+        <v>45.74720692117553</v>
+      </c>
+      <c r="F97" t="n">
+        <v>41.84851252396025</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2.648534174522336</v>
+      </c>
+      <c r="H97" t="n">
+        <v>473</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.2476</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.3016</v>
+      </c>
+      <c r="L97" t="n">
+        <v>1.8177</v>
+      </c>
+      <c r="M97" t="n">
+        <v>4.0304</v>
+      </c>
+      <c r="N97" t="n">
+        <v>2.8152</v>
+      </c>
+      <c r="O97" t="n">
+        <v>2.7401</v>
+      </c>
+      <c r="P97" t="n">
+        <v>51.39</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>48.61</v>
+      </c>
+      <c r="R97" t="n">
+        <v>2.78</v>
       </c>
     </row>
   </sheetData>
@@ -10299,7 +10401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J96"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13741,36 +13843,72 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-04-04</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D96" t="n">
-        <v>42.77</v>
+        <v>42.63</v>
       </c>
       <c r="E96" t="n">
-        <v>54.11</v>
+        <v>54.23</v>
       </c>
       <c r="F96" t="n">
-        <v>-11.34</v>
+        <v>-11.6</v>
       </c>
       <c r="G96" t="n">
         <v>30</v>
       </c>
       <c r="H96" t="n">
-        <v>-5.42</v>
+        <v>-5.45</v>
       </c>
       <c r="I96" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="J96" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>212</v>
+      </c>
+      <c r="D97" t="n">
+        <v>42.63</v>
+      </c>
+      <c r="E97" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="F97" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="G97" t="n">
+        <v>30</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="I97" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="J97" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4485,43 +4485,85 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D97" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E97" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1213</v>
+        <v>0.1225</v>
       </c>
       <c r="G97" t="n">
-        <v>48</v>
+        <v>48.1</v>
       </c>
       <c r="H97" t="n">
-        <v>29.3</v>
+        <v>27.7</v>
       </c>
       <c r="I97" t="n">
-        <v>227.5</v>
+        <v>227.4</v>
       </c>
       <c r="J97" t="n">
-        <v>52.2</v>
+        <v>52.1</v>
       </c>
       <c r="K97" t="n">
         <v>22.1</v>
       </c>
       <c r="L97" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>211</v>
+      </c>
+      <c r="D98" t="n">
+        <v>211</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="G98" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="I98" t="n">
+        <v>227.4</v>
+      </c>
+      <c r="J98" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="K98" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>36.3</v>
       </c>
     </row>
   </sheetData>
@@ -4535,7 +4577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10333,19 +10375,19 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D97" t="n">
-        <v>0.4508</v>
+        <v>0.4516</v>
       </c>
       <c r="E97" t="n">
         <v>45.74720692117553</v>
@@ -10360,34 +10402,94 @@
         <v>473</v>
       </c>
       <c r="I97" t="n">
-        <v>0.4508</v>
+        <v>0.4516</v>
       </c>
       <c r="J97" t="n">
-        <v>0.2476</v>
+        <v>0.2477</v>
       </c>
       <c r="K97" t="n">
-        <v>0.3016</v>
+        <v>0.3008</v>
       </c>
       <c r="L97" t="n">
         <v>1.8177</v>
       </c>
       <c r="M97" t="n">
-        <v>4.0304</v>
+        <v>4.0205</v>
       </c>
       <c r="N97" t="n">
-        <v>2.8152</v>
+        <v>2.8125</v>
       </c>
       <c r="O97" t="n">
-        <v>2.7401</v>
+        <v>2.7384</v>
       </c>
       <c r="P97" t="n">
-        <v>51.39</v>
+        <v>51.43</v>
       </c>
       <c r="Q97" t="n">
-        <v>48.61</v>
+        <v>48.57</v>
       </c>
       <c r="R97" t="n">
-        <v>2.78</v>
+        <v>2.86</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>211</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="E98" t="n">
+        <v>45.74720692117553</v>
+      </c>
+      <c r="F98" t="n">
+        <v>41.84851252396025</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2.648534174522336</v>
+      </c>
+      <c r="H98" t="n">
+        <v>473</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="L98" t="n">
+        <v>1.8177</v>
+      </c>
+      <c r="M98" t="n">
+        <v>4.0205</v>
+      </c>
+      <c r="N98" t="n">
+        <v>2.8125</v>
+      </c>
+      <c r="O98" t="n">
+        <v>2.7384</v>
+      </c>
+      <c r="P98" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="R98" t="n">
+        <v>2.86</v>
       </c>
     </row>
   </sheetData>
@@ -10401,7 +10503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13879,25 +13981,25 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D97" t="n">
-        <v>42.63</v>
+        <v>42.65</v>
       </c>
       <c r="E97" t="n">
-        <v>54.23</v>
+        <v>54.21</v>
       </c>
       <c r="F97" t="n">
-        <v>-11.6</v>
+        <v>-11.56</v>
       </c>
       <c r="G97" t="n">
         <v>30</v>
@@ -13909,6 +14011,42 @@
         <v>5.45</v>
       </c>
       <c r="J97" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>211</v>
+      </c>
+      <c r="D98" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="E98" t="n">
+        <v>54.21</v>
+      </c>
+      <c r="F98" t="n">
+        <v>-11.56</v>
+      </c>
+      <c r="G98" t="n">
+        <v>30</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="I98" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="J98" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L98"/>
+  <dimension ref="A1:L99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4527,43 +4527,85 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D98" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E98" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1225</v>
+        <v>0.1237</v>
       </c>
       <c r="G98" t="n">
-        <v>48.1</v>
+        <v>48</v>
       </c>
       <c r="H98" t="n">
-        <v>27.7</v>
+        <v>27.1</v>
       </c>
       <c r="I98" t="n">
-        <v>227.4</v>
+        <v>227.2</v>
       </c>
       <c r="J98" t="n">
-        <v>52.1</v>
+        <v>52.7</v>
       </c>
       <c r="K98" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="L98" t="n">
-        <v>36.3</v>
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>210</v>
+      </c>
+      <c r="D99" t="n">
+        <v>210</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.1237</v>
+      </c>
+      <c r="G99" t="n">
+        <v>48</v>
+      </c>
+      <c r="H99" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="I99" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="J99" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="K99" t="n">
+        <v>22</v>
+      </c>
+      <c r="L99" t="n">
+        <v>35.9</v>
       </c>
     </row>
   </sheetData>
@@ -4577,7 +4619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R98"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10435,61 +10477,121 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D98" t="n">
-        <v>0.4516</v>
+        <v>0.4523</v>
       </c>
       <c r="E98" t="n">
-        <v>45.74720692117553</v>
+        <v>45.70463935304412</v>
       </c>
       <c r="F98" t="n">
-        <v>41.84851252396025</v>
+        <v>41.82882974611812</v>
       </c>
       <c r="G98" t="n">
-        <v>2.648534174522336</v>
+        <v>2.627710937449196</v>
       </c>
       <c r="H98" t="n">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="I98" t="n">
-        <v>0.4516</v>
+        <v>0.4523</v>
       </c>
       <c r="J98" t="n">
         <v>0.2477</v>
       </c>
       <c r="K98" t="n">
-        <v>0.3008</v>
+        <v>0.2999</v>
       </c>
       <c r="L98" t="n">
-        <v>1.8177</v>
+        <v>1.8404</v>
       </c>
       <c r="M98" t="n">
-        <v>4.0205</v>
+        <v>4.0544</v>
       </c>
       <c r="N98" t="n">
-        <v>2.8125</v>
+        <v>2.8418</v>
       </c>
       <c r="O98" t="n">
-        <v>2.7384</v>
+        <v>2.745</v>
       </c>
       <c r="P98" t="n">
-        <v>51.43</v>
+        <v>51.4</v>
       </c>
       <c r="Q98" t="n">
-        <v>48.57</v>
+        <v>48.6</v>
       </c>
       <c r="R98" t="n">
-        <v>2.86</v>
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>210</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="E99" t="n">
+        <v>45.70463935304412</v>
+      </c>
+      <c r="F99" t="n">
+        <v>41.82882974611812</v>
+      </c>
+      <c r="G99" t="n">
+        <v>2.627710937449196</v>
+      </c>
+      <c r="H99" t="n">
+        <v>475</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.4523</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="L99" t="n">
+        <v>1.8404</v>
+      </c>
+      <c r="M99" t="n">
+        <v>4.0544</v>
+      </c>
+      <c r="N99" t="n">
+        <v>2.8418</v>
+      </c>
+      <c r="O99" t="n">
+        <v>2.745</v>
+      </c>
+      <c r="P99" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="R99" t="n">
+        <v>2.79</v>
       </c>
     </row>
   </sheetData>
@@ -10503,7 +10605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J98"/>
+  <dimension ref="A1:J99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14017,36 +14119,72 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D98" t="n">
-        <v>42.65</v>
+        <v>42.58</v>
       </c>
       <c r="E98" t="n">
-        <v>54.21</v>
+        <v>54.24</v>
       </c>
       <c r="F98" t="n">
-        <v>-11.56</v>
+        <v>-11.66</v>
       </c>
       <c r="G98" t="n">
         <v>30</v>
       </c>
       <c r="H98" t="n">
-        <v>-5.45</v>
+        <v>-5.46</v>
       </c>
       <c r="I98" t="n">
-        <v>5.45</v>
+        <v>5.46</v>
       </c>
       <c r="J98" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>210</v>
+      </c>
+      <c r="D99" t="n">
+        <v>42.58</v>
+      </c>
+      <c r="E99" t="n">
+        <v>54.24</v>
+      </c>
+      <c r="F99" t="n">
+        <v>-11.66</v>
+      </c>
+      <c r="G99" t="n">
+        <v>30</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-5.46</v>
+      </c>
+      <c r="I99" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="J99" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L99"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4569,43 +4569,85 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D99" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E99" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
       </c>
       <c r="F99" t="n">
-        <v>0.1237</v>
+        <v>0.125</v>
       </c>
       <c r="G99" t="n">
         <v>48</v>
       </c>
       <c r="H99" t="n">
-        <v>27.1</v>
+        <v>30.1</v>
       </c>
       <c r="I99" t="n">
-        <v>227.2</v>
+        <v>227.7</v>
       </c>
       <c r="J99" t="n">
-        <v>52.7</v>
+        <v>52.4</v>
       </c>
       <c r="K99" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="L99" t="n">
-        <v>35.9</v>
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>209</v>
+      </c>
+      <c r="D100" t="n">
+        <v>209</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G100" t="n">
+        <v>48</v>
+      </c>
+      <c r="H100" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="I100" t="n">
+        <v>227.7</v>
+      </c>
+      <c r="J100" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="K100" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L100" t="n">
+        <v>34.7</v>
       </c>
     </row>
   </sheetData>
@@ -4619,7 +4661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10537,61 +10579,121 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D99" t="n">
-        <v>0.4523</v>
+        <v>0.4531</v>
       </c>
       <c r="E99" t="n">
-        <v>45.70463935304412</v>
+        <v>45.74386101569746</v>
       </c>
       <c r="F99" t="n">
-        <v>41.82882974611812</v>
+        <v>41.84747110975376</v>
       </c>
       <c r="G99" t="n">
-        <v>2.627710937449196</v>
+        <v>2.638287853912544</v>
       </c>
       <c r="H99" t="n">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I99" t="n">
-        <v>0.4523</v>
+        <v>0.4531</v>
       </c>
       <c r="J99" t="n">
-        <v>0.2477</v>
+        <v>0.2478</v>
       </c>
       <c r="K99" t="n">
-        <v>0.2999</v>
+        <v>0.2991</v>
       </c>
       <c r="L99" t="n">
-        <v>1.8404</v>
+        <v>1.3299</v>
       </c>
       <c r="M99" t="n">
-        <v>4.0544</v>
+        <v>4.0653</v>
       </c>
       <c r="N99" t="n">
-        <v>2.8418</v>
+        <v>2.5693</v>
       </c>
       <c r="O99" t="n">
-        <v>2.745</v>
+        <v>2.6006</v>
       </c>
       <c r="P99" t="n">
-        <v>51.4</v>
+        <v>51.42</v>
       </c>
       <c r="Q99" t="n">
-        <v>48.6</v>
+        <v>48.58</v>
       </c>
       <c r="R99" t="n">
-        <v>2.79</v>
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>209</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="E100" t="n">
+        <v>45.74386101569746</v>
+      </c>
+      <c r="F100" t="n">
+        <v>41.84747110975376</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2.638287853912544</v>
+      </c>
+      <c r="H100" t="n">
+        <v>476</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.2478</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="L100" t="n">
+        <v>1.3299</v>
+      </c>
+      <c r="M100" t="n">
+        <v>4.0653</v>
+      </c>
+      <c r="N100" t="n">
+        <v>2.5693</v>
+      </c>
+      <c r="O100" t="n">
+        <v>2.6006</v>
+      </c>
+      <c r="P100" t="n">
+        <v>51.42</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>48.58</v>
+      </c>
+      <c r="R100" t="n">
+        <v>2.85</v>
       </c>
     </row>
   </sheetData>
@@ -10605,7 +10707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J99"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14155,36 +14257,72 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D99" t="n">
-        <v>42.58</v>
+        <v>42.56</v>
       </c>
       <c r="E99" t="n">
-        <v>54.24</v>
+        <v>54.26</v>
       </c>
       <c r="F99" t="n">
-        <v>-11.66</v>
+        <v>-11.7</v>
       </c>
       <c r="G99" t="n">
         <v>30</v>
       </c>
       <c r="H99" t="n">
-        <v>-5.46</v>
+        <v>-5.47</v>
       </c>
       <c r="I99" t="n">
-        <v>5.46</v>
+        <v>5.47</v>
       </c>
       <c r="J99" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>209</v>
+      </c>
+      <c r="D100" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="E100" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="F100" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="G100" t="n">
+        <v>30</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="I100" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J100" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L100"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4611,43 +4611,85 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D100" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E100" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="F100" t="n">
-        <v>0.125</v>
+        <v>0.1262</v>
       </c>
       <c r="G100" t="n">
         <v>48</v>
       </c>
       <c r="H100" t="n">
-        <v>30.1</v>
+        <v>28.4</v>
       </c>
       <c r="I100" t="n">
-        <v>227.7</v>
+        <v>226.9</v>
       </c>
       <c r="J100" t="n">
-        <v>52.4</v>
+        <v>51.7</v>
       </c>
       <c r="K100" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="L100" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>208</v>
+      </c>
+      <c r="D101" t="n">
+        <v>208</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.1262</v>
+      </c>
+      <c r="G101" t="n">
+        <v>48</v>
+      </c>
+      <c r="H101" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="I101" t="n">
+        <v>226.9</v>
+      </c>
+      <c r="J101" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="K101" t="n">
+        <v>22</v>
+      </c>
+      <c r="L101" t="n">
+        <v>32.8</v>
       </c>
     </row>
   </sheetData>
@@ -4661,7 +4703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R100"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10639,19 +10681,19 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D100" t="n">
-        <v>0.4531</v>
+        <v>0.4539</v>
       </c>
       <c r="E100" t="n">
         <v>45.74386101569746</v>
@@ -10666,34 +10708,94 @@
         <v>476</v>
       </c>
       <c r="I100" t="n">
-        <v>0.4531</v>
+        <v>0.4539</v>
       </c>
       <c r="J100" t="n">
-        <v>0.2478</v>
+        <v>0.2479</v>
       </c>
       <c r="K100" t="n">
-        <v>0.2991</v>
+        <v>0.2982</v>
       </c>
       <c r="L100" t="n">
-        <v>1.3299</v>
+        <v>2.5765</v>
       </c>
       <c r="M100" t="n">
         <v>4.0653</v>
       </c>
       <c r="N100" t="n">
-        <v>2.5693</v>
+        <v>3.2522</v>
       </c>
       <c r="O100" t="n">
-        <v>2.6006</v>
+        <v>2.9736</v>
       </c>
       <c r="P100" t="n">
-        <v>51.42</v>
+        <v>51.41</v>
       </c>
       <c r="Q100" t="n">
-        <v>48.58</v>
+        <v>48.59</v>
       </c>
       <c r="R100" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>208</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="E101" t="n">
+        <v>45.74386101569746</v>
+      </c>
+      <c r="F101" t="n">
+        <v>41.84747110975376</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2.638287853912544</v>
+      </c>
+      <c r="H101" t="n">
+        <v>476</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.4539</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="L101" t="n">
+        <v>2.5765</v>
+      </c>
+      <c r="M101" t="n">
+        <v>4.0653</v>
+      </c>
+      <c r="N101" t="n">
+        <v>3.2522</v>
+      </c>
+      <c r="O101" t="n">
+        <v>2.9736</v>
+      </c>
+      <c r="P101" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="R101" t="n">
+        <v>2.83</v>
       </c>
     </row>
   </sheetData>
@@ -10707,7 +10809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J100"/>
+  <dimension ref="A1:J101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14293,16 +14395,16 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D100" t="n">
         <v>42.56</v>
@@ -14323,6 +14425,42 @@
         <v>5.47</v>
       </c>
       <c r="J100" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>208</v>
+      </c>
+      <c r="D101" t="n">
+        <v>42.56</v>
+      </c>
+      <c r="E101" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="F101" t="n">
+        <v>-11.7</v>
+      </c>
+      <c r="G101" t="n">
+        <v>30</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="I101" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J101" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4653,43 +4653,85 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D101" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E101" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
       </c>
       <c r="F101" t="n">
-        <v>0.1262</v>
+        <v>0.1275</v>
       </c>
       <c r="G101" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="H101" t="n">
-        <v>28.4</v>
+        <v>28.8</v>
       </c>
       <c r="I101" t="n">
-        <v>226.9</v>
+        <v>229.4</v>
       </c>
       <c r="J101" t="n">
-        <v>51.7</v>
+        <v>54</v>
       </c>
       <c r="K101" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="L101" t="n">
-        <v>32.8</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>207</v>
+      </c>
+      <c r="D102" t="n">
+        <v>207</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.1275</v>
+      </c>
+      <c r="G102" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="I102" t="n">
+        <v>229.4</v>
+      </c>
+      <c r="J102" t="n">
+        <v>54</v>
+      </c>
+      <c r="K102" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L102" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -4703,7 +4745,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10741,61 +10783,121 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D101" t="n">
-        <v>0.4539</v>
+        <v>0.4547</v>
       </c>
       <c r="E101" t="n">
-        <v>45.74386101569746</v>
+        <v>45.76728590329925</v>
       </c>
       <c r="F101" t="n">
-        <v>41.84747110975376</v>
+        <v>41.83974619104041</v>
       </c>
       <c r="G101" t="n">
-        <v>2.638287853912544</v>
+        <v>2.664921518841438</v>
       </c>
       <c r="H101" t="n">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="I101" t="n">
-        <v>0.4539</v>
+        <v>0.4547</v>
       </c>
       <c r="J101" t="n">
         <v>0.2479</v>
       </c>
       <c r="K101" t="n">
-        <v>0.2982</v>
+        <v>0.2974</v>
       </c>
       <c r="L101" t="n">
-        <v>2.5765</v>
+        <v>3.7775</v>
       </c>
       <c r="M101" t="n">
-        <v>4.0653</v>
+        <v>4.0806</v>
       </c>
       <c r="N101" t="n">
-        <v>3.2522</v>
+        <v>3.9154</v>
       </c>
       <c r="O101" t="n">
-        <v>2.9736</v>
+        <v>3.3468</v>
       </c>
       <c r="P101" t="n">
-        <v>51.41</v>
+        <v>51.62</v>
       </c>
       <c r="Q101" t="n">
-        <v>48.59</v>
+        <v>48.38</v>
       </c>
       <c r="R101" t="n">
-        <v>2.83</v>
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>207</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="E102" t="n">
+        <v>45.76728590329925</v>
+      </c>
+      <c r="F102" t="n">
+        <v>41.83974619104041</v>
+      </c>
+      <c r="G102" t="n">
+        <v>2.664921518841438</v>
+      </c>
+      <c r="H102" t="n">
+        <v>479</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.4547</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.2479</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="L102" t="n">
+        <v>3.7775</v>
+      </c>
+      <c r="M102" t="n">
+        <v>4.0806</v>
+      </c>
+      <c r="N102" t="n">
+        <v>3.9154</v>
+      </c>
+      <c r="O102" t="n">
+        <v>3.3468</v>
+      </c>
+      <c r="P102" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="R102" t="n">
+        <v>3.25</v>
       </c>
     </row>
   </sheetData>
@@ -10809,7 +10911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14431,25 +14533,25 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D101" t="n">
-        <v>42.56</v>
+        <v>42.55</v>
       </c>
       <c r="E101" t="n">
         <v>54.26</v>
       </c>
       <c r="F101" t="n">
-        <v>-11.7</v>
+        <v>-11.71</v>
       </c>
       <c r="G101" t="n">
         <v>30</v>
@@ -14461,6 +14563,42 @@
         <v>5.47</v>
       </c>
       <c r="J101" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>207</v>
+      </c>
+      <c r="D102" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="E102" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="F102" t="n">
+        <v>-11.71</v>
+      </c>
+      <c r="G102" t="n">
+        <v>30</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="I102" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J102" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:L103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4695,43 +4695,85 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D102" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E102" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="F102" t="n">
-        <v>0.1275</v>
+        <v>0.1288</v>
       </c>
       <c r="G102" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="H102" t="n">
-        <v>28.8</v>
+        <v>30.1</v>
       </c>
       <c r="I102" t="n">
-        <v>229.4</v>
+        <v>229.2</v>
       </c>
       <c r="J102" t="n">
-        <v>54</v>
+        <v>53.1</v>
       </c>
       <c r="K102" t="n">
         <v>22.2</v>
       </c>
       <c r="L102" t="n">
-        <v>36</v>
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>206</v>
+      </c>
+      <c r="D103" t="n">
+        <v>206</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.1288</v>
+      </c>
+      <c r="G103" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="H103" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="I103" t="n">
+        <v>229.2</v>
+      </c>
+      <c r="J103" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L103" t="n">
+        <v>35.9</v>
       </c>
     </row>
   </sheetData>
@@ -4745,7 +4787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R102"/>
+  <dimension ref="A1:R103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10843,19 +10885,19 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D102" t="n">
-        <v>0.4547</v>
+        <v>0.4555</v>
       </c>
       <c r="E102" t="n">
         <v>45.76728590329925</v>
@@ -10870,34 +10912,94 @@
         <v>479</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4547</v>
+        <v>0.4555</v>
       </c>
       <c r="J102" t="n">
-        <v>0.2479</v>
+        <v>0.248</v>
       </c>
       <c r="K102" t="n">
-        <v>0.2974</v>
+        <v>0.2965</v>
       </c>
       <c r="L102" t="n">
-        <v>3.7775</v>
+        <v>3.6085</v>
       </c>
       <c r="M102" t="n">
         <v>4.0806</v>
       </c>
       <c r="N102" t="n">
-        <v>3.9154</v>
+        <v>3.8235</v>
       </c>
       <c r="O102" t="n">
-        <v>3.3468</v>
+        <v>3.2958</v>
       </c>
       <c r="P102" t="n">
-        <v>51.62</v>
+        <v>51.66</v>
       </c>
       <c r="Q102" t="n">
-        <v>48.38</v>
+        <v>48.34</v>
       </c>
       <c r="R102" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>206</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.4555</v>
+      </c>
+      <c r="E103" t="n">
+        <v>45.76728590329925</v>
+      </c>
+      <c r="F103" t="n">
+        <v>41.83974619104041</v>
+      </c>
+      <c r="G103" t="n">
+        <v>2.664921518841438</v>
+      </c>
+      <c r="H103" t="n">
+        <v>479</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.4555</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="L103" t="n">
+        <v>3.6085</v>
+      </c>
+      <c r="M103" t="n">
+        <v>4.0806</v>
+      </c>
+      <c r="N103" t="n">
+        <v>3.8235</v>
+      </c>
+      <c r="O103" t="n">
+        <v>3.2958</v>
+      </c>
+      <c r="P103" t="n">
+        <v>51.66</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="R103" t="n">
+        <v>3.33</v>
       </c>
     </row>
   </sheetData>
@@ -10911,7 +11013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J102"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14569,16 +14671,16 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D102" t="n">
         <v>42.55</v>
@@ -14599,6 +14701,42 @@
         <v>5.47</v>
       </c>
       <c r="J102" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>206</v>
+      </c>
+      <c r="D103" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="E103" t="n">
+        <v>54.26</v>
+      </c>
+      <c r="F103" t="n">
+        <v>-11.71</v>
+      </c>
+      <c r="G103" t="n">
+        <v>30</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="I103" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J103" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L103"/>
+  <dimension ref="A1:L104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4737,43 +4737,85 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D103" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E103" t="n">
-        <v>3.33</v>
+        <v>3.24</v>
       </c>
       <c r="F103" t="n">
-        <v>0.1288</v>
+        <v>0.1301</v>
       </c>
       <c r="G103" t="n">
         <v>48.2</v>
       </c>
       <c r="H103" t="n">
-        <v>30.1</v>
+        <v>27.8</v>
       </c>
       <c r="I103" t="n">
-        <v>229.2</v>
+        <v>228.9</v>
       </c>
       <c r="J103" t="n">
-        <v>53.1</v>
+        <v>53</v>
       </c>
       <c r="K103" t="n">
         <v>22.2</v>
       </c>
       <c r="L103" t="n">
-        <v>35.9</v>
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>205</v>
+      </c>
+      <c r="D104" t="n">
+        <v>205</v>
+      </c>
+      <c r="E104" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.1301</v>
+      </c>
+      <c r="G104" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="I104" t="n">
+        <v>228.9</v>
+      </c>
+      <c r="J104" t="n">
+        <v>53</v>
+      </c>
+      <c r="K104" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="L104" t="n">
+        <v>36.6</v>
       </c>
     </row>
   </sheetData>
@@ -4787,7 +4829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R103"/>
+  <dimension ref="A1:R104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10945,19 +10987,19 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D103" t="n">
-        <v>0.4555</v>
+        <v>0.4563</v>
       </c>
       <c r="E103" t="n">
         <v>45.76728590329925</v>
@@ -10972,34 +11014,94 @@
         <v>479</v>
       </c>
       <c r="I103" t="n">
-        <v>0.4555</v>
+        <v>0.4563</v>
       </c>
       <c r="J103" t="n">
-        <v>0.248</v>
+        <v>0.2481</v>
       </c>
       <c r="K103" t="n">
-        <v>0.2965</v>
+        <v>0.2956</v>
       </c>
       <c r="L103" t="n">
         <v>3.6085</v>
       </c>
       <c r="M103" t="n">
-        <v>4.0806</v>
+        <v>4.0869</v>
       </c>
       <c r="N103" t="n">
-        <v>3.8235</v>
+        <v>3.8268</v>
       </c>
       <c r="O103" t="n">
-        <v>3.2958</v>
+        <v>3.2966</v>
       </c>
       <c r="P103" t="n">
-        <v>51.66</v>
+        <v>51.62</v>
       </c>
       <c r="Q103" t="n">
-        <v>48.34</v>
+        <v>48.38</v>
       </c>
       <c r="R103" t="n">
-        <v>3.33</v>
+        <v>3.24</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>205</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="E104" t="n">
+        <v>45.76728590329925</v>
+      </c>
+      <c r="F104" t="n">
+        <v>41.83974619104041</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2.664921518841438</v>
+      </c>
+      <c r="H104" t="n">
+        <v>479</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.4563</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.2481</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.2956</v>
+      </c>
+      <c r="L104" t="n">
+        <v>3.6085</v>
+      </c>
+      <c r="M104" t="n">
+        <v>4.0869</v>
+      </c>
+      <c r="N104" t="n">
+        <v>3.8268</v>
+      </c>
+      <c r="O104" t="n">
+        <v>3.2966</v>
+      </c>
+      <c r="P104" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>48.38</v>
+      </c>
+      <c r="R104" t="n">
+        <v>3.24</v>
       </c>
     </row>
   </sheetData>
@@ -11013,7 +11115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14707,25 +14809,25 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D103" t="n">
-        <v>42.55</v>
+        <v>42.54</v>
       </c>
       <c r="E103" t="n">
-        <v>54.26</v>
+        <v>54.29</v>
       </c>
       <c r="F103" t="n">
-        <v>-11.71</v>
+        <v>-11.74</v>
       </c>
       <c r="G103" t="n">
         <v>30</v>
@@ -14737,6 +14839,42 @@
         <v>5.47</v>
       </c>
       <c r="J103" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>205</v>
+      </c>
+      <c r="D104" t="n">
+        <v>42.54</v>
+      </c>
+      <c r="E104" t="n">
+        <v>54.29</v>
+      </c>
+      <c r="F104" t="n">
+        <v>-11.74</v>
+      </c>
+      <c r="G104" t="n">
+        <v>30</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="I104" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J104" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L104"/>
+  <dimension ref="A1:L105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4779,43 +4779,85 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D104" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E104" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
       </c>
       <c r="F104" t="n">
-        <v>0.1301</v>
+        <v>0.1314</v>
       </c>
       <c r="G104" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="H104" t="n">
-        <v>27.8</v>
+        <v>28.3</v>
       </c>
       <c r="I104" t="n">
-        <v>228.9</v>
+        <v>227.8</v>
       </c>
       <c r="J104" t="n">
-        <v>53</v>
+        <v>53.2</v>
       </c>
       <c r="K104" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="L104" t="n">
-        <v>36.6</v>
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>204</v>
+      </c>
+      <c r="D105" t="n">
+        <v>204</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="G105" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="H105" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="I105" t="n">
+        <v>227.8</v>
+      </c>
+      <c r="J105" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="K105" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="L105" t="n">
+        <v>34.5</v>
       </c>
     </row>
   </sheetData>
@@ -4829,7 +4871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R104"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11047,61 +11089,121 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D104" t="n">
-        <v>0.4563</v>
+        <v>0.4571</v>
       </c>
       <c r="E104" t="n">
-        <v>45.76728590329925</v>
+        <v>45.7693685895654</v>
       </c>
       <c r="F104" t="n">
-        <v>41.83974619104041</v>
+        <v>41.85639462409353</v>
       </c>
       <c r="G104" t="n">
-        <v>2.664921518841438</v>
+        <v>2.661655635741611</v>
       </c>
       <c r="H104" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="I104" t="n">
-        <v>0.4563</v>
+        <v>0.4571</v>
       </c>
       <c r="J104" t="n">
-        <v>0.2481</v>
+        <v>0.2482</v>
       </c>
       <c r="K104" t="n">
-        <v>0.2956</v>
+        <v>0.2947</v>
       </c>
       <c r="L104" t="n">
         <v>3.6085</v>
       </c>
       <c r="M104" t="n">
-        <v>4.0869</v>
+        <v>4.0877</v>
       </c>
       <c r="N104" t="n">
-        <v>3.8268</v>
+        <v>3.8275</v>
       </c>
       <c r="O104" t="n">
-        <v>3.2966</v>
+        <v>3.2946</v>
       </c>
       <c r="P104" t="n">
-        <v>51.62</v>
+        <v>51.47</v>
       </c>
       <c r="Q104" t="n">
-        <v>48.38</v>
+        <v>48.53</v>
       </c>
       <c r="R104" t="n">
-        <v>3.24</v>
+        <v>2.95</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>204</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="E105" t="n">
+        <v>45.7693685895654</v>
+      </c>
+      <c r="F105" t="n">
+        <v>41.85639462409353</v>
+      </c>
+      <c r="G105" t="n">
+        <v>2.661655635741611</v>
+      </c>
+      <c r="H105" t="n">
+        <v>480</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.4571</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="L105" t="n">
+        <v>3.6085</v>
+      </c>
+      <c r="M105" t="n">
+        <v>4.0877</v>
+      </c>
+      <c r="N105" t="n">
+        <v>3.8275</v>
+      </c>
+      <c r="O105" t="n">
+        <v>3.2946</v>
+      </c>
+      <c r="P105" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="R105" t="n">
+        <v>2.95</v>
       </c>
     </row>
   </sheetData>
@@ -11115,7 +11217,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14845,25 +14947,25 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D104" t="n">
-        <v>42.54</v>
+        <v>42.53</v>
       </c>
       <c r="E104" t="n">
-        <v>54.29</v>
+        <v>54.3</v>
       </c>
       <c r="F104" t="n">
-        <v>-11.74</v>
+        <v>-11.76</v>
       </c>
       <c r="G104" t="n">
         <v>30</v>
@@ -14875,6 +14977,42 @@
         <v>5.47</v>
       </c>
       <c r="J104" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>204</v>
+      </c>
+      <c r="D105" t="n">
+        <v>42.53</v>
+      </c>
+      <c r="E105" t="n">
+        <v>54.3</v>
+      </c>
+      <c r="F105" t="n">
+        <v>-11.76</v>
+      </c>
+      <c r="G105" t="n">
+        <v>30</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-5.47</v>
+      </c>
+      <c r="I105" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="J105" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4821,43 +4821,85 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D105" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E105" t="n">
-        <v>2.95</v>
+        <v>3.74</v>
       </c>
       <c r="F105" t="n">
-        <v>0.1314</v>
+        <v>0.1327</v>
       </c>
       <c r="G105" t="n">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
       <c r="H105" t="n">
-        <v>28.3</v>
+        <v>31.1</v>
       </c>
       <c r="I105" t="n">
-        <v>227.8</v>
+        <v>231.3</v>
       </c>
       <c r="J105" t="n">
-        <v>53.2</v>
+        <v>54.6</v>
       </c>
       <c r="K105" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="L105" t="n">
-        <v>34.5</v>
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>203</v>
+      </c>
+      <c r="D106" t="n">
+        <v>203</v>
+      </c>
+      <c r="E106" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.1327</v>
+      </c>
+      <c r="G106" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H106" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="I106" t="n">
+        <v>231.3</v>
+      </c>
+      <c r="J106" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="K106" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L106" t="n">
+        <v>36.9</v>
       </c>
     </row>
   </sheetData>
@@ -4871,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11149,61 +11191,121 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4571</v>
+        <v>0.4579</v>
       </c>
       <c r="E105" t="n">
-        <v>45.7693685895654</v>
+        <v>45.73433896290638</v>
       </c>
       <c r="F105" t="n">
-        <v>41.85639462409353</v>
+        <v>41.81528399596738</v>
       </c>
       <c r="G105" t="n">
-        <v>2.661655635741611</v>
+        <v>2.66985670954591</v>
       </c>
       <c r="H105" t="n">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="I105" t="n">
-        <v>0.4571</v>
+        <v>0.4579</v>
       </c>
       <c r="J105" t="n">
         <v>0.2482</v>
       </c>
       <c r="K105" t="n">
-        <v>0.2947</v>
+        <v>0.2939</v>
       </c>
       <c r="L105" t="n">
-        <v>3.6085</v>
+        <v>4.5084</v>
       </c>
       <c r="M105" t="n">
-        <v>4.0877</v>
+        <v>4.1001</v>
       </c>
       <c r="N105" t="n">
-        <v>3.8275</v>
+        <v>4.3214</v>
       </c>
       <c r="O105" t="n">
-        <v>3.2946</v>
+        <v>3.5651</v>
       </c>
       <c r="P105" t="n">
-        <v>51.47</v>
+        <v>51.87</v>
       </c>
       <c r="Q105" t="n">
-        <v>48.53</v>
+        <v>48.13</v>
       </c>
       <c r="R105" t="n">
-        <v>2.95</v>
+        <v>3.74</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>203</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.4579</v>
+      </c>
+      <c r="E106" t="n">
+        <v>45.73433896290638</v>
+      </c>
+      <c r="F106" t="n">
+        <v>41.81528399596738</v>
+      </c>
+      <c r="G106" t="n">
+        <v>2.66985670954591</v>
+      </c>
+      <c r="H106" t="n">
+        <v>482</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.4579</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="L106" t="n">
+        <v>4.5084</v>
+      </c>
+      <c r="M106" t="n">
+        <v>4.1001</v>
+      </c>
+      <c r="N106" t="n">
+        <v>4.3214</v>
+      </c>
+      <c r="O106" t="n">
+        <v>3.5651</v>
+      </c>
+      <c r="P106" t="n">
+        <v>51.87</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>48.13</v>
+      </c>
+      <c r="R106" t="n">
+        <v>3.74</v>
       </c>
     </row>
   </sheetData>
@@ -11217,7 +11319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14983,36 +15085,72 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D105" t="n">
-        <v>42.53</v>
+        <v>42.51</v>
       </c>
       <c r="E105" t="n">
-        <v>54.3</v>
+        <v>54.33</v>
       </c>
       <c r="F105" t="n">
-        <v>-11.76</v>
+        <v>-11.82</v>
       </c>
       <c r="G105" t="n">
         <v>30</v>
       </c>
       <c r="H105" t="n">
-        <v>-5.47</v>
+        <v>-5.48</v>
       </c>
       <c r="I105" t="n">
-        <v>5.47</v>
+        <v>5.48</v>
       </c>
       <c r="J105" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>203</v>
+      </c>
+      <c r="D106" t="n">
+        <v>42.51</v>
+      </c>
+      <c r="E106" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="F106" t="n">
+        <v>-11.82</v>
+      </c>
+      <c r="G106" t="n">
+        <v>30</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-5.48</v>
+      </c>
+      <c r="I106" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="J106" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4863,43 +4863,211 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D106" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E106" t="n">
-        <v>3.74</v>
+        <v>3.51</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1327</v>
+        <v>0.134</v>
       </c>
       <c r="G106" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="H106" t="n">
-        <v>31.1</v>
+        <v>28.8</v>
       </c>
       <c r="I106" t="n">
-        <v>231.3</v>
+        <v>231</v>
       </c>
       <c r="J106" t="n">
-        <v>54.6</v>
+        <v>55.2</v>
       </c>
       <c r="K106" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="L106" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>201</v>
+      </c>
+      <c r="D107" t="n">
+        <v>201</v>
+      </c>
+      <c r="E107" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.1353</v>
+      </c>
+      <c r="G107" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H107" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I107" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="J107" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="K107" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L107" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>200</v>
+      </c>
+      <c r="D108" t="n">
+        <v>200</v>
+      </c>
+      <c r="E108" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.1367</v>
+      </c>
+      <c r="G108" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="H108" t="n">
+        <v>28</v>
+      </c>
+      <c r="I108" t="n">
+        <v>229.7</v>
+      </c>
+      <c r="J108" t="n">
+        <v>54</v>
+      </c>
+      <c r="K108" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L108" t="n">
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>199</v>
+      </c>
+      <c r="D109" t="n">
+        <v>199</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="G109" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H109" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I109" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="J109" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="K109" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L109" t="n">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>199</v>
+      </c>
+      <c r="D110" t="n">
+        <v>199</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.1381</v>
+      </c>
+      <c r="G110" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H110" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="I110" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="J110" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="K110" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L110" t="n">
+        <v>35.4</v>
       </c>
     </row>
   </sheetData>
@@ -4913,7 +5081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R106"/>
+  <dimension ref="A1:R110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11251,61 +11419,301 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D106" t="n">
-        <v>0.4579</v>
+        <v>0.4587</v>
       </c>
       <c r="E106" t="n">
-        <v>45.73433896290638</v>
+        <v>45.67583791674215</v>
       </c>
       <c r="F106" t="n">
-        <v>41.81528399596738</v>
+        <v>41.80611540000019</v>
       </c>
       <c r="G106" t="n">
-        <v>2.66985670954591</v>
+        <v>2.607256410243362</v>
       </c>
       <c r="H106" t="n">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="I106" t="n">
-        <v>0.4579</v>
+        <v>0.4587</v>
       </c>
       <c r="J106" t="n">
-        <v>0.2482</v>
+        <v>0.2483</v>
       </c>
       <c r="K106" t="n">
-        <v>0.2939</v>
+        <v>0.293</v>
       </c>
       <c r="L106" t="n">
-        <v>4.5084</v>
+        <v>4.194</v>
       </c>
       <c r="M106" t="n">
-        <v>4.1001</v>
+        <v>3.9489</v>
       </c>
       <c r="N106" t="n">
-        <v>4.3214</v>
+        <v>4.0816</v>
       </c>
       <c r="O106" t="n">
-        <v>3.5651</v>
+        <v>3.4052</v>
       </c>
       <c r="P106" t="n">
-        <v>51.87</v>
+        <v>51.75</v>
       </c>
       <c r="Q106" t="n">
-        <v>48.13</v>
+        <v>48.25</v>
       </c>
       <c r="R106" t="n">
-        <v>3.74</v>
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>201</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="E107" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F107" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G107" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H107" t="n">
+        <v>465</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.2921</v>
+      </c>
+      <c r="L107" t="n">
+        <v>4.194</v>
+      </c>
+      <c r="M107" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N107" t="n">
+        <v>4.0814</v>
+      </c>
+      <c r="O107" t="n">
+        <v>3.4039</v>
+      </c>
+      <c r="P107" t="n">
+        <v>51.73</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>48.27</v>
+      </c>
+      <c r="R107" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>200</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.4604</v>
+      </c>
+      <c r="E108" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F108" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G108" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H108" t="n">
+        <v>465</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.4604</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="L108" t="n">
+        <v>4.194</v>
+      </c>
+      <c r="M108" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N108" t="n">
+        <v>4.0812</v>
+      </c>
+      <c r="O108" t="n">
+        <v>3.4025</v>
+      </c>
+      <c r="P108" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="R108" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>199</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="E109" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F109" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G109" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H109" t="n">
+        <v>465</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.2485</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="L109" t="n">
+        <v>4.194</v>
+      </c>
+      <c r="M109" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N109" t="n">
+        <v>4.081</v>
+      </c>
+      <c r="O109" t="n">
+        <v>3.4012</v>
+      </c>
+      <c r="P109" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="R109" t="n">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>199</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="E110" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F110" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G110" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H110" t="n">
+        <v>465</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.4613</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.2485</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="L110" t="n">
+        <v>4.194</v>
+      </c>
+      <c r="M110" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N110" t="n">
+        <v>4.081</v>
+      </c>
+      <c r="O110" t="n">
+        <v>3.4012</v>
+      </c>
+      <c r="P110" t="n">
+        <v>51.79</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="R110" t="n">
+        <v>3.58</v>
       </c>
     </row>
   </sheetData>
@@ -11319,7 +11727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15121,36 +15529,180 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D106" t="n">
-        <v>42.51</v>
+        <v>42.77</v>
       </c>
       <c r="E106" t="n">
-        <v>54.33</v>
+        <v>54.11</v>
       </c>
       <c r="F106" t="n">
-        <v>-11.82</v>
+        <v>-11.34</v>
       </c>
       <c r="G106" t="n">
         <v>30</v>
       </c>
       <c r="H106" t="n">
-        <v>-5.48</v>
+        <v>-5.42</v>
       </c>
       <c r="I106" t="n">
-        <v>5.48</v>
+        <v>5.42</v>
       </c>
       <c r="J106" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>201</v>
+      </c>
+      <c r="D107" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E107" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F107" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G107" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I107" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>200</v>
+      </c>
+      <c r="D108" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E108" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F108" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G108" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I108" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>199</v>
+      </c>
+      <c r="D109" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E109" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F109" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G109" t="n">
+        <v>30</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I109" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>199</v>
+      </c>
+      <c r="D110" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E110" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F110" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G110" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I110" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J110" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5031,43 +5031,85 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D110" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E110" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="F110" t="n">
-        <v>0.1381</v>
+        <v>0.1394</v>
       </c>
       <c r="G110" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="H110" t="n">
-        <v>29.6</v>
+        <v>35.8</v>
       </c>
       <c r="I110" t="n">
-        <v>231.2</v>
+        <v>230.1</v>
       </c>
       <c r="J110" t="n">
-        <v>55.7</v>
+        <v>55.4</v>
       </c>
       <c r="K110" t="n">
         <v>22.4</v>
       </c>
       <c r="L110" t="n">
-        <v>35.4</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>198</v>
+      </c>
+      <c r="D111" t="n">
+        <v>198</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.1394</v>
+      </c>
+      <c r="G111" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H111" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="I111" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="J111" t="n">
+        <v>55.4</v>
+      </c>
+      <c r="K111" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L111" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -5081,7 +5123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R110"/>
+  <dimension ref="A1:R111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11659,61 +11701,121 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D110" t="n">
-        <v>0.4613</v>
+        <v>0.4621</v>
       </c>
       <c r="E110" t="n">
-        <v>45.67583791674215</v>
+        <v>45.73978949204303</v>
       </c>
       <c r="F110" t="n">
-        <v>41.80611540000019</v>
+        <v>41.81965567570384</v>
       </c>
       <c r="G110" t="n">
-        <v>2.607256410243362</v>
+        <v>2.692972869420909</v>
       </c>
       <c r="H110" t="n">
-        <v>465</v>
+        <v>484</v>
       </c>
       <c r="I110" t="n">
-        <v>0.4613</v>
+        <v>0.4621</v>
       </c>
       <c r="J110" t="n">
-        <v>0.2485</v>
+        <v>0.2486</v>
       </c>
       <c r="K110" t="n">
-        <v>0.2902</v>
+        <v>0.2893</v>
       </c>
       <c r="L110" t="n">
         <v>4.194</v>
       </c>
       <c r="M110" t="n">
-        <v>3.9489</v>
+        <v>4.1162</v>
       </c>
       <c r="N110" t="n">
-        <v>4.081</v>
+        <v>4.158</v>
       </c>
       <c r="O110" t="n">
-        <v>3.4012</v>
+        <v>3.481</v>
       </c>
       <c r="P110" t="n">
-        <v>51.79</v>
+        <v>51.71</v>
       </c>
       <c r="Q110" t="n">
-        <v>48.21</v>
+        <v>48.29</v>
       </c>
       <c r="R110" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>198</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="E111" t="n">
+        <v>45.73978949204303</v>
+      </c>
+      <c r="F111" t="n">
+        <v>41.81965567570384</v>
+      </c>
+      <c r="G111" t="n">
+        <v>2.692972869420909</v>
+      </c>
+      <c r="H111" t="n">
+        <v>484</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.2486</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.2893</v>
+      </c>
+      <c r="L111" t="n">
+        <v>4.194</v>
+      </c>
+      <c r="M111" t="n">
+        <v>4.1162</v>
+      </c>
+      <c r="N111" t="n">
+        <v>4.158</v>
+      </c>
+      <c r="O111" t="n">
+        <v>3.481</v>
+      </c>
+      <c r="P111" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="R111" t="n">
+        <v>3.42</v>
       </c>
     </row>
   </sheetData>
@@ -11727,7 +11829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J110"/>
+  <dimension ref="A1:J111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15673,36 +15775,72 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D110" t="n">
-        <v>42.77</v>
+        <v>42.49</v>
       </c>
       <c r="E110" t="n">
-        <v>54.11</v>
+        <v>54.34</v>
       </c>
       <c r="F110" t="n">
-        <v>-11.34</v>
+        <v>-11.85</v>
       </c>
       <c r="G110" t="n">
         <v>30</v>
       </c>
       <c r="H110" t="n">
-        <v>-5.42</v>
+        <v>-5.48</v>
       </c>
       <c r="I110" t="n">
-        <v>5.42</v>
+        <v>5.48</v>
       </c>
       <c r="J110" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>198</v>
+      </c>
+      <c r="D111" t="n">
+        <v>42.49</v>
+      </c>
+      <c r="E111" t="n">
+        <v>54.34</v>
+      </c>
+      <c r="F111" t="n">
+        <v>-11.85</v>
+      </c>
+      <c r="G111" t="n">
+        <v>30</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-5.48</v>
+      </c>
+      <c r="I111" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="J111" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5073,43 +5073,127 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D111" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E111" t="n">
-        <v>3.42</v>
+        <v>3.21</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1394</v>
+        <v>0.1408</v>
       </c>
       <c r="G111" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="H111" t="n">
-        <v>35.8</v>
+        <v>32.3</v>
       </c>
       <c r="I111" t="n">
-        <v>230.1</v>
+        <v>229.6</v>
       </c>
       <c r="J111" t="n">
-        <v>55.4</v>
+        <v>56</v>
       </c>
       <c r="K111" t="n">
         <v>22.4</v>
       </c>
       <c r="L111" t="n">
-        <v>36</v>
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>196</v>
+      </c>
+      <c r="D112" t="n">
+        <v>196</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="G112" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H112" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="I112" t="n">
+        <v>229.9</v>
+      </c>
+      <c r="J112" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="K112" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L112" t="n">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>196</v>
+      </c>
+      <c r="D113" t="n">
+        <v>196</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.1422</v>
+      </c>
+      <c r="G113" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H113" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="I113" t="n">
+        <v>229.9</v>
+      </c>
+      <c r="J113" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="K113" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L113" t="n">
+        <v>36.5</v>
       </c>
     </row>
   </sheetData>
@@ -5123,7 +5207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R111"/>
+  <dimension ref="A1:R113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11761,61 +11845,181 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D111" t="n">
-        <v>0.4621</v>
+        <v>0.463</v>
       </c>
       <c r="E111" t="n">
-        <v>45.73978949204303</v>
+        <v>45.67583791674215</v>
       </c>
       <c r="F111" t="n">
-        <v>41.81965567570384</v>
+        <v>41.80611540000019</v>
       </c>
       <c r="G111" t="n">
-        <v>2.692972869420909</v>
+        <v>2.607256410243362</v>
       </c>
       <c r="H111" t="n">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="I111" t="n">
-        <v>0.4621</v>
+        <v>0.463</v>
       </c>
       <c r="J111" t="n">
         <v>0.2486</v>
       </c>
       <c r="K111" t="n">
-        <v>0.2893</v>
+        <v>0.2884</v>
       </c>
       <c r="L111" t="n">
-        <v>4.194</v>
+        <v>3.8711</v>
       </c>
       <c r="M111" t="n">
-        <v>4.1162</v>
+        <v>3.9489</v>
       </c>
       <c r="N111" t="n">
-        <v>4.158</v>
+        <v>3.9071</v>
       </c>
       <c r="O111" t="n">
-        <v>3.481</v>
+        <v>3.3053</v>
       </c>
       <c r="P111" t="n">
-        <v>51.71</v>
+        <v>51.6</v>
       </c>
       <c r="Q111" t="n">
-        <v>48.29</v>
+        <v>48.4</v>
       </c>
       <c r="R111" t="n">
-        <v>3.42</v>
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>196</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="E112" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F112" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H112" t="n">
+        <v>465</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="L112" t="n">
+        <v>3.8711</v>
+      </c>
+      <c r="M112" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N112" t="n">
+        <v>3.9072</v>
+      </c>
+      <c r="O112" t="n">
+        <v>3.3042</v>
+      </c>
+      <c r="P112" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="R112" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>196</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="E113" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F113" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G113" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H113" t="n">
+        <v>465</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.2487</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="L113" t="n">
+        <v>3.8711</v>
+      </c>
+      <c r="M113" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N113" t="n">
+        <v>3.9072</v>
+      </c>
+      <c r="O113" t="n">
+        <v>3.3042</v>
+      </c>
+      <c r="P113" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="R113" t="n">
+        <v>3.19</v>
       </c>
     </row>
   </sheetData>
@@ -11829,7 +12033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15811,36 +16015,108 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D111" t="n">
-        <v>42.49</v>
+        <v>42.77</v>
       </c>
       <c r="E111" t="n">
-        <v>54.34</v>
+        <v>54.11</v>
       </c>
       <c r="F111" t="n">
-        <v>-11.85</v>
+        <v>-11.34</v>
       </c>
       <c r="G111" t="n">
         <v>30</v>
       </c>
       <c r="H111" t="n">
-        <v>-5.48</v>
+        <v>-5.42</v>
       </c>
       <c r="I111" t="n">
-        <v>5.48</v>
+        <v>5.42</v>
       </c>
       <c r="J111" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>196</v>
+      </c>
+      <c r="D112" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E112" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F112" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G112" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I112" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>196</v>
+      </c>
+      <c r="D113" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E113" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F113" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G113" t="n">
+        <v>30</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I113" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J113" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L113"/>
+  <dimension ref="A1:L123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5157,43 +5157,463 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D113" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E113" t="n">
-        <v>3.19</v>
+        <v>3.29</v>
       </c>
       <c r="F113" t="n">
-        <v>0.1422</v>
+        <v>0.1437</v>
       </c>
       <c r="G113" t="n">
         <v>48.4</v>
       </c>
       <c r="H113" t="n">
-        <v>32.2</v>
+        <v>31.5</v>
       </c>
       <c r="I113" t="n">
-        <v>229.9</v>
+        <v>232.6</v>
       </c>
       <c r="J113" t="n">
-        <v>56.1</v>
+        <v>58.7</v>
       </c>
       <c r="K113" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L113" t="n">
+        <v>35.9</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>194</v>
+      </c>
+      <c r="D114" t="n">
+        <v>194</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.1451</v>
+      </c>
+      <c r="G114" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H114" t="n">
+        <v>33</v>
+      </c>
+      <c r="I114" t="n">
+        <v>231.6</v>
+      </c>
+      <c r="J114" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="K114" t="n">
         <v>22.4</v>
       </c>
-      <c r="L113" t="n">
-        <v>36.5</v>
+      <c r="L114" t="n">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>193</v>
+      </c>
+      <c r="D115" t="n">
+        <v>193</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="G115" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H115" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="I115" t="n">
+        <v>233.4</v>
+      </c>
+      <c r="J115" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="K115" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="L115" t="n">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>192</v>
+      </c>
+      <c r="D116" t="n">
+        <v>192</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="G116" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H116" t="n">
+        <v>32.6</v>
+      </c>
+      <c r="I116" t="n">
+        <v>232.6</v>
+      </c>
+      <c r="J116" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="K116" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="L116" t="n">
+        <v>35.1</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>191</v>
+      </c>
+      <c r="D117" t="n">
+        <v>191</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.1495</v>
+      </c>
+      <c r="G117" t="n">
+        <v>48.3</v>
+      </c>
+      <c r="H117" t="n">
+        <v>32</v>
+      </c>
+      <c r="I117" t="n">
+        <v>230.9</v>
+      </c>
+      <c r="J117" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="K117" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="L117" t="n">
+        <v>34.8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>190</v>
+      </c>
+      <c r="D118" t="n">
+        <v>190</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="G118" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H118" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I118" t="n">
+        <v>231.4</v>
+      </c>
+      <c r="J118" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="K118" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L118" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>189</v>
+      </c>
+      <c r="D119" t="n">
+        <v>189</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="G119" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="H119" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="I119" t="n">
+        <v>233.8</v>
+      </c>
+      <c r="J119" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="K119" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L119" t="n">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>188</v>
+      </c>
+      <c r="D120" t="n">
+        <v>188</v>
+      </c>
+      <c r="E120" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="G120" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H120" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="I120" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="J120" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="K120" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L120" t="n">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>187</v>
+      </c>
+      <c r="D121" t="n">
+        <v>187</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.1556</v>
+      </c>
+      <c r="G121" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H121" t="n">
+        <v>31.7</v>
+      </c>
+      <c r="I121" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="J121" t="n">
+        <v>59.4</v>
+      </c>
+      <c r="K121" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="L121" t="n">
+        <v>36.7</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>186</v>
+      </c>
+      <c r="D122" t="n">
+        <v>186</v>
+      </c>
+      <c r="E122" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="G122" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H122" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I122" t="n">
+        <v>234.4</v>
+      </c>
+      <c r="J122" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="K122" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L122" t="n">
+        <v>35.4</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>186</v>
+      </c>
+      <c r="D123" t="n">
+        <v>186</v>
+      </c>
+      <c r="E123" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.1571</v>
+      </c>
+      <c r="G123" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H123" t="n">
+        <v>34.6</v>
+      </c>
+      <c r="I123" t="n">
+        <v>234.4</v>
+      </c>
+      <c r="J123" t="n">
+        <v>59.6</v>
+      </c>
+      <c r="K123" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L123" t="n">
+        <v>35.4</v>
       </c>
     </row>
   </sheetData>
@@ -5207,7 +5627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R113"/>
+  <dimension ref="A1:R123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11965,19 +12385,19 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D113" t="n">
-        <v>0.4639</v>
+        <v>0.4648</v>
       </c>
       <c r="E113" t="n">
         <v>45.67583791674215</v>
@@ -11992,34 +12412,634 @@
         <v>465</v>
       </c>
       <c r="I113" t="n">
-        <v>0.4639</v>
+        <v>0.4648</v>
       </c>
       <c r="J113" t="n">
-        <v>0.2487</v>
+        <v>0.2488</v>
       </c>
       <c r="K113" t="n">
-        <v>0.2874</v>
+        <v>0.2865</v>
       </c>
       <c r="L113" t="n">
-        <v>3.8711</v>
+        <v>3.6221</v>
       </c>
       <c r="M113" t="n">
         <v>3.9489</v>
       </c>
       <c r="N113" t="n">
-        <v>3.9072</v>
+        <v>3.774</v>
       </c>
       <c r="O113" t="n">
-        <v>3.3042</v>
+        <v>3.2317</v>
       </c>
       <c r="P113" t="n">
-        <v>51.6</v>
+        <v>51.64</v>
       </c>
       <c r="Q113" t="n">
-        <v>48.4</v>
+        <v>48.36</v>
       </c>
       <c r="R113" t="n">
-        <v>3.19</v>
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>194</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="E114" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F114" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G114" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H114" t="n">
+        <v>465</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.4657</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.2488</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.2855</v>
+      </c>
+      <c r="L114" t="n">
+        <v>3.9568</v>
+      </c>
+      <c r="M114" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N114" t="n">
+        <v>3.9531</v>
+      </c>
+      <c r="O114" t="n">
+        <v>3.3264</v>
+      </c>
+      <c r="P114" t="n">
+        <v>51.57</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="R114" t="n">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>193</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="E115" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F115" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G115" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H115" t="n">
+        <v>465</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="L115" t="n">
+        <v>4.0542</v>
+      </c>
+      <c r="M115" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N115" t="n">
+        <v>4.0051</v>
+      </c>
+      <c r="O115" t="n">
+        <v>3.3529</v>
+      </c>
+      <c r="P115" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="R115" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>192</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="E116" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F116" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G116" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H116" t="n">
+        <v>465</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.2835</v>
+      </c>
+      <c r="L116" t="n">
+        <v>4.0542</v>
+      </c>
+      <c r="M116" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N116" t="n">
+        <v>4.005</v>
+      </c>
+      <c r="O116" t="n">
+        <v>3.3515</v>
+      </c>
+      <c r="P116" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="R116" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>191</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="E117" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F117" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G117" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H117" t="n">
+        <v>465</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.249</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.2826</v>
+      </c>
+      <c r="L117" t="n">
+        <v>4.0542</v>
+      </c>
+      <c r="M117" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N117" t="n">
+        <v>4.0049</v>
+      </c>
+      <c r="O117" t="n">
+        <v>3.3502</v>
+      </c>
+      <c r="P117" t="n">
+        <v>51.51</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="R117" t="n">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>190</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="E118" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F118" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G118" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H118" t="n">
+        <v>465</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.4694</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.2816</v>
+      </c>
+      <c r="L118" t="n">
+        <v>4.2649</v>
+      </c>
+      <c r="M118" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N118" t="n">
+        <v>4.1166</v>
+      </c>
+      <c r="O118" t="n">
+        <v>3.4082</v>
+      </c>
+      <c r="P118" t="n">
+        <v>51.53</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>48.47</v>
+      </c>
+      <c r="R118" t="n">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>189</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="E119" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F119" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H119" t="n">
+        <v>465</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.2491</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.2806</v>
+      </c>
+      <c r="L119" t="n">
+        <v>4.3999</v>
+      </c>
+      <c r="M119" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N119" t="n">
+        <v>4.1878</v>
+      </c>
+      <c r="O119" t="n">
+        <v>3.4445</v>
+      </c>
+      <c r="P119" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>48.26</v>
+      </c>
+      <c r="R119" t="n">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>188</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="E120" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F120" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G120" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H120" t="n">
+        <v>465</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="L120" t="n">
+        <v>4.4113</v>
+      </c>
+      <c r="M120" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N120" t="n">
+        <v>4.1934</v>
+      </c>
+      <c r="O120" t="n">
+        <v>3.4459</v>
+      </c>
+      <c r="P120" t="n">
+        <v>51.76</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="R120" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>187</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.4722</v>
+      </c>
+      <c r="E121" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F121" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G121" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H121" t="n">
+        <v>465</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.4722</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.2492</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="L121" t="n">
+        <v>4.3631</v>
+      </c>
+      <c r="M121" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N121" t="n">
+        <v>4.1675</v>
+      </c>
+      <c r="O121" t="n">
+        <v>3.4307</v>
+      </c>
+      <c r="P121" t="n">
+        <v>51.76</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>48.24</v>
+      </c>
+      <c r="R121" t="n">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>186</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="E122" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F122" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G122" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H122" t="n">
+        <v>465</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.2493</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="L122" t="n">
+        <v>4.3631</v>
+      </c>
+      <c r="M122" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N122" t="n">
+        <v>4.1671</v>
+      </c>
+      <c r="O122" t="n">
+        <v>3.429</v>
+      </c>
+      <c r="P122" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="R122" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>186</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="E123" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F123" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G123" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H123" t="n">
+        <v>465</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.4732</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.2493</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="L123" t="n">
+        <v>4.3631</v>
+      </c>
+      <c r="M123" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N123" t="n">
+        <v>4.1671</v>
+      </c>
+      <c r="O123" t="n">
+        <v>3.429</v>
+      </c>
+      <c r="P123" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="R123" t="n">
+        <v>3.69</v>
       </c>
     </row>
   </sheetData>
@@ -12033,7 +13053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J113"/>
+  <dimension ref="A1:J123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16087,16 +17107,16 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D113" t="n">
         <v>42.77</v>
@@ -16117,6 +17137,366 @@
         <v>5.42</v>
       </c>
       <c r="J113" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>194</v>
+      </c>
+      <c r="D114" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E114" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F114" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G114" t="n">
+        <v>30</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I114" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>193</v>
+      </c>
+      <c r="D115" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E115" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F115" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G115" t="n">
+        <v>30</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I115" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>192</v>
+      </c>
+      <c r="D116" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E116" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F116" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G116" t="n">
+        <v>30</v>
+      </c>
+      <c r="H116" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I116" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>191</v>
+      </c>
+      <c r="D117" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E117" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F117" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G117" t="n">
+        <v>30</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I117" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>190</v>
+      </c>
+      <c r="D118" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E118" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F118" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G118" t="n">
+        <v>30</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I118" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>189</v>
+      </c>
+      <c r="D119" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E119" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F119" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G119" t="n">
+        <v>30</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I119" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>188</v>
+      </c>
+      <c r="D120" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E120" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F120" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G120" t="n">
+        <v>30</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I120" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>187</v>
+      </c>
+      <c r="D121" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E121" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F121" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G121" t="n">
+        <v>30</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I121" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>186</v>
+      </c>
+      <c r="D122" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E122" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F122" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G122" t="n">
+        <v>30</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I122" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>186</v>
+      </c>
+      <c r="D123" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E123" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F123" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G123" t="n">
+        <v>30</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J123" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5577,43 +5577,127 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D123" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E123" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="F123" t="n">
-        <v>0.1571</v>
+        <v>0.1587</v>
       </c>
       <c r="G123" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="H123" t="n">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="I123" t="n">
-        <v>234.4</v>
+        <v>234.6</v>
       </c>
       <c r="J123" t="n">
-        <v>59.6</v>
+        <v>59</v>
       </c>
       <c r="K123" t="n">
         <v>22.7</v>
       </c>
       <c r="L123" t="n">
-        <v>35.4</v>
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>184</v>
+      </c>
+      <c r="D124" t="n">
+        <v>184</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="G124" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H124" t="n">
+        <v>34</v>
+      </c>
+      <c r="I124" t="n">
+        <v>233.2</v>
+      </c>
+      <c r="J124" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="K124" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L124" t="n">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>184</v>
+      </c>
+      <c r="D125" t="n">
+        <v>184</v>
+      </c>
+      <c r="E125" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.1603</v>
+      </c>
+      <c r="G125" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H125" t="n">
+        <v>34</v>
+      </c>
+      <c r="I125" t="n">
+        <v>233.2</v>
+      </c>
+      <c r="J125" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="K125" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L125" t="n">
+        <v>36.9</v>
       </c>
     </row>
   </sheetData>
@@ -5627,7 +5711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R123"/>
+  <dimension ref="A1:R125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12985,19 +13069,19 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D123" t="n">
-        <v>0.4732</v>
+        <v>0.4742</v>
       </c>
       <c r="E123" t="n">
         <v>45.67583791674215</v>
@@ -13012,34 +13096,154 @@
         <v>465</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4732</v>
+        <v>0.4742</v>
       </c>
       <c r="J123" t="n">
         <v>0.2493</v>
       </c>
       <c r="K123" t="n">
-        <v>0.2775</v>
+        <v>0.2765</v>
       </c>
       <c r="L123" t="n">
-        <v>4.3631</v>
+        <v>4.3472</v>
       </c>
       <c r="M123" t="n">
         <v>3.9489</v>
       </c>
       <c r="N123" t="n">
-        <v>4.1671</v>
+        <v>4.1583</v>
       </c>
       <c r="O123" t="n">
-        <v>3.429</v>
+        <v>3.4228</v>
       </c>
       <c r="P123" t="n">
-        <v>51.84</v>
+        <v>51.86</v>
       </c>
       <c r="Q123" t="n">
-        <v>48.16</v>
+        <v>48.14</v>
       </c>
       <c r="R123" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>184</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="E124" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F124" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G124" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H124" t="n">
+        <v>465</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="L124" t="n">
+        <v>4.3472</v>
+      </c>
+      <c r="M124" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N124" t="n">
+        <v>4.1579</v>
+      </c>
+      <c r="O124" t="n">
+        <v>3.4211</v>
+      </c>
+      <c r="P124" t="n">
+        <v>51.72</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="R124" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>184</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="E125" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F125" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G125" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H125" t="n">
+        <v>465</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.4752</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="L125" t="n">
+        <v>4.3472</v>
+      </c>
+      <c r="M125" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N125" t="n">
+        <v>4.1579</v>
+      </c>
+      <c r="O125" t="n">
+        <v>3.4211</v>
+      </c>
+      <c r="P125" t="n">
+        <v>51.72</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="R125" t="n">
+        <v>3.44</v>
       </c>
     </row>
   </sheetData>
@@ -13053,7 +13257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J123"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17467,16 +17671,16 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D123" t="n">
         <v>42.77</v>
@@ -17497,6 +17701,78 @@
         <v>5.42</v>
       </c>
       <c r="J123" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>184</v>
+      </c>
+      <c r="D124" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E124" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F124" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G124" t="n">
+        <v>30</v>
+      </c>
+      <c r="H124" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I124" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>184</v>
+      </c>
+      <c r="D125" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E125" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F125" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G125" t="n">
+        <v>30</v>
+      </c>
+      <c r="H125" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I125" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J125" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L125"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5661,43 +5661,85 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D125" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E125" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
       </c>
       <c r="F125" t="n">
-        <v>0.1603</v>
+        <v>0.1619</v>
       </c>
       <c r="G125" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="H125" t="n">
-        <v>34</v>
+        <v>37.9</v>
       </c>
       <c r="I125" t="n">
-        <v>233.2</v>
+        <v>233.6</v>
       </c>
       <c r="J125" t="n">
-        <v>60.4</v>
+        <v>57.4</v>
       </c>
       <c r="K125" t="n">
-        <v>22.7</v>
+        <v>23</v>
       </c>
       <c r="L125" t="n">
-        <v>36.9</v>
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>183</v>
+      </c>
+      <c r="D126" t="n">
+        <v>183</v>
+      </c>
+      <c r="E126" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.1619</v>
+      </c>
+      <c r="G126" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H126" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="I126" t="n">
+        <v>233.6</v>
+      </c>
+      <c r="J126" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="K126" t="n">
+        <v>23</v>
+      </c>
+      <c r="L126" t="n">
+        <v>37.8</v>
       </c>
     </row>
   </sheetData>
@@ -5711,7 +5753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R125"/>
+  <dimension ref="A1:R126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13189,61 +13231,121 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D125" t="n">
-        <v>0.4752</v>
+        <v>0.4762</v>
       </c>
       <c r="E125" t="n">
-        <v>45.67583791674215</v>
+        <v>45.90701584403696</v>
       </c>
       <c r="F125" t="n">
-        <v>41.80611540000019</v>
+        <v>41.76531884857454</v>
       </c>
       <c r="G125" t="n">
-        <v>2.607256410243362</v>
+        <v>2.914983911301792</v>
       </c>
       <c r="H125" t="n">
-        <v>465</v>
+        <v>526</v>
       </c>
       <c r="I125" t="n">
-        <v>0.4752</v>
+        <v>0.4762</v>
       </c>
       <c r="J125" t="n">
         <v>0.2494</v>
       </c>
       <c r="K125" t="n">
-        <v>0.2754</v>
+        <v>0.2744</v>
       </c>
       <c r="L125" t="n">
         <v>4.3472</v>
       </c>
       <c r="M125" t="n">
-        <v>3.9489</v>
+        <v>4.3445</v>
       </c>
       <c r="N125" t="n">
-        <v>4.1579</v>
+        <v>4.3459</v>
       </c>
       <c r="O125" t="n">
-        <v>3.4211</v>
+        <v>3.6645</v>
       </c>
       <c r="P125" t="n">
-        <v>51.72</v>
+        <v>51.8</v>
       </c>
       <c r="Q125" t="n">
-        <v>48.28</v>
+        <v>48.2</v>
       </c>
       <c r="R125" t="n">
-        <v>3.44</v>
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>183</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="E126" t="n">
+        <v>45.90701584403696</v>
+      </c>
+      <c r="F126" t="n">
+        <v>41.76531884857454</v>
+      </c>
+      <c r="G126" t="n">
+        <v>2.914983911301792</v>
+      </c>
+      <c r="H126" t="n">
+        <v>526</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.4762</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="L126" t="n">
+        <v>4.3472</v>
+      </c>
+      <c r="M126" t="n">
+        <v>4.3445</v>
+      </c>
+      <c r="N126" t="n">
+        <v>4.3459</v>
+      </c>
+      <c r="O126" t="n">
+        <v>3.6645</v>
+      </c>
+      <c r="P126" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="R126" t="n">
+        <v>3.59</v>
       </c>
     </row>
   </sheetData>
@@ -13257,7 +13359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J125"/>
+  <dimension ref="A1:J126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17743,36 +17845,72 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D125" t="n">
-        <v>42.77</v>
+        <v>42.04</v>
       </c>
       <c r="E125" t="n">
-        <v>54.11</v>
+        <v>54.92</v>
       </c>
       <c r="F125" t="n">
-        <v>-11.34</v>
+        <v>-12.87</v>
       </c>
       <c r="G125" t="n">
         <v>30</v>
       </c>
       <c r="H125" t="n">
-        <v>-5.42</v>
+        <v>-5.58</v>
       </c>
       <c r="I125" t="n">
-        <v>5.42</v>
+        <v>5.58</v>
       </c>
       <c r="J125" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>183</v>
+      </c>
+      <c r="D126" t="n">
+        <v>42.04</v>
+      </c>
+      <c r="E126" t="n">
+        <v>54.92</v>
+      </c>
+      <c r="F126" t="n">
+        <v>-12.87</v>
+      </c>
+      <c r="G126" t="n">
+        <v>30</v>
+      </c>
+      <c r="H126" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="I126" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="J126" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L126"/>
+  <dimension ref="A1:L127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5703,43 +5703,85 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D126" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E126" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
       </c>
       <c r="F126" t="n">
-        <v>0.1619</v>
+        <v>0.1635</v>
       </c>
       <c r="G126" t="n">
-        <v>48.9</v>
+        <v>48.7</v>
       </c>
       <c r="H126" t="n">
-        <v>37.9</v>
+        <v>34.5</v>
       </c>
       <c r="I126" t="n">
-        <v>233.6</v>
+        <v>232.8</v>
       </c>
       <c r="J126" t="n">
-        <v>57.4</v>
+        <v>56.8</v>
       </c>
       <c r="K126" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L126" t="n">
-        <v>37.8</v>
+        <v>36.6</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>182</v>
+      </c>
+      <c r="D127" t="n">
+        <v>182</v>
+      </c>
+      <c r="E127" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="G127" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="H127" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="I127" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="J127" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="K127" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L127" t="n">
+        <v>36.6</v>
       </c>
     </row>
   </sheetData>
@@ -5753,7 +5795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R126"/>
+  <dimension ref="A1:R127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13291,61 +13333,121 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D126" t="n">
-        <v>0.4762</v>
+        <v>0.4772</v>
       </c>
       <c r="E126" t="n">
-        <v>45.90701584403696</v>
+        <v>45.86781913136987</v>
       </c>
       <c r="F126" t="n">
-        <v>41.76531884857454</v>
+        <v>41.74017049578097</v>
       </c>
       <c r="G126" t="n">
-        <v>2.914983911301792</v>
+        <v>2.893167007267448</v>
       </c>
       <c r="H126" t="n">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="I126" t="n">
-        <v>0.4762</v>
+        <v>0.4772</v>
       </c>
       <c r="J126" t="n">
-        <v>0.2494</v>
+        <v>0.2495</v>
       </c>
       <c r="K126" t="n">
-        <v>0.2744</v>
+        <v>0.2733</v>
       </c>
       <c r="L126" t="n">
-        <v>4.3472</v>
+        <v>4.4605</v>
       </c>
       <c r="M126" t="n">
-        <v>4.3445</v>
+        <v>4.3577</v>
       </c>
       <c r="N126" t="n">
-        <v>4.3459</v>
+        <v>4.4114</v>
       </c>
       <c r="O126" t="n">
-        <v>3.6645</v>
+        <v>3.6869</v>
       </c>
       <c r="P126" t="n">
-        <v>51.8</v>
+        <v>51.83</v>
       </c>
       <c r="Q126" t="n">
-        <v>48.2</v>
+        <v>48.17</v>
       </c>
       <c r="R126" t="n">
-        <v>3.59</v>
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>182</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.4772</v>
+      </c>
+      <c r="E127" t="n">
+        <v>45.86781913136987</v>
+      </c>
+      <c r="F127" t="n">
+        <v>41.74017049578097</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2.893167007267448</v>
+      </c>
+      <c r="H127" t="n">
+        <v>529</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.4772</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.2495</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="L127" t="n">
+        <v>4.4605</v>
+      </c>
+      <c r="M127" t="n">
+        <v>4.3577</v>
+      </c>
+      <c r="N127" t="n">
+        <v>4.4114</v>
+      </c>
+      <c r="O127" t="n">
+        <v>3.6869</v>
+      </c>
+      <c r="P127" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="R127" t="n">
+        <v>3.65</v>
       </c>
     </row>
   </sheetData>
@@ -13359,7 +13461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J126"/>
+  <dimension ref="A1:J127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17881,25 +17983,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D126" t="n">
-        <v>42.04</v>
+        <v>42.02</v>
       </c>
       <c r="E126" t="n">
-        <v>54.92</v>
+        <v>54.94</v>
       </c>
       <c r="F126" t="n">
-        <v>-12.87</v>
+        <v>-12.91</v>
       </c>
       <c r="G126" t="n">
         <v>30</v>
@@ -17911,6 +18013,42 @@
         <v>5.58</v>
       </c>
       <c r="J126" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>182</v>
+      </c>
+      <c r="D127" t="n">
+        <v>42.02</v>
+      </c>
+      <c r="E127" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="F127" t="n">
+        <v>-12.91</v>
+      </c>
+      <c r="G127" t="n">
+        <v>30</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-5.58</v>
+      </c>
+      <c r="I127" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="J127" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L127"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5745,43 +5745,85 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D127" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E127" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="F127" t="n">
-        <v>0.1635</v>
+        <v>0.1651</v>
       </c>
       <c r="G127" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="H127" t="n">
-        <v>34.5</v>
+        <v>33.9</v>
       </c>
       <c r="I127" t="n">
-        <v>232.8</v>
+        <v>233.4</v>
       </c>
       <c r="J127" t="n">
-        <v>56.8</v>
+        <v>58.1</v>
       </c>
       <c r="K127" t="n">
         <v>22.8</v>
       </c>
       <c r="L127" t="n">
-        <v>36.6</v>
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>181</v>
+      </c>
+      <c r="D128" t="n">
+        <v>181</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.1651</v>
+      </c>
+      <c r="G128" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="H128" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="I128" t="n">
+        <v>233.4</v>
+      </c>
+      <c r="J128" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="K128" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L128" t="n">
+        <v>37.6</v>
       </c>
     </row>
   </sheetData>
@@ -5795,7 +5837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R127"/>
+  <dimension ref="A1:R128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13393,61 +13435,121 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D127" t="n">
-        <v>0.4772</v>
+        <v>0.4782</v>
       </c>
       <c r="E127" t="n">
-        <v>45.86781913136987</v>
+        <v>45.94070937118612</v>
       </c>
       <c r="F127" t="n">
-        <v>41.74017049578097</v>
+        <v>41.76207599158589</v>
       </c>
       <c r="G127" t="n">
-        <v>2.893167007267448</v>
+        <v>2.949721191364733</v>
       </c>
       <c r="H127" t="n">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I127" t="n">
-        <v>0.4772</v>
+        <v>0.4782</v>
       </c>
       <c r="J127" t="n">
         <v>0.2495</v>
       </c>
       <c r="K127" t="n">
-        <v>0.2733</v>
+        <v>0.2723</v>
       </c>
       <c r="L127" t="n">
-        <v>4.4605</v>
+        <v>4.5314</v>
       </c>
       <c r="M127" t="n">
-        <v>4.3577</v>
+        <v>4.3709</v>
       </c>
       <c r="N127" t="n">
-        <v>4.4114</v>
+        <v>4.4547</v>
       </c>
       <c r="O127" t="n">
-        <v>3.6869</v>
+        <v>3.735</v>
       </c>
       <c r="P127" t="n">
-        <v>51.83</v>
+        <v>51.82</v>
       </c>
       <c r="Q127" t="n">
-        <v>48.17</v>
+        <v>48.18</v>
       </c>
       <c r="R127" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>181</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4782</v>
+      </c>
+      <c r="E128" t="n">
+        <v>45.94070937118612</v>
+      </c>
+      <c r="F128" t="n">
+        <v>41.76207599158589</v>
+      </c>
+      <c r="G128" t="n">
+        <v>2.949721191364733</v>
+      </c>
+      <c r="H128" t="n">
+        <v>531</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.4782</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.2495</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.2723</v>
+      </c>
+      <c r="L128" t="n">
+        <v>4.5314</v>
+      </c>
+      <c r="M128" t="n">
+        <v>4.3709</v>
+      </c>
+      <c r="N128" t="n">
+        <v>4.4547</v>
+      </c>
+      <c r="O128" t="n">
+        <v>3.735</v>
+      </c>
+      <c r="P128" t="n">
+        <v>51.82</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>48.18</v>
+      </c>
+      <c r="R128" t="n">
+        <v>3.64</v>
       </c>
     </row>
   </sheetData>
@@ -13461,7 +13563,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18019,36 +18121,72 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D127" t="n">
-        <v>42.02</v>
+        <v>42</v>
       </c>
       <c r="E127" t="n">
-        <v>54.94</v>
+        <v>54.97</v>
       </c>
       <c r="F127" t="n">
-        <v>-12.91</v>
+        <v>-12.98</v>
       </c>
       <c r="G127" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H127" t="n">
-        <v>-5.58</v>
+        <v>-5.59</v>
       </c>
       <c r="I127" t="n">
-        <v>5.58</v>
+        <v>5.59</v>
       </c>
       <c r="J127" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>181</v>
+      </c>
+      <c r="D128" t="n">
+        <v>42</v>
+      </c>
+      <c r="E128" t="n">
+        <v>54.97</v>
+      </c>
+      <c r="F128" t="n">
+        <v>-12.98</v>
+      </c>
+      <c r="G128" t="n">
+        <v>25</v>
+      </c>
+      <c r="H128" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="I128" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="J128" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5787,43 +5787,85 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D128" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E128" t="n">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="F128" t="n">
-        <v>0.1651</v>
+        <v>0.1668</v>
       </c>
       <c r="G128" t="n">
-        <v>48.8</v>
+        <v>48.6</v>
       </c>
       <c r="H128" t="n">
-        <v>33.9</v>
+        <v>35.3</v>
       </c>
       <c r="I128" t="n">
-        <v>233.4</v>
+        <v>231.6</v>
       </c>
       <c r="J128" t="n">
-        <v>58.1</v>
+        <v>56.1</v>
       </c>
       <c r="K128" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="L128" t="n">
-        <v>37.6</v>
+        <v>34.8</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>180</v>
+      </c>
+      <c r="D129" t="n">
+        <v>180</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.1668</v>
+      </c>
+      <c r="G129" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="H129" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="I129" t="n">
+        <v>231.6</v>
+      </c>
+      <c r="J129" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="K129" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L129" t="n">
+        <v>34.8</v>
       </c>
     </row>
   </sheetData>
@@ -5837,7 +5879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R128"/>
+  <dimension ref="A1:R129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13495,61 +13537,121 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4782</v>
+        <v>0.4792</v>
       </c>
       <c r="E128" t="n">
-        <v>45.94070937118612</v>
+        <v>45.95982988692332</v>
       </c>
       <c r="F128" t="n">
-        <v>41.76207599158589</v>
+        <v>41.83819671875935</v>
       </c>
       <c r="G128" t="n">
-        <v>2.949721191364733</v>
+        <v>2.939979938845405</v>
       </c>
       <c r="H128" t="n">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4782</v>
+        <v>0.4792</v>
       </c>
       <c r="J128" t="n">
-        <v>0.2495</v>
+        <v>0.2496</v>
       </c>
       <c r="K128" t="n">
-        <v>0.2723</v>
+        <v>0.2712</v>
       </c>
       <c r="L128" t="n">
-        <v>4.5314</v>
+        <v>4.303</v>
       </c>
       <c r="M128" t="n">
-        <v>4.3709</v>
+        <v>4.3592</v>
       </c>
       <c r="N128" t="n">
-        <v>4.4547</v>
+        <v>4.33</v>
       </c>
       <c r="O128" t="n">
-        <v>3.735</v>
+        <v>3.6638</v>
       </c>
       <c r="P128" t="n">
-        <v>51.82</v>
+        <v>51.8</v>
       </c>
       <c r="Q128" t="n">
-        <v>48.18</v>
+        <v>48.2</v>
       </c>
       <c r="R128" t="n">
-        <v>3.64</v>
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>180</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4792</v>
+      </c>
+      <c r="E129" t="n">
+        <v>45.95982988692332</v>
+      </c>
+      <c r="F129" t="n">
+        <v>41.83819671875935</v>
+      </c>
+      <c r="G129" t="n">
+        <v>2.939979938845405</v>
+      </c>
+      <c r="H129" t="n">
+        <v>534</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.4792</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="L129" t="n">
+        <v>4.303</v>
+      </c>
+      <c r="M129" t="n">
+        <v>4.3592</v>
+      </c>
+      <c r="N129" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O129" t="n">
+        <v>3.6638</v>
+      </c>
+      <c r="P129" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="R129" t="n">
+        <v>3.59</v>
       </c>
     </row>
   </sheetData>
@@ -13563,7 +13665,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18157,28 +18259,28 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D128" t="n">
         <v>42</v>
       </c>
       <c r="E128" t="n">
-        <v>54.97</v>
+        <v>54.98</v>
       </c>
       <c r="F128" t="n">
         <v>-12.98</v>
       </c>
       <c r="G128" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H128" t="n">
         <v>-5.59</v>
@@ -18187,6 +18289,42 @@
         <v>5.59</v>
       </c>
       <c r="J128" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>180</v>
+      </c>
+      <c r="D129" t="n">
+        <v>42</v>
+      </c>
+      <c r="E129" t="n">
+        <v>54.98</v>
+      </c>
+      <c r="F129" t="n">
+        <v>-12.98</v>
+      </c>
+      <c r="G129" t="n">
+        <v>30</v>
+      </c>
+      <c r="H129" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="I129" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="J129" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L129"/>
+  <dimension ref="A1:L130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5829,43 +5829,85 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D129" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E129" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="F129" t="n">
-        <v>0.1668</v>
+        <v>0.1685</v>
       </c>
       <c r="G129" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="H129" t="n">
-        <v>35.3</v>
+        <v>34.5</v>
       </c>
       <c r="I129" t="n">
-        <v>231.6</v>
+        <v>230.4</v>
       </c>
       <c r="J129" t="n">
-        <v>56.1</v>
+        <v>54.5</v>
       </c>
       <c r="K129" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="L129" t="n">
-        <v>34.8</v>
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>179</v>
+      </c>
+      <c r="D130" t="n">
+        <v>179</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.1685</v>
+      </c>
+      <c r="G130" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="H130" t="n">
+        <v>34.5</v>
+      </c>
+      <c r="I130" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="J130" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="K130" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L130" t="n">
+        <v>36.8</v>
       </c>
     </row>
   </sheetData>
@@ -5879,7 +5921,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R129"/>
+  <dimension ref="A1:R130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13597,52 +13639,52 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D129" t="n">
-        <v>0.4792</v>
+        <v>0.4803</v>
       </c>
       <c r="E129" t="n">
-        <v>45.95982988692332</v>
+        <v>45.99567850469536</v>
       </c>
       <c r="F129" t="n">
-        <v>41.83819671875935</v>
+        <v>41.83075936019583</v>
       </c>
       <c r="G129" t="n">
-        <v>2.939979938845405</v>
+        <v>2.964933207527987</v>
       </c>
       <c r="H129" t="n">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="I129" t="n">
-        <v>0.4792</v>
+        <v>0.4803</v>
       </c>
       <c r="J129" t="n">
         <v>0.2496</v>
       </c>
       <c r="K129" t="n">
-        <v>0.2712</v>
+        <v>0.2701</v>
       </c>
       <c r="L129" t="n">
-        <v>4.303</v>
+        <v>4.2771</v>
       </c>
       <c r="M129" t="n">
-        <v>4.3592</v>
+        <v>4.3685</v>
       </c>
       <c r="N129" t="n">
-        <v>4.33</v>
+        <v>4.321</v>
       </c>
       <c r="O129" t="n">
-        <v>3.6638</v>
+        <v>3.6697</v>
       </c>
       <c r="P129" t="n">
         <v>51.8</v>
@@ -13651,7 +13693,67 @@
         <v>48.2</v>
       </c>
       <c r="R129" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>179</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="E130" t="n">
+        <v>45.99567850469536</v>
+      </c>
+      <c r="F130" t="n">
+        <v>41.83075936019583</v>
+      </c>
+      <c r="G130" t="n">
+        <v>2.964933207527987</v>
+      </c>
+      <c r="H130" t="n">
+        <v>535</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.4803</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="L130" t="n">
+        <v>4.2771</v>
+      </c>
+      <c r="M130" t="n">
+        <v>4.3685</v>
+      </c>
+      <c r="N130" t="n">
+        <v>4.321</v>
+      </c>
+      <c r="O130" t="n">
+        <v>3.6697</v>
+      </c>
+      <c r="P130" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="R130" t="n">
+        <v>3.6</v>
       </c>
     </row>
   </sheetData>
@@ -13665,7 +13767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J129"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18295,28 +18397,28 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D129" t="n">
-        <v>42</v>
+        <v>41.99</v>
       </c>
       <c r="E129" t="n">
-        <v>54.98</v>
+        <v>55.01</v>
       </c>
       <c r="F129" t="n">
-        <v>-12.98</v>
+        <v>-13.02</v>
       </c>
       <c r="G129" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H129" t="n">
         <v>-5.59</v>
@@ -18325,6 +18427,42 @@
         <v>5.59</v>
       </c>
       <c r="J129" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>179</v>
+      </c>
+      <c r="D130" t="n">
+        <v>41.99</v>
+      </c>
+      <c r="E130" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="F130" t="n">
+        <v>-13.02</v>
+      </c>
+      <c r="G130" t="n">
+        <v>25</v>
+      </c>
+      <c r="H130" t="n">
+        <v>-5.59</v>
+      </c>
+      <c r="I130" t="n">
+        <v>5.59</v>
+      </c>
+      <c r="J130" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L130"/>
+  <dimension ref="A1:L133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5871,43 +5871,169 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D130" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E130" t="n">
-        <v>3.6</v>
+        <v>3.13</v>
       </c>
       <c r="F130" t="n">
-        <v>0.1685</v>
+        <v>0.1701</v>
       </c>
       <c r="G130" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="H130" t="n">
-        <v>34.5</v>
+        <v>33.2</v>
       </c>
       <c r="I130" t="n">
-        <v>230.4</v>
+        <v>227.8</v>
       </c>
       <c r="J130" t="n">
-        <v>54.5</v>
+        <v>54</v>
       </c>
       <c r="K130" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="L130" t="n">
-        <v>36.8</v>
+        <v>37.2</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>177</v>
+      </c>
+      <c r="D131" t="n">
+        <v>177</v>
+      </c>
+      <c r="E131" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.1718</v>
+      </c>
+      <c r="G131" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="H131" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="I131" t="n">
+        <v>228.8</v>
+      </c>
+      <c r="J131" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="K131" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="L131" t="n">
+        <v>37.2</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>176</v>
+      </c>
+      <c r="D132" t="n">
+        <v>176</v>
+      </c>
+      <c r="E132" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="G132" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H132" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I132" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="J132" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K132" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L132" t="n">
+        <v>36.3</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>176</v>
+      </c>
+      <c r="D133" t="n">
+        <v>176</v>
+      </c>
+      <c r="E133" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.1736</v>
+      </c>
+      <c r="G133" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="H133" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="I133" t="n">
+        <v>228.5</v>
+      </c>
+      <c r="J133" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="K133" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="L133" t="n">
+        <v>36.3</v>
       </c>
     </row>
   </sheetData>
@@ -5921,7 +6047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R130"/>
+  <dimension ref="A1:R133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13699,61 +13825,241 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D130" t="n">
-        <v>0.4803</v>
+        <v>0.4813</v>
       </c>
       <c r="E130" t="n">
-        <v>45.99567850469536</v>
+        <v>45.67583791674215</v>
       </c>
       <c r="F130" t="n">
-        <v>41.83075936019583</v>
+        <v>41.80611540000019</v>
       </c>
       <c r="G130" t="n">
-        <v>2.964933207527987</v>
+        <v>2.607256410243362</v>
       </c>
       <c r="H130" t="n">
-        <v>535</v>
+        <v>465</v>
       </c>
       <c r="I130" t="n">
-        <v>0.4803</v>
+        <v>0.4813</v>
       </c>
       <c r="J130" t="n">
-        <v>0.2496</v>
+        <v>0.2497</v>
       </c>
       <c r="K130" t="n">
-        <v>0.2701</v>
+        <v>0.269</v>
       </c>
       <c r="L130" t="n">
-        <v>4.2771</v>
+        <v>4.232</v>
       </c>
       <c r="M130" t="n">
-        <v>4.3685</v>
+        <v>3.9489</v>
       </c>
       <c r="N130" t="n">
-        <v>4.321</v>
+        <v>4.0958</v>
       </c>
       <c r="O130" t="n">
-        <v>3.6697</v>
+        <v>3.3793</v>
       </c>
       <c r="P130" t="n">
-        <v>51.8</v>
+        <v>51.56</v>
       </c>
       <c r="Q130" t="n">
-        <v>48.2</v>
+        <v>48.44</v>
       </c>
       <c r="R130" t="n">
-        <v>3.6</v>
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>177</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="E131" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F131" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G131" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H131" t="n">
+        <v>465</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="L131" t="n">
+        <v>4.232</v>
+      </c>
+      <c r="M131" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N131" t="n">
+        <v>4.0955</v>
+      </c>
+      <c r="O131" t="n">
+        <v>3.3775</v>
+      </c>
+      <c r="P131" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="R131" t="n">
+        <v>3.51</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>176</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="E132" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F132" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G132" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H132" t="n">
+        <v>465</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="L132" t="n">
+        <v>4.232</v>
+      </c>
+      <c r="M132" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N132" t="n">
+        <v>4.0951</v>
+      </c>
+      <c r="O132" t="n">
+        <v>3.3758</v>
+      </c>
+      <c r="P132" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="R132" t="n">
+        <v>3.42</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>176</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="E133" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F133" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G133" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H133" t="n">
+        <v>465</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4835</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.2497</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.2668</v>
+      </c>
+      <c r="L133" t="n">
+        <v>4.232</v>
+      </c>
+      <c r="M133" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N133" t="n">
+        <v>4.0951</v>
+      </c>
+      <c r="O133" t="n">
+        <v>3.3758</v>
+      </c>
+      <c r="P133" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>48.29</v>
+      </c>
+      <c r="R133" t="n">
+        <v>3.42</v>
       </c>
     </row>
   </sheetData>
@@ -13767,7 +14073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18433,36 +18739,144 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D130" t="n">
-        <v>41.99</v>
+        <v>42.77</v>
       </c>
       <c r="E130" t="n">
-        <v>55.01</v>
+        <v>54.11</v>
       </c>
       <c r="F130" t="n">
-        <v>-13.02</v>
+        <v>-11.34</v>
       </c>
       <c r="G130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H130" t="n">
-        <v>-5.59</v>
+        <v>-5.42</v>
       </c>
       <c r="I130" t="n">
-        <v>5.59</v>
+        <v>5.42</v>
       </c>
       <c r="J130" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>177</v>
+      </c>
+      <c r="D131" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E131" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F131" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G131" t="n">
+        <v>30</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I131" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>176</v>
+      </c>
+      <c r="D132" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E132" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F132" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G132" t="n">
+        <v>30</v>
+      </c>
+      <c r="H132" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I132" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>176</v>
+      </c>
+      <c r="D133" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E133" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F133" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G133" t="n">
+        <v>30</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I133" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J133" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L133"/>
+  <dimension ref="A1:L134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5997,43 +5997,85 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D133" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E133" t="n">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="F133" t="n">
-        <v>0.1736</v>
+        <v>0.1753</v>
       </c>
       <c r="G133" t="n">
-        <v>48.4</v>
+        <v>48.9</v>
       </c>
       <c r="H133" t="n">
-        <v>30.5</v>
+        <v>34.1</v>
       </c>
       <c r="I133" t="n">
-        <v>228.5</v>
+        <v>230.7</v>
       </c>
       <c r="J133" t="n">
-        <v>53.1</v>
+        <v>54.7</v>
       </c>
       <c r="K133" t="n">
-        <v>22.5</v>
+        <v>22.9</v>
       </c>
       <c r="L133" t="n">
-        <v>36.3</v>
+        <v>35.2</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>175</v>
+      </c>
+      <c r="D134" t="n">
+        <v>175</v>
+      </c>
+      <c r="E134" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.1753</v>
+      </c>
+      <c r="G134" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H134" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="I134" t="n">
+        <v>230.7</v>
+      </c>
+      <c r="J134" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="K134" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L134" t="n">
+        <v>35.2</v>
       </c>
     </row>
   </sheetData>
@@ -6047,7 +6089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R133"/>
+  <dimension ref="A1:R134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14005,61 +14047,121 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D133" t="n">
-        <v>0.4835</v>
+        <v>0.4846</v>
       </c>
       <c r="E133" t="n">
-        <v>45.67583791674215</v>
+        <v>45.95884287755909</v>
       </c>
       <c r="F133" t="n">
-        <v>41.80611540000019</v>
+        <v>41.75097002204278</v>
       </c>
       <c r="G133" t="n">
-        <v>2.607256410243362</v>
+        <v>3.005524995901361</v>
       </c>
       <c r="H133" t="n">
-        <v>465</v>
+        <v>540</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4835</v>
+        <v>0.4846</v>
       </c>
       <c r="J133" t="n">
-        <v>0.2497</v>
+        <v>0.2498</v>
       </c>
       <c r="K133" t="n">
-        <v>0.2668</v>
+        <v>0.2657</v>
       </c>
       <c r="L133" t="n">
-        <v>4.232</v>
+        <v>4.2755</v>
       </c>
       <c r="M133" t="n">
-        <v>3.9489</v>
+        <v>4.3853</v>
       </c>
       <c r="N133" t="n">
-        <v>4.0951</v>
+        <v>4.3287</v>
       </c>
       <c r="O133" t="n">
-        <v>3.3758</v>
+        <v>3.6875</v>
       </c>
       <c r="P133" t="n">
-        <v>51.71</v>
+        <v>51.84</v>
       </c>
       <c r="Q133" t="n">
-        <v>48.29</v>
+        <v>48.16</v>
       </c>
       <c r="R133" t="n">
-        <v>3.42</v>
+        <v>3.68</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>175</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4846</v>
+      </c>
+      <c r="E134" t="n">
+        <v>45.95884287755909</v>
+      </c>
+      <c r="F134" t="n">
+        <v>41.75097002204278</v>
+      </c>
+      <c r="G134" t="n">
+        <v>3.005524995901361</v>
+      </c>
+      <c r="H134" t="n">
+        <v>540</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4846</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="L134" t="n">
+        <v>4.2755</v>
+      </c>
+      <c r="M134" t="n">
+        <v>4.3853</v>
+      </c>
+      <c r="N134" t="n">
+        <v>4.3287</v>
+      </c>
+      <c r="O134" t="n">
+        <v>3.6875</v>
+      </c>
+      <c r="P134" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>48.16</v>
+      </c>
+      <c r="R134" t="n">
+        <v>3.68</v>
       </c>
     </row>
   </sheetData>
@@ -14073,7 +14175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18847,36 +18949,72 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D133" t="n">
-        <v>42.77</v>
+        <v>41.96</v>
       </c>
       <c r="E133" t="n">
-        <v>54.11</v>
+        <v>55.05</v>
       </c>
       <c r="F133" t="n">
-        <v>-11.34</v>
+        <v>-13.09</v>
       </c>
       <c r="G133" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H133" t="n">
-        <v>-5.42</v>
+        <v>-5.6</v>
       </c>
       <c r="I133" t="n">
-        <v>5.42</v>
+        <v>5.6</v>
       </c>
       <c r="J133" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>175</v>
+      </c>
+      <c r="D134" t="n">
+        <v>41.96</v>
+      </c>
+      <c r="E134" t="n">
+        <v>55.05</v>
+      </c>
+      <c r="F134" t="n">
+        <v>-13.09</v>
+      </c>
+      <c r="G134" t="n">
+        <v>25</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-5.6</v>
+      </c>
+      <c r="I134" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J134" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -6012,28 +6012,28 @@
         <v>175</v>
       </c>
       <c r="E133" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="F133" t="n">
         <v>0.1753</v>
       </c>
       <c r="G133" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="H133" t="n">
-        <v>34.1</v>
+        <v>35.9</v>
       </c>
       <c r="I133" t="n">
-        <v>230.7</v>
+        <v>232.1</v>
       </c>
       <c r="J133" t="n">
-        <v>54.7</v>
+        <v>55.4</v>
       </c>
       <c r="K133" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="L133" t="n">
-        <v>35.2</v>
+        <v>39</v>
       </c>
     </row>
     <row r="134">
@@ -6054,28 +6054,28 @@
         <v>175</v>
       </c>
       <c r="E134" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
       <c r="F134" t="n">
         <v>0.1753</v>
       </c>
       <c r="G134" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="H134" t="n">
-        <v>34.1</v>
+        <v>35.9</v>
       </c>
       <c r="I134" t="n">
-        <v>230.7</v>
+        <v>232.1</v>
       </c>
       <c r="J134" t="n">
-        <v>54.7</v>
+        <v>55.4</v>
       </c>
       <c r="K134" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="L134" t="n">
-        <v>35.2</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -14062,16 +14062,16 @@
         <v>0.4846</v>
       </c>
       <c r="E133" t="n">
-        <v>45.95884287755909</v>
+        <v>45.97110130064148</v>
       </c>
       <c r="F133" t="n">
-        <v>41.75097002204278</v>
+        <v>41.69673661773497</v>
       </c>
       <c r="G133" t="n">
-        <v>3.005524995901361</v>
+        <v>3.071614633567011</v>
       </c>
       <c r="H133" t="n">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="I133" t="n">
         <v>0.4846</v>
@@ -14086,22 +14086,22 @@
         <v>4.2755</v>
       </c>
       <c r="M133" t="n">
-        <v>4.3853</v>
+        <v>4.4285</v>
       </c>
       <c r="N133" t="n">
-        <v>4.3287</v>
+        <v>4.3496</v>
       </c>
       <c r="O133" t="n">
-        <v>3.6875</v>
+        <v>3.7303</v>
       </c>
       <c r="P133" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="Q133" t="n">
-        <v>48.16</v>
+        <v>48.08</v>
       </c>
       <c r="R133" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
     </row>
     <row r="134">
@@ -14122,16 +14122,16 @@
         <v>0.4846</v>
       </c>
       <c r="E134" t="n">
-        <v>45.95884287755909</v>
+        <v>45.97110130064148</v>
       </c>
       <c r="F134" t="n">
-        <v>41.75097002204278</v>
+        <v>41.69673661773497</v>
       </c>
       <c r="G134" t="n">
-        <v>3.005524995901361</v>
+        <v>3.071614633567011</v>
       </c>
       <c r="H134" t="n">
-        <v>540</v>
+        <v>545</v>
       </c>
       <c r="I134" t="n">
         <v>0.4846</v>
@@ -14146,22 +14146,22 @@
         <v>4.2755</v>
       </c>
       <c r="M134" t="n">
-        <v>4.3853</v>
+        <v>4.4285</v>
       </c>
       <c r="N134" t="n">
-        <v>4.3287</v>
+        <v>4.3496</v>
       </c>
       <c r="O134" t="n">
-        <v>3.6875</v>
+        <v>3.7303</v>
       </c>
       <c r="P134" t="n">
-        <v>51.84</v>
+        <v>51.92</v>
       </c>
       <c r="Q134" t="n">
-        <v>48.16</v>
+        <v>48.08</v>
       </c>
       <c r="R134" t="n">
-        <v>3.68</v>
+        <v>3.84</v>
       </c>
     </row>
   </sheetData>
@@ -18961,22 +18961,22 @@
         <v>175</v>
       </c>
       <c r="D133" t="n">
-        <v>41.96</v>
+        <v>41.88</v>
       </c>
       <c r="E133" t="n">
-        <v>55.05</v>
+        <v>55.15</v>
       </c>
       <c r="F133" t="n">
-        <v>-13.09</v>
+        <v>-13.28</v>
       </c>
       <c r="G133" t="n">
         <v>25</v>
       </c>
       <c r="H133" t="n">
-        <v>-5.6</v>
+        <v>-5.61</v>
       </c>
       <c r="I133" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="J133" t="n">
         <v>0.151</v>
@@ -18997,22 +18997,22 @@
         <v>175</v>
       </c>
       <c r="D134" t="n">
-        <v>41.96</v>
+        <v>41.88</v>
       </c>
       <c r="E134" t="n">
-        <v>55.05</v>
+        <v>55.15</v>
       </c>
       <c r="F134" t="n">
-        <v>-13.09</v>
+        <v>-13.28</v>
       </c>
       <c r="G134" t="n">
         <v>25</v>
       </c>
       <c r="H134" t="n">
-        <v>-5.6</v>
+        <v>-5.61</v>
       </c>
       <c r="I134" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="J134" t="n">
         <v>0.151</v>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6039,43 +6039,85 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D134" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E134" t="n">
-        <v>3.84</v>
+        <v>4.26</v>
       </c>
       <c r="F134" t="n">
-        <v>0.1753</v>
+        <v>0.177</v>
       </c>
       <c r="G134" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="H134" t="n">
-        <v>35.9</v>
+        <v>37.3</v>
       </c>
       <c r="I134" t="n">
-        <v>232.1</v>
+        <v>233.2</v>
       </c>
       <c r="J134" t="n">
-        <v>55.4</v>
+        <v>56.6</v>
       </c>
       <c r="K134" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="L134" t="n">
-        <v>39</v>
+        <v>36.8</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>174</v>
+      </c>
+      <c r="D135" t="n">
+        <v>174</v>
+      </c>
+      <c r="E135" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="G135" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>37.3</v>
+      </c>
+      <c r="I135" t="n">
+        <v>233.2</v>
+      </c>
+      <c r="J135" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="K135" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L135" t="n">
+        <v>36.8</v>
       </c>
     </row>
   </sheetData>
@@ -6089,7 +6131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R134"/>
+  <dimension ref="A1:R135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14107,61 +14149,121 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D134" t="n">
-        <v>0.4846</v>
+        <v>0.4857</v>
       </c>
       <c r="E134" t="n">
-        <v>45.97110130064148</v>
+        <v>46.00006970604374</v>
       </c>
       <c r="F134" t="n">
-        <v>41.69673661773497</v>
+        <v>41.70479246384978</v>
       </c>
       <c r="G134" t="n">
-        <v>3.071614633567011</v>
+        <v>3.082964461026319</v>
       </c>
       <c r="H134" t="n">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="I134" t="n">
-        <v>0.4846</v>
+        <v>0.4857</v>
       </c>
       <c r="J134" t="n">
         <v>0.2498</v>
       </c>
       <c r="K134" t="n">
-        <v>0.2657</v>
+        <v>0.2646</v>
       </c>
       <c r="L134" t="n">
-        <v>4.2755</v>
+        <v>5.526</v>
       </c>
       <c r="M134" t="n">
         <v>4.4285</v>
       </c>
       <c r="N134" t="n">
-        <v>4.3496</v>
+        <v>4.993</v>
       </c>
       <c r="O134" t="n">
-        <v>3.7303</v>
+        <v>4.0654</v>
       </c>
       <c r="P134" t="n">
-        <v>51.92</v>
+        <v>52.13</v>
       </c>
       <c r="Q134" t="n">
-        <v>48.08</v>
+        <v>47.87</v>
       </c>
       <c r="R134" t="n">
-        <v>3.84</v>
+        <v>4.26</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>174</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.4857</v>
+      </c>
+      <c r="E135" t="n">
+        <v>46.00006970604374</v>
+      </c>
+      <c r="F135" t="n">
+        <v>41.70479246384978</v>
+      </c>
+      <c r="G135" t="n">
+        <v>3.082964461026319</v>
+      </c>
+      <c r="H135" t="n">
+        <v>546</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.4857</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.2646</v>
+      </c>
+      <c r="L135" t="n">
+        <v>5.526</v>
+      </c>
+      <c r="M135" t="n">
+        <v>4.4285</v>
+      </c>
+      <c r="N135" t="n">
+        <v>4.993</v>
+      </c>
+      <c r="O135" t="n">
+        <v>4.0654</v>
+      </c>
+      <c r="P135" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="R135" t="n">
+        <v>4.26</v>
       </c>
     </row>
   </sheetData>
@@ -14175,7 +14277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J134"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18985,16 +19087,16 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D134" t="n">
         <v>41.88</v>
@@ -19015,6 +19117,42 @@
         <v>5.61</v>
       </c>
       <c r="J134" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>174</v>
+      </c>
+      <c r="D135" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="E135" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="F135" t="n">
+        <v>-13.28</v>
+      </c>
+      <c r="G135" t="n">
+        <v>25</v>
+      </c>
+      <c r="H135" t="n">
+        <v>-5.61</v>
+      </c>
+      <c r="I135" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="J135" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:L138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6081,43 +6081,169 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D135" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E135" t="n">
-        <v>4.26</v>
+        <v>3.72</v>
       </c>
       <c r="F135" t="n">
-        <v>0.177</v>
+        <v>0.1788</v>
       </c>
       <c r="G135" t="n">
-        <v>49.1</v>
+        <v>48.6</v>
       </c>
       <c r="H135" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="I135" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="J135" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="K135" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="L135" t="n">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>172</v>
+      </c>
+      <c r="D136" t="n">
+        <v>172</v>
+      </c>
+      <c r="E136" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.1806</v>
+      </c>
+      <c r="G136" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="H136" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="I136" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="J136" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="K136" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L136" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>171</v>
+      </c>
+      <c r="D137" t="n">
+        <v>171</v>
+      </c>
+      <c r="E137" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="G137" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="H137" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="I137" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="J137" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="K137" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L137" t="n">
         <v>37.3</v>
       </c>
-      <c r="I135" t="n">
-        <v>233.2</v>
-      </c>
-      <c r="J135" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="K135" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="L135" t="n">
-        <v>36.8</v>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>171</v>
+      </c>
+      <c r="D138" t="n">
+        <v>171</v>
+      </c>
+      <c r="E138" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="G138" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="H138" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="I138" t="n">
+        <v>230.2</v>
+      </c>
+      <c r="J138" t="n">
+        <v>54.2</v>
+      </c>
+      <c r="K138" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="L138" t="n">
+        <v>37.3</v>
       </c>
     </row>
   </sheetData>
@@ -6131,7 +6257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R135"/>
+  <dimension ref="A1:R138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14209,61 +14335,241 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D135" t="n">
-        <v>0.4857</v>
+        <v>0.4868</v>
       </c>
       <c r="E135" t="n">
-        <v>46.00006970604374</v>
+        <v>45.67583791674215</v>
       </c>
       <c r="F135" t="n">
-        <v>41.70479246384978</v>
+        <v>41.80611540000019</v>
       </c>
       <c r="G135" t="n">
-        <v>3.082964461026319</v>
+        <v>2.607256410243362</v>
       </c>
       <c r="H135" t="n">
-        <v>546</v>
+        <v>465</v>
       </c>
       <c r="I135" t="n">
-        <v>0.4857</v>
+        <v>0.4868</v>
       </c>
       <c r="J135" t="n">
         <v>0.2498</v>
       </c>
       <c r="K135" t="n">
-        <v>0.2646</v>
+        <v>0.2634</v>
       </c>
       <c r="L135" t="n">
-        <v>5.526</v>
+        <v>5.7306</v>
       </c>
       <c r="M135" t="n">
-        <v>4.4285</v>
+        <v>3.9489</v>
       </c>
       <c r="N135" t="n">
-        <v>4.993</v>
+        <v>4.8633</v>
       </c>
       <c r="O135" t="n">
-        <v>4.0654</v>
+        <v>3.7652</v>
       </c>
       <c r="P135" t="n">
-        <v>52.13</v>
+        <v>51.86</v>
       </c>
       <c r="Q135" t="n">
-        <v>47.87</v>
+        <v>48.14</v>
       </c>
       <c r="R135" t="n">
-        <v>4.26</v>
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>172</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.4879</v>
+      </c>
+      <c r="E136" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F136" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G136" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H136" t="n">
+        <v>465</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.4879</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.2623</v>
+      </c>
+      <c r="L136" t="n">
+        <v>5.8751</v>
+      </c>
+      <c r="M136" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N136" t="n">
+        <v>4.9353</v>
+      </c>
+      <c r="O136" t="n">
+        <v>3.7995</v>
+      </c>
+      <c r="P136" t="n">
+        <v>51.98</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>48.02</v>
+      </c>
+      <c r="R136" t="n">
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>171</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="E137" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F137" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G137" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H137" t="n">
+        <v>465</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="L137" t="n">
+        <v>5.8751</v>
+      </c>
+      <c r="M137" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N137" t="n">
+        <v>4.9332</v>
+      </c>
+      <c r="O137" t="n">
+        <v>3.7958</v>
+      </c>
+      <c r="P137" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="R137" t="n">
+        <v>3.72</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>171</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="E138" t="n">
+        <v>45.67583791674215</v>
+      </c>
+      <c r="F138" t="n">
+        <v>41.80611540000019</v>
+      </c>
+      <c r="G138" t="n">
+        <v>2.607256410243362</v>
+      </c>
+      <c r="H138" t="n">
+        <v>465</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="L138" t="n">
+        <v>5.8751</v>
+      </c>
+      <c r="M138" t="n">
+        <v>3.9489</v>
+      </c>
+      <c r="N138" t="n">
+        <v>4.9332</v>
+      </c>
+      <c r="O138" t="n">
+        <v>3.7958</v>
+      </c>
+      <c r="P138" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>48.14</v>
+      </c>
+      <c r="R138" t="n">
+        <v>3.72</v>
       </c>
     </row>
   </sheetData>
@@ -14277,7 +14583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19123,36 +19429,144 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D135" t="n">
-        <v>41.88</v>
+        <v>42.77</v>
       </c>
       <c r="E135" t="n">
-        <v>55.15</v>
+        <v>54.11</v>
       </c>
       <c r="F135" t="n">
-        <v>-13.28</v>
+        <v>-11.34</v>
       </c>
       <c r="G135" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H135" t="n">
-        <v>-5.61</v>
+        <v>-5.42</v>
       </c>
       <c r="I135" t="n">
-        <v>5.61</v>
+        <v>5.42</v>
       </c>
       <c r="J135" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>172</v>
+      </c>
+      <c r="D136" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E136" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F136" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G136" t="n">
+        <v>30</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I136" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>171</v>
+      </c>
+      <c r="D137" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E137" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G137" t="n">
+        <v>30</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I137" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>171</v>
+      </c>
+      <c r="D138" t="n">
+        <v>42.77</v>
+      </c>
+      <c r="E138" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="F138" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="G138" t="n">
+        <v>30</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-5.42</v>
+      </c>
+      <c r="I138" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="J138" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L138"/>
+  <dimension ref="A1:L139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6207,43 +6207,85 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D138" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E138" t="n">
-        <v>3.72</v>
+        <v>4.07</v>
       </c>
       <c r="F138" t="n">
-        <v>0.1824</v>
+        <v>0.1842</v>
       </c>
       <c r="G138" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="H138" t="n">
-        <v>36.4</v>
+        <v>34.2</v>
       </c>
       <c r="I138" t="n">
-        <v>230.2</v>
+        <v>232.3</v>
       </c>
       <c r="J138" t="n">
-        <v>54.2</v>
+        <v>56.3</v>
       </c>
       <c r="K138" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="L138" t="n">
-        <v>37.3</v>
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>170</v>
+      </c>
+      <c r="D139" t="n">
+        <v>170</v>
+      </c>
+      <c r="E139" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="G139" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="H139" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="I139" t="n">
+        <v>232.3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>56.3</v>
+      </c>
+      <c r="K139" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L139" t="n">
+        <v>37.4</v>
       </c>
     </row>
   </sheetData>
@@ -6257,7 +6299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R138"/>
+  <dimension ref="A1:R139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14515,61 +14557,121 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D138" t="n">
-        <v>0.489</v>
+        <v>0.4901</v>
       </c>
       <c r="E138" t="n">
-        <v>45.67583791674215</v>
+        <v>46.00006970604374</v>
       </c>
       <c r="F138" t="n">
-        <v>41.80611540000019</v>
+        <v>41.70479246384978</v>
       </c>
       <c r="G138" t="n">
-        <v>2.607256410243362</v>
+        <v>3.082964461026319</v>
       </c>
       <c r="H138" t="n">
-        <v>465</v>
+        <v>546</v>
       </c>
       <c r="I138" t="n">
-        <v>0.489</v>
+        <v>0.4901</v>
       </c>
       <c r="J138" t="n">
         <v>0.2499</v>
       </c>
       <c r="K138" t="n">
-        <v>0.2611</v>
+        <v>0.26</v>
       </c>
       <c r="L138" t="n">
         <v>5.8751</v>
       </c>
       <c r="M138" t="n">
-        <v>3.9489</v>
+        <v>4.4382</v>
       </c>
       <c r="N138" t="n">
-        <v>4.9332</v>
+        <v>5.1708</v>
       </c>
       <c r="O138" t="n">
-        <v>3.7958</v>
+        <v>4.1475</v>
       </c>
       <c r="P138" t="n">
-        <v>51.86</v>
+        <v>52.03</v>
       </c>
       <c r="Q138" t="n">
-        <v>48.14</v>
+        <v>47.97</v>
       </c>
       <c r="R138" t="n">
-        <v>3.72</v>
+        <v>4.07</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>170</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="E139" t="n">
+        <v>46.00006970604374</v>
+      </c>
+      <c r="F139" t="n">
+        <v>41.70479246384978</v>
+      </c>
+      <c r="G139" t="n">
+        <v>3.082964461026319</v>
+      </c>
+      <c r="H139" t="n">
+        <v>546</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.4901</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L139" t="n">
+        <v>5.8751</v>
+      </c>
+      <c r="M139" t="n">
+        <v>4.4382</v>
+      </c>
+      <c r="N139" t="n">
+        <v>5.1708</v>
+      </c>
+      <c r="O139" t="n">
+        <v>4.1475</v>
+      </c>
+      <c r="P139" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="R139" t="n">
+        <v>4.07</v>
       </c>
     </row>
   </sheetData>
@@ -14583,7 +14685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J138"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19537,36 +19639,72 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D138" t="n">
-        <v>42.77</v>
+        <v>41.87</v>
       </c>
       <c r="E138" t="n">
-        <v>54.11</v>
+        <v>55.18</v>
       </c>
       <c r="F138" t="n">
-        <v>-11.34</v>
+        <v>-13.31</v>
       </c>
       <c r="G138" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H138" t="n">
-        <v>-5.42</v>
+        <v>-5.61</v>
       </c>
       <c r="I138" t="n">
-        <v>5.42</v>
+        <v>5.61</v>
       </c>
       <c r="J138" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>170</v>
+      </c>
+      <c r="D139" t="n">
+        <v>41.87</v>
+      </c>
+      <c r="E139" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="F139" t="n">
+        <v>-13.31</v>
+      </c>
+      <c r="G139" t="n">
+        <v>25</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-5.61</v>
+      </c>
+      <c r="I139" t="n">
+        <v>5.61</v>
+      </c>
+      <c r="J139" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L139"/>
+  <dimension ref="A1:L140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6249,43 +6249,85 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D139" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E139" t="n">
-        <v>4.07</v>
+        <v>4.29</v>
       </c>
       <c r="F139" t="n">
-        <v>0.1842</v>
+        <v>0.1861</v>
       </c>
       <c r="G139" t="n">
-        <v>49.1</v>
+        <v>49.3</v>
       </c>
       <c r="H139" t="n">
-        <v>34.2</v>
+        <v>37.2</v>
       </c>
       <c r="I139" t="n">
-        <v>232.3</v>
+        <v>234.3</v>
       </c>
       <c r="J139" t="n">
-        <v>56.3</v>
+        <v>56.7</v>
       </c>
       <c r="K139" t="n">
         <v>23.1</v>
       </c>
       <c r="L139" t="n">
-        <v>37.4</v>
+        <v>38.8</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>169</v>
+      </c>
+      <c r="D140" t="n">
+        <v>169</v>
+      </c>
+      <c r="E140" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="G140" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="H140" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="I140" t="n">
+        <v>234.3</v>
+      </c>
+      <c r="J140" t="n">
+        <v>56.7</v>
+      </c>
+      <c r="K140" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L140" t="n">
+        <v>38.8</v>
       </c>
     </row>
   </sheetData>
@@ -6299,7 +6341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R139"/>
+  <dimension ref="A1:R140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14617,61 +14659,121 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D139" t="n">
-        <v>0.4901</v>
+        <v>0.4913</v>
       </c>
       <c r="E139" t="n">
-        <v>46.00006970604374</v>
+        <v>46.03682869998445</v>
       </c>
       <c r="F139" t="n">
-        <v>41.70479246384978</v>
+        <v>41.68236276070941</v>
       </c>
       <c r="G139" t="n">
-        <v>3.082964461026319</v>
+        <v>3.140256454106748</v>
       </c>
       <c r="H139" t="n">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="I139" t="n">
-        <v>0.4901</v>
+        <v>0.4913</v>
       </c>
       <c r="J139" t="n">
         <v>0.2499</v>
       </c>
       <c r="K139" t="n">
-        <v>0.26</v>
+        <v>0.2588</v>
       </c>
       <c r="L139" t="n">
         <v>5.8751</v>
       </c>
       <c r="M139" t="n">
-        <v>4.4382</v>
+        <v>4.4625</v>
       </c>
       <c r="N139" t="n">
-        <v>5.1708</v>
+        <v>5.1811</v>
       </c>
       <c r="O139" t="n">
-        <v>4.1475</v>
+        <v>4.1784</v>
       </c>
       <c r="P139" t="n">
-        <v>52.03</v>
+        <v>52.15</v>
       </c>
       <c r="Q139" t="n">
-        <v>47.97</v>
+        <v>47.85</v>
       </c>
       <c r="R139" t="n">
-        <v>4.07</v>
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>169</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="E140" t="n">
+        <v>46.03682869998445</v>
+      </c>
+      <c r="F140" t="n">
+        <v>41.68236276070941</v>
+      </c>
+      <c r="G140" t="n">
+        <v>3.140256454106748</v>
+      </c>
+      <c r="H140" t="n">
+        <v>547</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.4913</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="L140" t="n">
+        <v>5.8751</v>
+      </c>
+      <c r="M140" t="n">
+        <v>4.4625</v>
+      </c>
+      <c r="N140" t="n">
+        <v>5.1811</v>
+      </c>
+      <c r="O140" t="n">
+        <v>4.1784</v>
+      </c>
+      <c r="P140" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="R140" t="n">
+        <v>4.29</v>
       </c>
     </row>
   </sheetData>
@@ -14685,7 +14787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J139"/>
+  <dimension ref="A1:J140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19675,36 +19777,72 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D139" t="n">
-        <v>41.87</v>
+        <v>41.83</v>
       </c>
       <c r="E139" t="n">
-        <v>55.18</v>
+        <v>55.21</v>
       </c>
       <c r="F139" t="n">
-        <v>-13.31</v>
+        <v>-13.39</v>
       </c>
       <c r="G139" t="n">
         <v>25</v>
       </c>
       <c r="H139" t="n">
-        <v>-5.61</v>
+        <v>-5.62</v>
       </c>
       <c r="I139" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="J139" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>169</v>
+      </c>
+      <c r="D140" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="E140" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="F140" t="n">
+        <v>-13.39</v>
+      </c>
+      <c r="G140" t="n">
+        <v>25</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="I140" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="J140" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L140"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6291,43 +6291,85 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D140" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E140" t="n">
-        <v>4.29</v>
+        <v>3.97</v>
       </c>
       <c r="F140" t="n">
-        <v>0.1861</v>
+        <v>0.1879</v>
       </c>
       <c r="G140" t="n">
-        <v>49.3</v>
+        <v>49.1</v>
       </c>
       <c r="H140" t="n">
-        <v>37.2</v>
+        <v>36.3</v>
       </c>
       <c r="I140" t="n">
-        <v>234.3</v>
+        <v>232.5</v>
       </c>
       <c r="J140" t="n">
-        <v>56.7</v>
+        <v>56.1</v>
       </c>
       <c r="K140" t="n">
         <v>23.1</v>
       </c>
       <c r="L140" t="n">
-        <v>38.8</v>
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>168</v>
+      </c>
+      <c r="D141" t="n">
+        <v>168</v>
+      </c>
+      <c r="E141" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="G141" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="H141" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="I141" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="J141" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="K141" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="L141" t="n">
+        <v>37.6</v>
       </c>
     </row>
   </sheetData>
@@ -6341,7 +6383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R140"/>
+  <dimension ref="A1:R141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14719,61 +14761,121 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D140" t="n">
-        <v>0.4913</v>
+        <v>0.4925</v>
       </c>
       <c r="E140" t="n">
-        <v>46.03682869998445</v>
+        <v>46.02538425589233</v>
       </c>
       <c r="F140" t="n">
-        <v>41.68236276070941</v>
+        <v>41.6858688187754</v>
       </c>
       <c r="G140" t="n">
-        <v>3.140256454106748</v>
+        <v>3.101514740364657</v>
       </c>
       <c r="H140" t="n">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="I140" t="n">
-        <v>0.4913</v>
+        <v>0.4925</v>
       </c>
       <c r="J140" t="n">
         <v>0.2499</v>
       </c>
       <c r="K140" t="n">
-        <v>0.2588</v>
+        <v>0.2576</v>
       </c>
       <c r="L140" t="n">
         <v>5.8751</v>
       </c>
       <c r="M140" t="n">
-        <v>4.4625</v>
+        <v>4.4643</v>
       </c>
       <c r="N140" t="n">
-        <v>5.1811</v>
+        <v>5.1803</v>
       </c>
       <c r="O140" t="n">
-        <v>4.1784</v>
+        <v>4.1566</v>
       </c>
       <c r="P140" t="n">
-        <v>52.15</v>
+        <v>51.99</v>
       </c>
       <c r="Q140" t="n">
-        <v>47.85</v>
+        <v>48.01</v>
       </c>
       <c r="R140" t="n">
-        <v>4.29</v>
+        <v>3.97</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>168</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.4925</v>
+      </c>
+      <c r="E141" t="n">
+        <v>46.02538425589233</v>
+      </c>
+      <c r="F141" t="n">
+        <v>41.6858688187754</v>
+      </c>
+      <c r="G141" t="n">
+        <v>3.101514740364657</v>
+      </c>
+      <c r="H141" t="n">
+        <v>548</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.4925</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.2499</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="L141" t="n">
+        <v>5.8751</v>
+      </c>
+      <c r="M141" t="n">
+        <v>4.4643</v>
+      </c>
+      <c r="N141" t="n">
+        <v>5.1803</v>
+      </c>
+      <c r="O141" t="n">
+        <v>4.1566</v>
+      </c>
+      <c r="P141" t="n">
+        <v>51.99</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="R141" t="n">
+        <v>3.97</v>
       </c>
     </row>
   </sheetData>
@@ -14787,7 +14889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J140"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19813,16 +19915,16 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D140" t="n">
         <v>41.83</v>
@@ -19843,6 +19945,42 @@
         <v>5.62</v>
       </c>
       <c r="J140" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>168</v>
+      </c>
+      <c r="D141" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="E141" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="F141" t="n">
+        <v>-13.39</v>
+      </c>
+      <c r="G141" t="n">
+        <v>25</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-5.62</v>
+      </c>
+      <c r="I141" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="J141" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -6306,7 +6306,7 @@
         <v>168</v>
       </c>
       <c r="E140" t="n">
-        <v>3.97</v>
+        <v>4.09</v>
       </c>
       <c r="F140" t="n">
         <v>0.1879</v>
@@ -6315,19 +6315,19 @@
         <v>49.1</v>
       </c>
       <c r="H140" t="n">
-        <v>36.3</v>
+        <v>35.9</v>
       </c>
       <c r="I140" t="n">
-        <v>232.5</v>
+        <v>232.6</v>
       </c>
       <c r="J140" t="n">
-        <v>56.1</v>
+        <v>55.8</v>
       </c>
       <c r="K140" t="n">
         <v>23.1</v>
       </c>
       <c r="L140" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
     </row>
     <row r="141">
@@ -6348,7 +6348,7 @@
         <v>168</v>
       </c>
       <c r="E141" t="n">
-        <v>3.97</v>
+        <v>4.09</v>
       </c>
       <c r="F141" t="n">
         <v>0.1879</v>
@@ -6357,19 +6357,19 @@
         <v>49.1</v>
       </c>
       <c r="H141" t="n">
-        <v>36.3</v>
+        <v>35.9</v>
       </c>
       <c r="I141" t="n">
-        <v>232.5</v>
+        <v>232.6</v>
       </c>
       <c r="J141" t="n">
-        <v>56.1</v>
+        <v>55.8</v>
       </c>
       <c r="K141" t="n">
         <v>23.1</v>
       </c>
       <c r="L141" t="n">
-        <v>37.6</v>
+        <v>38.6</v>
       </c>
     </row>
   </sheetData>
@@ -14776,16 +14776,16 @@
         <v>0.4925</v>
       </c>
       <c r="E140" t="n">
-        <v>46.02538425589233</v>
+        <v>46.05117874668544</v>
       </c>
       <c r="F140" t="n">
-        <v>41.6858688187754</v>
+        <v>41.68649862076933</v>
       </c>
       <c r="G140" t="n">
-        <v>3.101514740364657</v>
+        <v>3.141248781206886</v>
       </c>
       <c r="H140" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="I140" t="n">
         <v>0.4925</v>
@@ -14800,22 +14800,22 @@
         <v>5.8751</v>
       </c>
       <c r="M140" t="n">
-        <v>4.4643</v>
+        <v>4.4737</v>
       </c>
       <c r="N140" t="n">
-        <v>5.1803</v>
+        <v>5.1849</v>
       </c>
       <c r="O140" t="n">
-        <v>4.1566</v>
+        <v>4.1785</v>
       </c>
       <c r="P140" t="n">
-        <v>51.99</v>
+        <v>52.04</v>
       </c>
       <c r="Q140" t="n">
-        <v>48.01</v>
+        <v>47.96</v>
       </c>
       <c r="R140" t="n">
-        <v>3.97</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="141">
@@ -14836,16 +14836,16 @@
         <v>0.4925</v>
       </c>
       <c r="E141" t="n">
-        <v>46.02538425589233</v>
+        <v>46.05117874668544</v>
       </c>
       <c r="F141" t="n">
-        <v>41.6858688187754</v>
+        <v>41.68649862076933</v>
       </c>
       <c r="G141" t="n">
-        <v>3.101514740364657</v>
+        <v>3.141248781206886</v>
       </c>
       <c r="H141" t="n">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="I141" t="n">
         <v>0.4925</v>
@@ -14860,22 +14860,22 @@
         <v>5.8751</v>
       </c>
       <c r="M141" t="n">
-        <v>4.4643</v>
+        <v>4.4737</v>
       </c>
       <c r="N141" t="n">
-        <v>5.1803</v>
+        <v>5.1849</v>
       </c>
       <c r="O141" t="n">
-        <v>4.1566</v>
+        <v>4.1785</v>
       </c>
       <c r="P141" t="n">
-        <v>51.99</v>
+        <v>52.04</v>
       </c>
       <c r="Q141" t="n">
-        <v>48.01</v>
+        <v>47.96</v>
       </c>
       <c r="R141" t="n">
-        <v>3.97</v>
+        <v>4.09</v>
       </c>
     </row>
   </sheetData>
@@ -19927,22 +19927,22 @@
         <v>168</v>
       </c>
       <c r="D140" t="n">
-        <v>41.83</v>
+        <v>41.81</v>
       </c>
       <c r="E140" t="n">
-        <v>55.21</v>
+        <v>55.23</v>
       </c>
       <c r="F140" t="n">
-        <v>-13.39</v>
+        <v>-13.42</v>
       </c>
       <c r="G140" t="n">
         <v>25</v>
       </c>
       <c r="H140" t="n">
-        <v>-5.62</v>
+        <v>-5.63</v>
       </c>
       <c r="I140" t="n">
-        <v>5.62</v>
+        <v>5.63</v>
       </c>
       <c r="J140" t="n">
         <v>0.151</v>
@@ -19963,22 +19963,22 @@
         <v>168</v>
       </c>
       <c r="D141" t="n">
-        <v>41.83</v>
+        <v>41.81</v>
       </c>
       <c r="E141" t="n">
-        <v>55.21</v>
+        <v>55.23</v>
       </c>
       <c r="F141" t="n">
-        <v>-13.39</v>
+        <v>-13.42</v>
       </c>
       <c r="G141" t="n">
         <v>25</v>
       </c>
       <c r="H141" t="n">
-        <v>-5.62</v>
+        <v>-5.63</v>
       </c>
       <c r="I141" t="n">
-        <v>5.62</v>
+        <v>5.63</v>
       </c>
       <c r="J141" t="n">
         <v>0.151</v>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6333,43 +6333,85 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D141" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E141" t="n">
-        <v>4.09</v>
+        <v>4.42</v>
       </c>
       <c r="F141" t="n">
-        <v>0.1879</v>
+        <v>0.1898</v>
       </c>
       <c r="G141" t="n">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
       <c r="H141" t="n">
-        <v>35.9</v>
+        <v>39.3</v>
       </c>
       <c r="I141" t="n">
-        <v>232.6</v>
+        <v>234.9</v>
       </c>
       <c r="J141" t="n">
-        <v>55.8</v>
+        <v>57</v>
       </c>
       <c r="K141" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="L141" t="n">
-        <v>38.6</v>
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>167</v>
+      </c>
+      <c r="D142" t="n">
+        <v>167</v>
+      </c>
+      <c r="E142" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.1898</v>
+      </c>
+      <c r="G142" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="H142" t="n">
+        <v>39.3</v>
+      </c>
+      <c r="I142" t="n">
+        <v>234.9</v>
+      </c>
+      <c r="J142" t="n">
+        <v>57</v>
+      </c>
+      <c r="K142" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L142" t="n">
+        <v>37.4</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +6425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R141"/>
+  <dimension ref="A1:R142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14821,61 +14863,121 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D141" t="n">
-        <v>0.4925</v>
+        <v>0.4936</v>
       </c>
       <c r="E141" t="n">
-        <v>46.05117874668544</v>
+        <v>46.01252811601282</v>
       </c>
       <c r="F141" t="n">
-        <v>41.68649862076933</v>
+        <v>41.64428513141204</v>
       </c>
       <c r="G141" t="n">
-        <v>3.141248781206886</v>
+        <v>3.143973063379363</v>
       </c>
       <c r="H141" t="n">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="I141" t="n">
-        <v>0.4925</v>
+        <v>0.4936</v>
       </c>
       <c r="J141" t="n">
-        <v>0.2499</v>
+        <v>0.25</v>
       </c>
       <c r="K141" t="n">
-        <v>0.2576</v>
+        <v>0.2564</v>
       </c>
       <c r="L141" t="n">
-        <v>5.8751</v>
+        <v>6.0709</v>
       </c>
       <c r="M141" t="n">
-        <v>4.4737</v>
+        <v>4.5102</v>
       </c>
       <c r="N141" t="n">
-        <v>5.1849</v>
+        <v>5.3005</v>
       </c>
       <c r="O141" t="n">
-        <v>4.1785</v>
+        <v>4.2359</v>
       </c>
       <c r="P141" t="n">
-        <v>52.04</v>
+        <v>52.21</v>
       </c>
       <c r="Q141" t="n">
-        <v>47.96</v>
+        <v>47.79</v>
       </c>
       <c r="R141" t="n">
-        <v>4.09</v>
+        <v>4.42</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>167</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="E142" t="n">
+        <v>46.01252811601282</v>
+      </c>
+      <c r="F142" t="n">
+        <v>41.64428513141204</v>
+      </c>
+      <c r="G142" t="n">
+        <v>3.143973063379363</v>
+      </c>
+      <c r="H142" t="n">
+        <v>553</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="L142" t="n">
+        <v>6.0709</v>
+      </c>
+      <c r="M142" t="n">
+        <v>4.5102</v>
+      </c>
+      <c r="N142" t="n">
+        <v>5.3005</v>
+      </c>
+      <c r="O142" t="n">
+        <v>4.2359</v>
+      </c>
+      <c r="P142" t="n">
+        <v>52.21</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>47.79</v>
+      </c>
+      <c r="R142" t="n">
+        <v>4.42</v>
       </c>
     </row>
   </sheetData>
@@ -14889,7 +14991,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J141"/>
+  <dimension ref="A1:J142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19951,36 +20053,72 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D141" t="n">
-        <v>41.81</v>
+        <v>41.74</v>
       </c>
       <c r="E141" t="n">
-        <v>55.23</v>
+        <v>55.34</v>
       </c>
       <c r="F141" t="n">
-        <v>-13.42</v>
+        <v>-13.6</v>
       </c>
       <c r="G141" t="n">
         <v>25</v>
       </c>
       <c r="H141" t="n">
-        <v>-5.63</v>
+        <v>-5.64</v>
       </c>
       <c r="I141" t="n">
-        <v>5.63</v>
+        <v>5.64</v>
       </c>
       <c r="J141" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>167</v>
+      </c>
+      <c r="D142" t="n">
+        <v>41.74</v>
+      </c>
+      <c r="E142" t="n">
+        <v>55.34</v>
+      </c>
+      <c r="F142" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="G142" t="n">
+        <v>25</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="I142" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="J142" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -6348,28 +6348,28 @@
         <v>167</v>
       </c>
       <c r="E141" t="n">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="F141" t="n">
         <v>0.1898</v>
       </c>
       <c r="G141" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="H141" t="n">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="I141" t="n">
-        <v>234.9</v>
+        <v>233.2</v>
       </c>
       <c r="J141" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="K141" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="L141" t="n">
-        <v>37.4</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="142">
@@ -6390,28 +6390,28 @@
         <v>167</v>
       </c>
       <c r="E142" t="n">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
       <c r="F142" t="n">
         <v>0.1898</v>
       </c>
       <c r="G142" t="n">
-        <v>49.6</v>
+        <v>49.5</v>
       </c>
       <c r="H142" t="n">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="I142" t="n">
-        <v>234.9</v>
+        <v>233.2</v>
       </c>
       <c r="J142" t="n">
-        <v>57</v>
+        <v>56.5</v>
       </c>
       <c r="K142" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="L142" t="n">
-        <v>37.4</v>
+        <v>41.2</v>
       </c>
     </row>
   </sheetData>
@@ -14911,13 +14911,13 @@
         <v>4.2359</v>
       </c>
       <c r="P141" t="n">
-        <v>52.21</v>
+        <v>52.1</v>
       </c>
       <c r="Q141" t="n">
-        <v>47.79</v>
+        <v>47.9</v>
       </c>
       <c r="R141" t="n">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="142">
@@ -14971,13 +14971,13 @@
         <v>4.2359</v>
       </c>
       <c r="P142" t="n">
-        <v>52.21</v>
+        <v>52.1</v>
       </c>
       <c r="Q142" t="n">
-        <v>47.79</v>
+        <v>47.9</v>
       </c>
       <c r="R142" t="n">
-        <v>4.42</v>
+        <v>4.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -6348,28 +6348,28 @@
         <v>167</v>
       </c>
       <c r="E141" t="n">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
       <c r="F141" t="n">
         <v>0.1898</v>
       </c>
       <c r="G141" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="H141" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="I141" t="n">
-        <v>233.2</v>
+        <v>237.4</v>
       </c>
       <c r="J141" t="n">
-        <v>56.5</v>
+        <v>60.2</v>
       </c>
       <c r="K141" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="L141" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142">
@@ -6390,28 +6390,28 @@
         <v>167</v>
       </c>
       <c r="E142" t="n">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
       <c r="F142" t="n">
         <v>0.1898</v>
       </c>
       <c r="G142" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="H142" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="I142" t="n">
-        <v>233.2</v>
+        <v>237.4</v>
       </c>
       <c r="J142" t="n">
-        <v>56.5</v>
+        <v>60.2</v>
       </c>
       <c r="K142" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="L142" t="n">
-        <v>41.2</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -14878,16 +14878,16 @@
         <v>0.4936</v>
       </c>
       <c r="E141" t="n">
-        <v>46.01252811601282</v>
+        <v>46.04079087789657</v>
       </c>
       <c r="F141" t="n">
-        <v>41.64428513141204</v>
+        <v>41.62554272940991</v>
       </c>
       <c r="G141" t="n">
-        <v>3.143973063379363</v>
+        <v>3.195508712238839</v>
       </c>
       <c r="H141" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I141" t="n">
         <v>0.4936</v>
@@ -14902,22 +14902,22 @@
         <v>6.0709</v>
       </c>
       <c r="M141" t="n">
-        <v>4.5102</v>
+        <v>4.5387</v>
       </c>
       <c r="N141" t="n">
-        <v>5.3005</v>
+        <v>5.3145</v>
       </c>
       <c r="O141" t="n">
-        <v>4.2359</v>
+        <v>4.2685</v>
       </c>
       <c r="P141" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="Q141" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="R141" t="n">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="142">
@@ -14938,16 +14938,16 @@
         <v>0.4936</v>
       </c>
       <c r="E142" t="n">
-        <v>46.01252811601282</v>
+        <v>46.04079087789657</v>
       </c>
       <c r="F142" t="n">
-        <v>41.64428513141204</v>
+        <v>41.62554272940991</v>
       </c>
       <c r="G142" t="n">
-        <v>3.143973063379363</v>
+        <v>3.195508712238839</v>
       </c>
       <c r="H142" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="I142" t="n">
         <v>0.4936</v>
@@ -14962,22 +14962,22 @@
         <v>6.0709</v>
       </c>
       <c r="M142" t="n">
-        <v>4.5102</v>
+        <v>4.5387</v>
       </c>
       <c r="N142" t="n">
-        <v>5.3005</v>
+        <v>5.3145</v>
       </c>
       <c r="O142" t="n">
-        <v>4.2359</v>
+        <v>4.2685</v>
       </c>
       <c r="P142" t="n">
-        <v>52.1</v>
+        <v>52</v>
       </c>
       <c r="Q142" t="n">
-        <v>47.9</v>
+        <v>48</v>
       </c>
       <c r="R142" t="n">
-        <v>4.2</v>
+        <v>4.01</v>
       </c>
     </row>
   </sheetData>
@@ -20065,22 +20065,22 @@
         <v>167</v>
       </c>
       <c r="D141" t="n">
-        <v>41.74</v>
+        <v>41.68</v>
       </c>
       <c r="E141" t="n">
         <v>55.34</v>
       </c>
       <c r="F141" t="n">
-        <v>-13.6</v>
+        <v>-13.66</v>
       </c>
       <c r="G141" t="n">
         <v>25</v>
       </c>
       <c r="H141" t="n">
-        <v>-5.64</v>
+        <v>-5.65</v>
       </c>
       <c r="I141" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="J141" t="n">
         <v>0.151</v>
@@ -20101,22 +20101,22 @@
         <v>167</v>
       </c>
       <c r="D142" t="n">
-        <v>41.74</v>
+        <v>41.68</v>
       </c>
       <c r="E142" t="n">
         <v>55.34</v>
       </c>
       <c r="F142" t="n">
-        <v>-13.6</v>
+        <v>-13.66</v>
       </c>
       <c r="G142" t="n">
         <v>25</v>
       </c>
       <c r="H142" t="n">
-        <v>-5.64</v>
+        <v>-5.65</v>
       </c>
       <c r="I142" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="J142" t="n">
         <v>0.151</v>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -6348,7 +6348,7 @@
         <v>167</v>
       </c>
       <c r="E141" t="n">
-        <v>4.01</v>
+        <v>4.46</v>
       </c>
       <c r="F141" t="n">
         <v>0.1898</v>
@@ -6357,19 +6357,19 @@
         <v>49.7</v>
       </c>
       <c r="H141" t="n">
-        <v>39.4</v>
+        <v>43.4</v>
       </c>
       <c r="I141" t="n">
-        <v>237.4</v>
+        <v>235.2</v>
       </c>
       <c r="J141" t="n">
-        <v>60.2</v>
+        <v>58.1</v>
       </c>
       <c r="K141" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="L141" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="142">
@@ -6390,7 +6390,7 @@
         <v>167</v>
       </c>
       <c r="E142" t="n">
-        <v>4.01</v>
+        <v>4.46</v>
       </c>
       <c r="F142" t="n">
         <v>0.1898</v>
@@ -6399,19 +6399,19 @@
         <v>49.7</v>
       </c>
       <c r="H142" t="n">
-        <v>39.4</v>
+        <v>43.4</v>
       </c>
       <c r="I142" t="n">
-        <v>237.4</v>
+        <v>235.2</v>
       </c>
       <c r="J142" t="n">
-        <v>60.2</v>
+        <v>58.1</v>
       </c>
       <c r="K142" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="L142" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -14911,13 +14911,13 @@
         <v>4.2685</v>
       </c>
       <c r="P141" t="n">
-        <v>52</v>
+        <v>52.23</v>
       </c>
       <c r="Q141" t="n">
-        <v>48</v>
+        <v>47.77</v>
       </c>
       <c r="R141" t="n">
-        <v>4.01</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="142">
@@ -14971,13 +14971,13 @@
         <v>4.2685</v>
       </c>
       <c r="P142" t="n">
-        <v>52</v>
+        <v>52.23</v>
       </c>
       <c r="Q142" t="n">
-        <v>48</v>
+        <v>47.77</v>
       </c>
       <c r="R142" t="n">
-        <v>4.01</v>
+        <v>4.46</v>
       </c>
     </row>
   </sheetData>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L142"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6375,43 +6375,85 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D142" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E142" t="n">
-        <v>4.46</v>
+        <v>4.3</v>
       </c>
       <c r="F142" t="n">
-        <v>0.1898</v>
+        <v>0.1917</v>
       </c>
       <c r="G142" t="n">
-        <v>49.7</v>
+        <v>49.5</v>
       </c>
       <c r="H142" t="n">
-        <v>43.4</v>
+        <v>41.3</v>
       </c>
       <c r="I142" t="n">
-        <v>235.2</v>
+        <v>234.1</v>
       </c>
       <c r="J142" t="n">
-        <v>58.1</v>
+        <v>57.7</v>
       </c>
       <c r="K142" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="L142" t="n">
-        <v>41</v>
+        <v>40.8</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>166</v>
+      </c>
+      <c r="D143" t="n">
+        <v>166</v>
+      </c>
+      <c r="E143" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.1917</v>
+      </c>
+      <c r="G143" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="H143" t="n">
+        <v>41.3</v>
+      </c>
+      <c r="I143" t="n">
+        <v>234.1</v>
+      </c>
+      <c r="J143" t="n">
+        <v>57.7</v>
+      </c>
+      <c r="K143" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L143" t="n">
+        <v>40.8</v>
       </c>
     </row>
   </sheetData>
@@ -6425,7 +6467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R142"/>
+  <dimension ref="A1:R143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14923,19 +14965,19 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D142" t="n">
-        <v>0.4936</v>
+        <v>0.4948</v>
       </c>
       <c r="E142" t="n">
         <v>46.04079087789657</v>
@@ -14950,34 +14992,94 @@
         <v>554</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4936</v>
+        <v>0.4948</v>
       </c>
       <c r="J142" t="n">
         <v>0.25</v>
       </c>
       <c r="K142" t="n">
-        <v>0.2564</v>
+        <v>0.2552</v>
       </c>
       <c r="L142" t="n">
-        <v>6.0709</v>
+        <v>5.9672</v>
       </c>
       <c r="M142" t="n">
-        <v>4.5387</v>
+        <v>4.5757</v>
       </c>
       <c r="N142" t="n">
-        <v>5.3145</v>
+        <v>5.2787</v>
       </c>
       <c r="O142" t="n">
-        <v>4.2685</v>
+        <v>4.2479</v>
       </c>
       <c r="P142" t="n">
-        <v>52.23</v>
+        <v>52.15</v>
       </c>
       <c r="Q142" t="n">
-        <v>47.77</v>
+        <v>47.85</v>
       </c>
       <c r="R142" t="n">
-        <v>4.46</v>
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>166</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="E143" t="n">
+        <v>46.04079087789657</v>
+      </c>
+      <c r="F143" t="n">
+        <v>41.62554272940991</v>
+      </c>
+      <c r="G143" t="n">
+        <v>3.195508712238839</v>
+      </c>
+      <c r="H143" t="n">
+        <v>554</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.2552</v>
+      </c>
+      <c r="L143" t="n">
+        <v>5.9672</v>
+      </c>
+      <c r="M143" t="n">
+        <v>4.5757</v>
+      </c>
+      <c r="N143" t="n">
+        <v>5.2787</v>
+      </c>
+      <c r="O143" t="n">
+        <v>4.2479</v>
+      </c>
+      <c r="P143" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>47.85</v>
+      </c>
+      <c r="R143" t="n">
+        <v>4.3</v>
       </c>
     </row>
   </sheetData>
@@ -14991,7 +15093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J142"/>
+  <dimension ref="A1:J143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20089,36 +20191,72 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D142" t="n">
-        <v>41.68</v>
+        <v>41.61</v>
       </c>
       <c r="E142" t="n">
-        <v>55.34</v>
+        <v>55.42</v>
       </c>
       <c r="F142" t="n">
-        <v>-13.66</v>
+        <v>-13.81</v>
       </c>
       <c r="G142" t="n">
         <v>25</v>
       </c>
       <c r="H142" t="n">
-        <v>-5.65</v>
+        <v>-5.67</v>
       </c>
       <c r="I142" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="J142" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>166</v>
+      </c>
+      <c r="D143" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E143" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-13.81</v>
+      </c>
+      <c r="G143" t="n">
+        <v>25</v>
+      </c>
+      <c r="H143" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="I143" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="J143" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L143"/>
+  <dimension ref="A1:L144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6417,43 +6417,85 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D143" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E143" t="n">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="F143" t="n">
-        <v>0.1917</v>
+        <v>0.1936</v>
       </c>
       <c r="G143" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="H143" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="I143" t="n">
+        <v>235</v>
+      </c>
+      <c r="J143" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="K143" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L143" t="n">
         <v>41.3</v>
       </c>
-      <c r="I143" t="n">
-        <v>234.1</v>
-      </c>
-      <c r="J143" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="K143" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="L143" t="n">
-        <v>40.8</v>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>165</v>
+      </c>
+      <c r="D144" t="n">
+        <v>165</v>
+      </c>
+      <c r="E144" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="F144" t="n">
+        <v>0.1936</v>
+      </c>
+      <c r="G144" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="H144" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="I144" t="n">
+        <v>235</v>
+      </c>
+      <c r="J144" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="K144" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L144" t="n">
+        <v>41.3</v>
       </c>
     </row>
   </sheetData>
@@ -6467,7 +6509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R143"/>
+  <dimension ref="A1:R144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15025,61 +15067,121 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D143" t="n">
-        <v>0.4948</v>
+        <v>0.496</v>
       </c>
       <c r="E143" t="n">
-        <v>46.04079087789657</v>
+        <v>46.07217102427733</v>
       </c>
       <c r="F143" t="n">
-        <v>41.62554272940991</v>
+        <v>41.63423981583707</v>
       </c>
       <c r="G143" t="n">
-        <v>3.195508712238839</v>
+        <v>3.215830743483078</v>
       </c>
       <c r="H143" t="n">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I143" t="n">
-        <v>0.4948</v>
+        <v>0.496</v>
       </c>
       <c r="J143" t="n">
         <v>0.25</v>
       </c>
       <c r="K143" t="n">
-        <v>0.2552</v>
+        <v>0.254</v>
       </c>
       <c r="L143" t="n">
-        <v>5.9672</v>
+        <v>5.9079</v>
       </c>
       <c r="M143" t="n">
-        <v>4.5757</v>
+        <v>4.5724</v>
       </c>
       <c r="N143" t="n">
-        <v>5.2787</v>
+        <v>5.2454</v>
       </c>
       <c r="O143" t="n">
-        <v>4.2479</v>
+        <v>4.2387</v>
       </c>
       <c r="P143" t="n">
-        <v>52.15</v>
+        <v>52.17</v>
       </c>
       <c r="Q143" t="n">
-        <v>47.85</v>
+        <v>47.83</v>
       </c>
       <c r="R143" t="n">
-        <v>4.3</v>
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>165</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="E144" t="n">
+        <v>46.07217102427733</v>
+      </c>
+      <c r="F144" t="n">
+        <v>41.63423981583707</v>
+      </c>
+      <c r="G144" t="n">
+        <v>3.215830743483078</v>
+      </c>
+      <c r="H144" t="n">
+        <v>555</v>
+      </c>
+      <c r="I144" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="L144" t="n">
+        <v>5.9079</v>
+      </c>
+      <c r="M144" t="n">
+        <v>4.5724</v>
+      </c>
+      <c r="N144" t="n">
+        <v>5.2454</v>
+      </c>
+      <c r="O144" t="n">
+        <v>4.2387</v>
+      </c>
+      <c r="P144" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="Q144" t="n">
+        <v>47.83</v>
+      </c>
+      <c r="R144" t="n">
+        <v>4.34</v>
       </c>
     </row>
   </sheetData>
@@ -15093,7 +15195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J143"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20227,16 +20329,16 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D143" t="n">
         <v>41.61</v>
@@ -20257,6 +20359,42 @@
         <v>5.67</v>
       </c>
       <c r="J143" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>165</v>
+      </c>
+      <c r="D144" t="n">
+        <v>41.61</v>
+      </c>
+      <c r="E144" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="F144" t="n">
+        <v>-13.81</v>
+      </c>
+      <c r="G144" t="n">
+        <v>25</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-5.67</v>
+      </c>
+      <c r="I144" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="J144" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -6432,7 +6432,7 @@
         <v>165</v>
       </c>
       <c r="E143" t="n">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="F143" t="n">
         <v>0.1936</v>
@@ -6441,19 +6441,19 @@
         <v>49.6</v>
       </c>
       <c r="H143" t="n">
-        <v>44.1</v>
+        <v>41.9</v>
       </c>
       <c r="I143" t="n">
-        <v>235</v>
+        <v>233.6</v>
       </c>
       <c r="J143" t="n">
-        <v>59.1</v>
+        <v>56.9</v>
       </c>
       <c r="K143" t="n">
         <v>23.4</v>
       </c>
       <c r="L143" t="n">
-        <v>41.3</v>
+        <v>42.8</v>
       </c>
     </row>
     <row r="144">
@@ -6474,7 +6474,7 @@
         <v>165</v>
       </c>
       <c r="E144" t="n">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="F144" t="n">
         <v>0.1936</v>
@@ -6483,19 +6483,19 @@
         <v>49.6</v>
       </c>
       <c r="H144" t="n">
-        <v>44.1</v>
+        <v>41.9</v>
       </c>
       <c r="I144" t="n">
-        <v>235</v>
+        <v>233.6</v>
       </c>
       <c r="J144" t="n">
-        <v>59.1</v>
+        <v>56.9</v>
       </c>
       <c r="K144" t="n">
         <v>23.4</v>
       </c>
       <c r="L144" t="n">
-        <v>41.3</v>
+        <v>42.8</v>
       </c>
     </row>
   </sheetData>
@@ -15082,16 +15082,16 @@
         <v>0.496</v>
       </c>
       <c r="E143" t="n">
-        <v>46.07217102427733</v>
+        <v>46.10114953881143</v>
       </c>
       <c r="F143" t="n">
-        <v>41.63423981583707</v>
+        <v>41.63425321689331</v>
       </c>
       <c r="G143" t="n">
-        <v>3.215830743483078</v>
+        <v>3.234638709551942</v>
       </c>
       <c r="H143" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="I143" t="n">
         <v>0.496</v>
@@ -15106,22 +15106,22 @@
         <v>5.9079</v>
       </c>
       <c r="M143" t="n">
-        <v>4.5724</v>
+        <v>4.5681</v>
       </c>
       <c r="N143" t="n">
-        <v>5.2454</v>
+        <v>5.2433</v>
       </c>
       <c r="O143" t="n">
-        <v>4.2387</v>
+        <v>4.247</v>
       </c>
       <c r="P143" t="n">
-        <v>52.17</v>
+        <v>52.12</v>
       </c>
       <c r="Q143" t="n">
-        <v>47.83</v>
+        <v>47.88</v>
       </c>
       <c r="R143" t="n">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="144">
@@ -15142,16 +15142,16 @@
         <v>0.496</v>
       </c>
       <c r="E144" t="n">
-        <v>46.07217102427733</v>
+        <v>46.10114953881143</v>
       </c>
       <c r="F144" t="n">
-        <v>41.63423981583707</v>
+        <v>41.63425321689331</v>
       </c>
       <c r="G144" t="n">
-        <v>3.215830743483078</v>
+        <v>3.234638709551942</v>
       </c>
       <c r="H144" t="n">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="I144" t="n">
         <v>0.496</v>
@@ -15166,22 +15166,22 @@
         <v>5.9079</v>
       </c>
       <c r="M144" t="n">
-        <v>4.5724</v>
+        <v>4.5681</v>
       </c>
       <c r="N144" t="n">
-        <v>5.2454</v>
+        <v>5.2433</v>
       </c>
       <c r="O144" t="n">
-        <v>4.2387</v>
+        <v>4.247</v>
       </c>
       <c r="P144" t="n">
-        <v>52.17</v>
+        <v>52.12</v>
       </c>
       <c r="Q144" t="n">
-        <v>47.83</v>
+        <v>47.88</v>
       </c>
       <c r="R144" t="n">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
     </row>
   </sheetData>
@@ -20341,22 +20341,22 @@
         <v>165</v>
       </c>
       <c r="D143" t="n">
-        <v>41.61</v>
+        <v>41.63</v>
       </c>
       <c r="E143" t="n">
-        <v>55.42</v>
+        <v>55.43</v>
       </c>
       <c r="F143" t="n">
-        <v>-13.81</v>
+        <v>-13.8</v>
       </c>
       <c r="G143" t="n">
         <v>25</v>
       </c>
       <c r="H143" t="n">
-        <v>-5.67</v>
+        <v>-5.66</v>
       </c>
       <c r="I143" t="n">
-        <v>5.67</v>
+        <v>5.66</v>
       </c>
       <c r="J143" t="n">
         <v>0.151</v>
@@ -20377,22 +20377,22 @@
         <v>165</v>
       </c>
       <c r="D144" t="n">
-        <v>41.61</v>
+        <v>41.63</v>
       </c>
       <c r="E144" t="n">
-        <v>55.42</v>
+        <v>55.43</v>
       </c>
       <c r="F144" t="n">
-        <v>-13.81</v>
+        <v>-13.8</v>
       </c>
       <c r="G144" t="n">
         <v>25</v>
       </c>
       <c r="H144" t="n">
-        <v>-5.67</v>
+        <v>-5.66</v>
       </c>
       <c r="I144" t="n">
-        <v>5.67</v>
+        <v>5.66</v>
       </c>
       <c r="J144" t="n">
         <v>0.151</v>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L144"/>
+  <dimension ref="A1:L145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6459,43 +6459,85 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D144" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E144" t="n">
-        <v>4.24</v>
+        <v>4.06</v>
       </c>
       <c r="F144" t="n">
-        <v>0.1936</v>
+        <v>0.1956</v>
       </c>
       <c r="G144" t="n">
         <v>49.6</v>
       </c>
       <c r="H144" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="I144" t="n">
-        <v>233.6</v>
+        <v>233.1</v>
       </c>
       <c r="J144" t="n">
-        <v>56.9</v>
+        <v>57.1</v>
       </c>
       <c r="K144" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="L144" t="n">
-        <v>42.8</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>164</v>
+      </c>
+      <c r="D145" t="n">
+        <v>164</v>
+      </c>
+      <c r="E145" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.1956</v>
+      </c>
+      <c r="G145" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="H145" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="I145" t="n">
+        <v>233.1</v>
+      </c>
+      <c r="J145" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="K145" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L145" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -6509,7 +6551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R144"/>
+  <dimension ref="A1:R145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15127,61 +15169,121 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D144" t="n">
-        <v>0.496</v>
+        <v>0.4972</v>
       </c>
       <c r="E144" t="n">
-        <v>46.10114953881143</v>
+        <v>46.10058695993109</v>
       </c>
       <c r="F144" t="n">
-        <v>41.63425321689331</v>
+        <v>41.63628744678844</v>
       </c>
       <c r="G144" t="n">
-        <v>3.234638709551942</v>
+        <v>3.248332511928131</v>
       </c>
       <c r="H144" t="n">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="I144" t="n">
-        <v>0.496</v>
+        <v>0.4972</v>
       </c>
       <c r="J144" t="n">
         <v>0.25</v>
       </c>
       <c r="K144" t="n">
-        <v>0.254</v>
+        <v>0.2528</v>
       </c>
       <c r="L144" t="n">
-        <v>5.9079</v>
+        <v>5.6934</v>
       </c>
       <c r="M144" t="n">
         <v>4.5681</v>
       </c>
       <c r="N144" t="n">
-        <v>5.2433</v>
+        <v>5.1338</v>
       </c>
       <c r="O144" t="n">
-        <v>4.247</v>
+        <v>4.1963</v>
       </c>
       <c r="P144" t="n">
-        <v>52.12</v>
+        <v>52.03</v>
       </c>
       <c r="Q144" t="n">
-        <v>47.88</v>
+        <v>47.97</v>
       </c>
       <c r="R144" t="n">
-        <v>4.24</v>
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>164</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="E145" t="n">
+        <v>46.10058695993109</v>
+      </c>
+      <c r="F145" t="n">
+        <v>41.63628744678844</v>
+      </c>
+      <c r="G145" t="n">
+        <v>3.248332511928131</v>
+      </c>
+      <c r="H145" t="n">
+        <v>558</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="L145" t="n">
+        <v>5.6934</v>
+      </c>
+      <c r="M145" t="n">
+        <v>4.5681</v>
+      </c>
+      <c r="N145" t="n">
+        <v>5.1338</v>
+      </c>
+      <c r="O145" t="n">
+        <v>4.1963</v>
+      </c>
+      <c r="P145" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>47.97</v>
+      </c>
+      <c r="R145" t="n">
+        <v>4.06</v>
       </c>
     </row>
   </sheetData>
@@ -15195,7 +15297,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20365,16 +20467,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D144" t="n">
         <v>41.63</v>
@@ -20395,6 +20497,42 @@
         <v>5.66</v>
       </c>
       <c r="J144" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>164</v>
+      </c>
+      <c r="D145" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="E145" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="G145" t="n">
+        <v>25</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="I145" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="J145" t="n">
         <v>0.151</v>
       </c>
     </row>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L145"/>
+  <dimension ref="A1:L144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6495,48 +6495,6 @@
         <v>23.2</v>
       </c>
       <c r="L144" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>164</v>
-      </c>
-      <c r="D145" t="n">
-        <v>164</v>
-      </c>
-      <c r="E145" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.1956</v>
-      </c>
-      <c r="G145" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="H145" t="n">
-        <v>41.4</v>
-      </c>
-      <c r="I145" t="n">
-        <v>233.1</v>
-      </c>
-      <c r="J145" t="n">
-        <v>57.1</v>
-      </c>
-      <c r="K145" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="L145" t="n">
         <v>42</v>
       </c>
     </row>
@@ -6551,7 +6509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R145"/>
+  <dimension ref="A1:R144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15223,66 +15181,6 @@
         <v>47.97</v>
       </c>
       <c r="R144" t="n">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>164</v>
-      </c>
-      <c r="D145" t="n">
-        <v>0.4972</v>
-      </c>
-      <c r="E145" t="n">
-        <v>46.10058695993109</v>
-      </c>
-      <c r="F145" t="n">
-        <v>41.63628744678844</v>
-      </c>
-      <c r="G145" t="n">
-        <v>3.248332511928131</v>
-      </c>
-      <c r="H145" t="n">
-        <v>558</v>
-      </c>
-      <c r="I145" t="n">
-        <v>0.4972</v>
-      </c>
-      <c r="J145" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K145" t="n">
-        <v>0.2528</v>
-      </c>
-      <c r="L145" t="n">
-        <v>5.6934</v>
-      </c>
-      <c r="M145" t="n">
-        <v>4.5681</v>
-      </c>
-      <c r="N145" t="n">
-        <v>5.1338</v>
-      </c>
-      <c r="O145" t="n">
-        <v>4.1963</v>
-      </c>
-      <c r="P145" t="n">
-        <v>52.03</v>
-      </c>
-      <c r="Q145" t="n">
-        <v>47.97</v>
-      </c>
-      <c r="R145" t="n">
         <v>4.06</v>
       </c>
     </row>
@@ -15297,7 +15195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J145"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20500,42 +20398,6 @@
         <v>0.151</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>164</v>
-      </c>
-      <c r="D145" t="n">
-        <v>41.63</v>
-      </c>
-      <c r="E145" t="n">
-        <v>55.43</v>
-      </c>
-      <c r="F145" t="n">
-        <v>-13.8</v>
-      </c>
-      <c r="G145" t="n">
-        <v>25</v>
-      </c>
-      <c r="H145" t="n">
-        <v>-5.66</v>
-      </c>
-      <c r="I145" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="J145" t="n">
-        <v>0.151</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L144"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6496,6 +6496,90 @@
       </c>
       <c r="L144" t="n">
         <v>42</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>163</v>
+      </c>
+      <c r="D145" t="n">
+        <v>163</v>
+      </c>
+      <c r="E145" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F145" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="G145" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="H145" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="I145" t="n">
+        <v>234.2</v>
+      </c>
+      <c r="J145" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="K145" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L145" t="n">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>163</v>
+      </c>
+      <c r="D146" t="n">
+        <v>163</v>
+      </c>
+      <c r="E146" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0.1975</v>
+      </c>
+      <c r="G146" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="H146" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="I146" t="n">
+        <v>234.2</v>
+      </c>
+      <c r="J146" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="K146" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="L146" t="n">
+        <v>43.6</v>
       </c>
     </row>
   </sheetData>
@@ -6509,7 +6593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R144"/>
+  <dimension ref="A1:R146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15182,6 +15266,126 @@
       </c>
       <c r="R144" t="n">
         <v>4.06</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>163</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="E145" t="n">
+        <v>46.10058695993109</v>
+      </c>
+      <c r="F145" t="n">
+        <v>41.63628744678844</v>
+      </c>
+      <c r="G145" t="n">
+        <v>3.248332511928131</v>
+      </c>
+      <c r="H145" t="n">
+        <v>558</v>
+      </c>
+      <c r="I145" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K145" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="L145" t="n">
+        <v>5.6934</v>
+      </c>
+      <c r="M145" t="n">
+        <v>4.5681</v>
+      </c>
+      <c r="N145" t="n">
+        <v>5.1325</v>
+      </c>
+      <c r="O145" t="n">
+        <v>4.1933</v>
+      </c>
+      <c r="P145" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="Q145" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="R145" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>163</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="E146" t="n">
+        <v>46.10058695993109</v>
+      </c>
+      <c r="F146" t="n">
+        <v>41.63628744678844</v>
+      </c>
+      <c r="G146" t="n">
+        <v>3.248332511928131</v>
+      </c>
+      <c r="H146" t="n">
+        <v>558</v>
+      </c>
+      <c r="I146" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="L146" t="n">
+        <v>5.6934</v>
+      </c>
+      <c r="M146" t="n">
+        <v>4.5681</v>
+      </c>
+      <c r="N146" t="n">
+        <v>5.1325</v>
+      </c>
+      <c r="O146" t="n">
+        <v>4.1933</v>
+      </c>
+      <c r="P146" t="n">
+        <v>52.16</v>
+      </c>
+      <c r="Q146" t="n">
+        <v>47.84</v>
+      </c>
+      <c r="R146" t="n">
+        <v>4.33</v>
       </c>
     </row>
   </sheetData>
@@ -15195,7 +15399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20398,6 +20602,78 @@
         <v>0.151</v>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>163</v>
+      </c>
+      <c r="D145" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="E145" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="F145" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="G145" t="n">
+        <v>25</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="I145" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>163</v>
+      </c>
+      <c r="D146" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="E146" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="F146" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="G146" t="n">
+        <v>25</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="I146" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/summary.xlsx
+++ b/output/summary.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6543,43 +6543,85 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D146" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E146" t="n">
-        <v>4.33</v>
+        <v>4.09</v>
       </c>
       <c r="F146" t="n">
-        <v>0.1975</v>
+        <v>0.1995</v>
       </c>
       <c r="G146" t="n">
-        <v>49.7</v>
+        <v>49.6</v>
       </c>
       <c r="H146" t="n">
-        <v>41.2</v>
+        <v>40.9</v>
       </c>
       <c r="I146" t="n">
-        <v>234.2</v>
+        <v>232.9</v>
       </c>
       <c r="J146" t="n">
-        <v>57.2</v>
+        <v>57.5</v>
       </c>
       <c r="K146" t="n">
-        <v>23.4</v>
+        <v>23.2</v>
       </c>
       <c r="L146" t="n">
-        <v>43.6</v>
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>162</v>
+      </c>
+      <c r="D147" t="n">
+        <v>162</v>
+      </c>
+      <c r="E147" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="F147" t="n">
+        <v>0.1995</v>
+      </c>
+      <c r="G147" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="H147" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I147" t="n">
+        <v>232.9</v>
+      </c>
+      <c r="J147" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="K147" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="L147" t="n">
+        <v>40.9</v>
       </c>
     </row>
   </sheetData>
@@ -6593,7 +6635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R146"/>
+  <dimension ref="A1:R147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15331,19 +15373,19 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D146" t="n">
-        <v>0.4985</v>
+        <v>0.4997</v>
       </c>
       <c r="E146" t="n">
         <v>46.10058695993109</v>
@@ -15358,13 +15400,13 @@
         <v>558</v>
       </c>
       <c r="I146" t="n">
-        <v>0.4985</v>
+        <v>0.4997</v>
       </c>
       <c r="J146" t="n">
         <v>0.25</v>
       </c>
       <c r="K146" t="n">
-        <v>0.2516</v>
+        <v>0.2503</v>
       </c>
       <c r="L146" t="n">
         <v>5.6934</v>
@@ -15373,19 +15415,79 @@
         <v>4.5681</v>
       </c>
       <c r="N146" t="n">
-        <v>5.1325</v>
+        <v>5.1311</v>
       </c>
       <c r="O146" t="n">
-        <v>4.1933</v>
+        <v>4.1903</v>
       </c>
       <c r="P146" t="n">
-        <v>52.16</v>
+        <v>52.04</v>
       </c>
       <c r="Q146" t="n">
-        <v>47.84</v>
+        <v>47.96</v>
       </c>
       <c r="R146" t="n">
-        <v>4.33</v>
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>162</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="E147" t="n">
+        <v>46.10058695993109</v>
+      </c>
+      <c r="F147" t="n">
+        <v>41.63628744678844</v>
+      </c>
+      <c r="G147" t="n">
+        <v>3.248332511928131</v>
+      </c>
+      <c r="H147" t="n">
+        <v>558</v>
+      </c>
+      <c r="I147" t="n">
+        <v>0.4997</v>
+      </c>
+      <c r="J147" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0.2503</v>
+      </c>
+      <c r="L147" t="n">
+        <v>5.6934</v>
+      </c>
+      <c r="M147" t="n">
+        <v>4.5681</v>
+      </c>
+      <c r="N147" t="n">
+        <v>5.1311</v>
+      </c>
+      <c r="O147" t="n">
+        <v>4.1903</v>
+      </c>
+      <c r="P147" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="Q147" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="R147" t="n">
+        <v>4.09</v>
       </c>
     </row>
   </sheetData>
@@ -15399,7 +15501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J146"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20641,16 +20743,16 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D146" t="n">
         <v>41.63</v>
@@ -20671,6 +20773,42 @@
         <v>5.66</v>
       </c>
       <c r="J146" t="n">
+        <v>0.151</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>162</v>
+      </c>
+      <c r="D147" t="n">
+        <v>41.63</v>
+      </c>
+      <c r="E147" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="F147" t="n">
+        <v>-13.8</v>
+      </c>
+      <c r="G147" t="n">
+        <v>25</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="I147" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="J147" t="n">
         <v>0.151</v>
       </c>
     </row>
